--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,85 +757,85 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3</v>
+        <v>1.83</v>
       </c>
       <c r="I2" t="n">
         <v>1.94</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.25</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.12</v>
-      </c>
       <c r="S2" t="n">
-        <v>1.46</v>
+        <v>4.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="V2" t="n">
         <v>2.06</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AG2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.21</v>
+        <v>5.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.21</v>
+        <v>3.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.15</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.21</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.21</v>
+        <v>4.3</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.21</v>
+        <v>4.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.16</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.18</v>
+        <v>7.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.21</v>
+        <v>6.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.21</v>
+        <v>6.6</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.19</v>
+        <v>7.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.21</v>
+        <v>8.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.21</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.21</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.21</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.21</v>
+        <v>8.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.15</v>
+        <v>6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
-        <v>420</v>
+        <v>1.77</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="J3" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25</v>
+        <v>2.28</v>
       </c>
       <c r="O3" t="n">
-        <v>1.02</v>
+        <v>1.67</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.7</v>
+        <v>3.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7</v>
+        <v>6.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>2.52</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.76</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.83</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.64</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>2.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.84</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.57</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.65</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1148,10 +1148,10 @@
         <v>2.22</v>
       </c>
       <c r="G4" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
         <v>3.55</v>
@@ -1178,7 +1178,7 @@
         <v>1.96</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G5" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="H5" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>3.5</v>
@@ -1384,7 +1384,7 @@
         <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1417,13 +1417,13 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AG5" t="n">
         <v>11.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1435,13 +1435,13 @@
         <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM5" t="n">
         <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1474,7 +1474,7 @@
         <v>9.6</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
         <v>19</v>
@@ -1489,7 +1489,7 @@
         <v>6.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
         <v>7.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H6" t="n">
         <v>3.45</v>
@@ -1545,10 +1545,10 @@
         <v>3.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
         <v>1.85</v>
@@ -1629,25 +1629,25 @@
         <v>24</v>
       </c>
       <c r="AL6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO6" t="n">
         <v>40</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS6" t="n">
         <v>48</v>
@@ -1662,7 +1662,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -1674,16 +1674,16 @@
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
         <v>19.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE6" t="n">
         <v>55</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -1727,40 +1727,40 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G7" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
@@ -1772,31 +1772,31 @@
         <v>1.96</v>
       </c>
       <c r="U7" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V7" t="n">
         <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="X7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1805,10 +1805,10 @@
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AX7" t="n">
         <v>3.95</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="AY7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE7" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BF7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BG7" t="n">
         <v>5.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="G10" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G11" t="n">
         <v>2.66</v>
@@ -2512,13 +2512,13 @@
         <v>3.25</v>
       </c>
       <c r="I11" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>3.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
         <v>5.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.1</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="H14" t="n">
-        <v>1.3</v>
+        <v>6.4</v>
       </c>
       <c r="I14" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 00:48:00</t>
+          <t>2026-03-30 02:53:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,91 +757,91 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83</v>
+        <v>1.93</v>
       </c>
       <c r="I2" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L2" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.92</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="P2" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="T2" t="n">
-        <v>2.06</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y2" t="n">
         <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
         <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE2" t="n">
         <v>6.8</v>
       </c>
-      <c r="AX2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AZ2" t="n">
+      <c r="BF2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BA2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8.4</v>
-      </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -951,52 +951,52 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
         <v>1.77</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
         <v>9.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="M3" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="N3" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="P3" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="S3" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="U3" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
@@ -1005,7 +1005,7 @@
         <v>2.28</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.52</v>
+        <v>3.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.74</v>
+        <v>3.05</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.6</v>
+        <v>2.26</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.02</v>
+        <v>4.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.84</v>
+        <v>1.72</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="BC3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BD3" t="n">
         <v>1.58</v>
       </c>
-      <c r="BD3" t="n">
-        <v>1.63</v>
-      </c>
       <c r="BE3" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G5" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H5" t="n">
         <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1372,7 +1372,7 @@
         <v>1.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
         <v>1.84</v>
@@ -1396,10 +1396,10 @@
         <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1417,7 +1417,7 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5" t="n">
         <v>11.5</v>
@@ -1435,13 +1435,13 @@
         <v>32</v>
       </c>
       <c r="AL5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1453,22 +1453,22 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>23</v>
+        <v>6.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV5" t="n">
         <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.2</v>
+        <v>48</v>
       </c>
       <c r="AX5" t="n">
         <v>9.6</v>
@@ -1486,23 +1486,23 @@
         <v>21</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
         <v>18</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
         <v>3.8</v>
@@ -1548,7 +1548,7 @@
         <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>2.06</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1590,7 +1590,7 @@
         <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
@@ -1608,7 +1608,7 @@
         <v>15.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF6" t="n">
         <v>15.5</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
         <v>40</v>
@@ -1647,7 +1647,7 @@
         <v>12.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AS6" t="n">
         <v>48</v>
@@ -1662,7 +1662,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AX6" t="n">
         <v>11</v>
@@ -1674,16 +1674,16 @@
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC6" t="n">
         <v>19.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
         <v>55</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="G7" t="n">
         <v>2.14</v>
@@ -1775,7 +1775,7 @@
         <v>1.9</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
         <v>1.89</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
         <v>2.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="H8" t="n">
         <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J8" t="n">
         <v>2.92</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G10" t="n">
         <v>2.02</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
         <v>2.58</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>1.73</v>
       </c>
       <c r="H14" t="n">
-        <v>6.4</v>
+        <v>1.31</v>
       </c>
       <c r="I14" t="n">
         <v>7.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>4.2</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 02:53:09</t>
+          <t>2026-03-30 04:58:23</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
         <v>5.4</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="J2" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="O2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.56</v>
+        <v>2.34</v>
       </c>
       <c r="R2" t="n">
         <v>1.19</v>
       </c>
       <c r="S2" t="n">
-        <v>5.3</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
         <v>2.18</v>
@@ -805,40 +805,40 @@
         <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
         <v>10.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="Z2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD2" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AE2" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH2" t="n">
         <v>30</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
         <v>5.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
         <v>5.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AY2" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE2" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -951,61 +951,61 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G3" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N3" t="n">
         <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="P3" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="R3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S3" t="n">
-        <v>6.8</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.8</v>
+        <v>1.99</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.75</v>
+        <v>1.98</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.26</v>
+        <v>2.04</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.9</v>
+        <v>2.12</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.7</v>
+        <v>2.24</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.72</v>
+        <v>2.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.69</v>
+        <v>2.42</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.7</v>
+        <v>2.48</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.58</v>
+        <v>1.99</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.43</v>
+        <v>2.02</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.69</v>
+        <v>2.48</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.44</v>
+        <v>2.02</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
         <v>3.55</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I5" t="n">
         <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
         <v>3.45</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
         <v>2.42</v>
@@ -1384,7 +1384,7 @@
         <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1393,19 +1393,19 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
@@ -1417,92 +1417,92 @@
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM5" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
       </c>
       <c r="AR5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AT5" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
         <v>6.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>48</v>
+        <v>5.3</v>
       </c>
       <c r="AX5" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY5" t="n">
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>19</v>
       </c>
-      <c r="BA5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>18</v>
-      </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1542,13 +1542,13 @@
         <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>3.55</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1587,116 +1587,116 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
         <v>16</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AB6" t="n">
         <v>11.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN6" t="n">
         <v>15.5</v>
       </c>
-      <c r="AE6" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>17</v>
-      </c>
       <c r="AO6" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP6" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>48</v>
+        <v>5.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
         <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>7.8</v>
+        <v>5.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>27</v>
+        <v>5.6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G7" t="n">
         <v>2.14</v>
       </c>
       <c r="H7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I7" t="n">
         <v>4.7</v>
@@ -1745,7 +1745,7 @@
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.09</v>
@@ -1760,7 +1760,7 @@
         <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
         <v>1.27</v>
@@ -1769,58 +1769,58 @@
         <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U7" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W7" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z7" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE7" t="n">
         <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1835,62 +1835,62 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS7" t="n">
         <v>5.7</v>
       </c>
-      <c r="AR7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AT7" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AU7" t="n">
         <v>6.8</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AY7" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.4</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -1921,19 +1921,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="G8" t="n">
-        <v>2.84</v>
+        <v>3.3</v>
       </c>
       <c r="H8" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="I8" t="n">
         <v>3.1</v>
       </c>
-      <c r="I8" t="n">
-        <v>3.45</v>
-      </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K8" t="n">
         <v>3.2</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2312,7 @@
         <v>1.87</v>
       </c>
       <c r="G10" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H10" t="n">
         <v>4.7</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q10" t="n">
         <v>2.36</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>2.16</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -2700,13 +2700,13 @@
         <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="H12" t="n">
         <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
@@ -2730,7 +2730,7 @@
         <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="G13" t="n">
         <v>2.16</v>
@@ -2906,7 +2906,7 @@
         <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 04:58:23</t>
+          <t>2026-03-30 07:03:50</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH15"/>
+  <dimension ref="A1:BH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.2</v>
+        <v>3.7</v>
       </c>
       <c r="G2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91</v>
+        <v>1.99</v>
       </c>
       <c r="I2" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
@@ -778,70 +778,70 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="R2" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>2.62</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
         <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="W2" t="n">
         <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -865,62 +865,62 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G3" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>1.89</v>
       </c>
       <c r="O3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P3" t="n">
-        <v>1.39</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.78</v>
+        <v>1.68</v>
       </c>
       <c r="R3" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="S3" t="n">
-        <v>3.45</v>
+        <v>2.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
         <v>1.11</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.98</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.42</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.36</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
@@ -1175,11 +1175,11 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1.93</v>
       </c>
-      <c r="Q4" t="n">
-        <v>1.76</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1339,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H5" t="n">
         <v>3.95</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q5" t="n">
         <v>2.42</v>
@@ -1396,7 +1396,7 @@
         <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="Z5" t="n">
         <v>34</v>
@@ -1405,7 +1405,7 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC5" t="n">
         <v>8.199999999999999</v>
@@ -1423,7 +1423,7 @@
         <v>13.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1435,13 +1435,13 @@
         <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1453,10 +1453,10 @@
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1486,23 +1486,23 @@
         <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BD5" t="n">
         <v>5.3</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BF5" t="n">
         <v>19</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -1519,42 +1519,42 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>AD Ceuta FC</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="G6" t="n">
-        <v>2.24</v>
+        <v>1.99</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>5.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>1.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1575,10 +1575,10 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -1587,123 +1587,123 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BE6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.02</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="I7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N7" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.72</v>
-      </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>1.84</v>
       </c>
       <c r="R7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>1.69</v>
       </c>
       <c r="U7" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
         <v>16</v>
       </c>
       <c r="Z7" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>14</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
+      <c r="AZ7" t="n">
         <v>14</v>
       </c>
-      <c r="AG7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>29</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BA7" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.7</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.86</v>
+        <v>2.02</v>
       </c>
       <c r="G8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J8" t="n">
         <v>3.3</v>
       </c>
-      <c r="H8" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.94</v>
-      </c>
       <c r="K8" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P8" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.48</v>
+        <v>1.88</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.02</v>
       </c>
       <c r="H11" t="n">
-        <v>3.25</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="J11" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="K11" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="G12" t="n">
-        <v>2.16</v>
+        <v>2.66</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="G13" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I13" t="n">
-        <v>6.2</v>
+        <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.8</v>
+        <v>2.24</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="G14" t="n">
-        <v>1.73</v>
+        <v>2.22</v>
       </c>
       <c r="H14" t="n">
-        <v>1.31</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.67</v>
+        <v>1.45</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.08</v>
+        <v>2.84</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,201 +3248,395 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 07:03:50</t>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>2026-03-30 09:10:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Sportivo Trinidense</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Olimpia</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q15" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>2026-03-30 07:03:50</t>
+      <c r="Q16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-30 09:10:27</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,82 +757,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.99</v>
+        <v>1.78</v>
       </c>
       <c r="I2" t="n">
-        <v>2.32</v>
+        <v>2.08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8</v>
+        <v>2.98</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="P2" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S2" t="n">
-        <v>2.62</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U2" t="n">
         <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -951,19 +951,19 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="J3" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
@@ -972,37 +972,37 @@
         <v>1.6</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N3" t="n">
-        <v>1.89</v>
+        <v>2.16</v>
       </c>
       <c r="O3" t="n">
         <v>1.68</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.68</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
         <v>1.12</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8</v>
+        <v>5.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="V3" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="AC3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H4" t="n">
         <v>3</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q4" t="n">
         <v>1.93</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H5" t="n">
         <v>3.95</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
         <v>2.42</v>
@@ -1396,7 +1396,7 @@
         <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z5" t="n">
         <v>34</v>
@@ -1408,10 +1408,10 @@
         <v>8.4</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
@@ -1420,16 +1420,16 @@
         <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
         <v>34</v>
@@ -1441,7 +1441,7 @@
         <v>180</v>
       </c>
       <c r="AN5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1456,7 +1456,7 @@
         <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1468,7 +1468,7 @@
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1477,32 +1477,32 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BA5" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB5" t="n">
         <v>5.4</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>5</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
         <v>19</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.87</v>
       </c>
       <c r="G6" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H6" t="n">
         <v>5.1</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q6" t="n">
         <v>2.5</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1733,10 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I7" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="Q7" t="n">
         <v>1.84</v>
@@ -1787,7 +1787,7 @@
         <v>16</v>
       </c>
       <c r="Z7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
         <v>80</v>
@@ -1823,28 +1823,28 @@
         <v>26</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT7" t="n">
         <v>9.4</v>
@@ -1856,7 +1856,7 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.2</v>
+        <v>34</v>
       </c>
       <c r="AX7" t="n">
         <v>12</v>
@@ -1868,29 +1868,29 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BC7" t="n">
         <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1963,7 +1963,7 @@
         <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U8" t="n">
         <v>1.92</v>
@@ -1987,10 +1987,10 @@
         <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
         <v>21</v>
@@ -2023,7 +2023,7 @@
         <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2032,13 +2032,13 @@
         <v>10</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2047,44 +2047,44 @@
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AX8" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>3.75</v>
       </c>
       <c r="AY8" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BA8" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB8" t="n">
         <v>4.8</v>
       </c>
-      <c r="BB8" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BC8" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="BD8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF8" t="n">
         <v>4.6</v>
       </c>
-      <c r="BE8" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG8" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>2.88</v>
       </c>
       <c r="G9" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
         <v>2.76</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="J9" t="n">
-        <v>2.86</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
         <v>3.25</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Q9" t="n">
         <v>2.56</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2506,13 +2506,13 @@
         <v>1.88</v>
       </c>
       <c r="G11" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H11" t="n">
         <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J11" t="n">
         <v>3.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G12" t="n">
         <v>2.66</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I12" t="n">
         <v>3.5</v>
@@ -2712,7 +2712,7 @@
         <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H13" t="n">
         <v>4.4</v>
@@ -2903,10 +2903,10 @@
         <v>5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
         <v>2.24</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3085,16 +3085,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.84</v>
+        <v>1.95</v>
       </c>
       <c r="G14" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J14" t="n">
         <v>3</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Q14" t="n">
         <v>2.84</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3282,16 +3282,16 @@
         <v>1.6</v>
       </c>
       <c r="G15" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="H15" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="I15" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
         <v>4.2</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q15" t="n">
         <v>2.08</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 09:10:27</t>
+          <t>2026-03-30 11:16:20</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H2" t="n">
         <v>1.78</v>
       </c>
       <c r="I2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
@@ -805,16 +805,16 @@
         <v>1.71</v>
       </c>
       <c r="V2" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="Z2" t="n">
         <v>11.5</v>
@@ -865,16 +865,16 @@
         <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="AT2" t="n">
         <v>5.3</v>
@@ -883,44 +883,44 @@
         <v>4.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
         <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
         <v>1.17</v>
@@ -990,22 +990,22 @@
         <v>1.12</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6</v>
+        <v>4.1</v>
       </c>
       <c r="T3" t="n">
         <v>2.72</v>
       </c>
       <c r="U3" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W3" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1071,25 +1071,25 @@
         <v>4.3</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.54</v>
+        <v>2.68</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AW3" t="n">
         <v>4.3</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BA3" t="n">
         <v>4.3</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1151,16 +1151,16 @@
         <v>2.52</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J4" t="n">
         <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="Q4" t="n">
         <v>1.93</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H5" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1381,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -1396,10 +1396,10 @@
         <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1420,7 +1420,7 @@
         <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH5" t="n">
         <v>25</v>
@@ -1447,7 +1447,7 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
@@ -1456,7 +1456,7 @@
         <v>21</v>
       </c>
       <c r="AS5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1468,7 +1468,7 @@
         <v>15.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
         <v>10.5</v>
@@ -1477,32 +1477,32 @@
         <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF5" t="n">
         <v>19</v>
       </c>
       <c r="BG5" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>2.2</v>
       </c>
       <c r="H7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I7" t="n">
         <v>3.9</v>
@@ -1817,10 +1817,10 @@
         <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AK7" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL7" t="n">
         <v>1000</v>
@@ -1841,10 +1841,10 @@
         <v>13</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT7" t="n">
         <v>9.4</v>
@@ -1868,7 +1868,7 @@
         <v>14</v>
       </c>
       <c r="BA7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB7" t="n">
         <v>6.6</v>
@@ -1877,20 +1877,20 @@
         <v>18.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF7" t="n">
         <v>11</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
         <v>2.14</v>
@@ -1939,7 +1939,7 @@
         <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M8" t="n">
         <v>1.09</v>
@@ -1969,7 +1969,7 @@
         <v>1.92</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
         <v>1.88</v>
@@ -2017,7 +2017,7 @@
         <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
         <v>160</v>
@@ -2035,10 +2035,10 @@
         <v>4.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2047,44 +2047,44 @@
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AY8" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BD8" t="n">
         <v>5.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="G9" t="n">
         <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I9" t="n">
         <v>2.98</v>
       </c>
       <c r="J9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>3.25</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
         <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="G14" t="n">
         <v>2.14</v>
@@ -3094,10 +3094,10 @@
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
         <v>3.3</v>
@@ -3118,7 +3118,7 @@
         <v>1.44</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G15" t="n">
         <v>1.73</v>
@@ -3294,7 +3294,7 @@
         <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q15" t="n">
         <v>2.08</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 11:16:20</t>
+          <t>2026-03-30 13:22:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH16"/>
+  <dimension ref="A1:BH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,82 +757,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="H2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="I2" t="n">
         <v>1.78</v>
       </c>
-      <c r="I2" t="n">
-        <v>2</v>
-      </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
       </c>
       <c r="M2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="O2" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q2" t="n">
         <v>2.36</v>
       </c>
       <c r="R2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>3.95</v>
       </c>
       <c r="T2" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U2" t="n">
-        <v>1.71</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>2.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AB2" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE2" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
@@ -841,7 +841,7 @@
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AQ2" t="n">
         <v>3.6</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AS2" t="n">
         <v>5.9</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BG2" t="n">
         <v>6</v>
       </c>
-      <c r="AX2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -975,28 +975,28 @@
         <v>1.17</v>
       </c>
       <c r="N3" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="P3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
         <v>1.12</v>
       </c>
       <c r="S3" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="U3" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
@@ -1059,69 +1059,69 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="AQ3" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AU3" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR3" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AV3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AX3" t="n">
         <v>3.4</v>
       </c>
       <c r="AY3" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA3" t="n">
         <v>3.7</v>
       </c>
-      <c r="AZ3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BB3" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Algerian Ligue 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Andorra CF</t>
+          <t>Kabylie</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>ES Ben Aknoun</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="G4" t="n">
-        <v>2.52</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>1.11</v>
       </c>
       <c r="I4" t="n">
-        <v>3.3</v>
+        <v>980</v>
       </c>
       <c r="J4" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6</v>
+        <v>1000</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>1.24</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,78 +1325,78 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>HIK Hellerup</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>Ishoj IF</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.16</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.22</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>4.1</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>1.84</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
         <v>1000</v>
@@ -1405,25 +1405,25 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1432,84 +1432,84 @@
         <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
         <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Danish 2nd Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Burgos</t>
+          <t>Fremad Amager</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AD Ceuta FC</t>
+          <t>Thisted</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1.97</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>5.1</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P6" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>1.3</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Andorra CF</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.84</v>
+        <v>1.93</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>48</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR7" t="n">
         <v>17</v>
       </c>
-      <c r="Y7" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB7" t="n">
+      <c r="AS7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV7" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP7" t="n">
+      <c r="AW7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW7" t="n">
+      <c r="BA7" t="n">
         <v>34</v>
       </c>
-      <c r="AX7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BB7" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
       <c r="BC7" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD7" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BE7" t="n">
-        <v>8</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Huesca</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P8" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
         <v>4.1</v>
       </c>
       <c r="T8" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
         <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>14</v>
-      </c>
       <c r="AG8" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
         <v>22</v>
       </c>
-      <c r="AO8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP8" t="n">
+      <c r="AS8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AY8" t="n">
         <v>10</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>4.8</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.9</v>
+        <v>24</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.9</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.3</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="BF8" t="n">
-        <v>4.7</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Burgos</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>AD Ceuta FC</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.86</v>
+        <v>1.87</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>1.96</v>
       </c>
       <c r="H9" t="n">
-        <v>2.78</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>2.98</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,42 +2295,42 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2351,10 +2351,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -2363,116 +2363,116 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W11" t="n">
         <v>1.88</v>
       </c>
-      <c r="G11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="H11" t="n">
+      <c r="X11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>14</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BF11" t="n">
         <v>4.7</v>
       </c>
-      <c r="I11" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,37 +2683,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.48</v>
+        <v>2.86</v>
       </c>
       <c r="G12" t="n">
-        <v>2.66</v>
+        <v>3.1</v>
       </c>
       <c r="H12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
         <v>3.25</v>
       </c>
-      <c r="I12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.34</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="G14" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="H14" t="n">
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.86</v>
+        <v>2.36</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="G15" t="n">
-        <v>1.73</v>
+        <v>2.66</v>
       </c>
       <c r="H15" t="n">
-        <v>6.4</v>
+        <v>3.25</v>
       </c>
       <c r="I15" t="n">
-        <v>8.6</v>
+        <v>3.5</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,201 +3442,783 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 13:22:09</t>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>19:00:00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Atletico GO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Nautico PE</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:28:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H17" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:28:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:28:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>Sportivo Trinidense</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>Olimpia</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>2026-03-30 13:22:09</t>
+      <c r="Q19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-30 15:28:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="G2" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>1.66</v>
       </c>
       <c r="I2" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="J2" t="n">
         <v>3.45</v>
       </c>
       <c r="K2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
         <v>1.44</v>
@@ -781,7 +781,7 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="O2" t="n">
         <v>1.47</v>
@@ -790,13 +790,13 @@
         <v>1.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R2" t="n">
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="T2" t="n">
         <v>2.24</v>
@@ -805,10 +805,10 @@
         <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X2" t="n">
         <v>11.5</v>
@@ -841,7 +841,7 @@
         <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -862,13 +862,13 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR2" t="n">
         <v>4.4</v>
@@ -880,10 +880,10 @@
         <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW2" t="n">
         <v>6.4</v>
@@ -901,26 +901,26 @@
         <v>7.6</v>
       </c>
       <c r="BB2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC2" t="n">
         <v>8.4</v>
       </c>
-      <c r="BC2" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BD2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG2" t="n">
         <v>6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
         <v>1.59</v>
@@ -975,16 +975,16 @@
         <v>1.17</v>
       </c>
       <c r="N3" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="O3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="P3" t="n">
         <v>1.36</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
         <v>1.12</v>
@@ -993,10 +993,10 @@
         <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.88</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="V3" t="n">
         <v>1.14</v>
@@ -1068,31 +1068,31 @@
         <v>3.6</v>
       </c>
       <c r="AS3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="AU3" t="n">
         <v>3.65</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="AW3" t="n">
         <v>3.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BB3" t="n">
         <v>3.25</v>
@@ -1107,14 +1107,14 @@
         <v>3.75</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG3" t="n">
         <v>3.75</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K5" t="n">
         <v>950</v>
@@ -1363,7 +1363,7 @@
         <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O5" t="n">
         <v>1.01</v>
@@ -1375,7 +1375,7 @@
         <v>1.35</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="S5" t="n">
         <v>1.36</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1533,19 +1533,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
         <v>950</v>
@@ -1566,7 +1566,7 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1730,7 @@
         <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.1</v>
@@ -1748,13 +1748,13 @@
         <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
         <v>1.93</v>
@@ -1763,16 +1763,16 @@
         <v>1.93</v>
       </c>
       <c r="R7" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="T7" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="V7" t="n">
         <v>1.44</v>
@@ -1781,116 +1781,116 @@
         <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>22</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX7" t="n">
         <v>14</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>17</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>44</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>13</v>
       </c>
       <c r="AY7" t="n">
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.7</v>
+        <v>13</v>
       </c>
       <c r="BF7" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>24</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
@@ -1939,16 +1939,16 @@
         <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O8" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
         <v>1.6</v>
@@ -1957,10 +1957,10 @@
         <v>2.42</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="T8" t="n">
         <v>2.04</v>
@@ -1969,7 +1969,7 @@
         <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.83</v>
@@ -1987,7 +1987,7 @@
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
@@ -1996,7 +1996,7 @@
         <v>19.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AF8" t="n">
         <v>13.5</v>
@@ -2008,7 +2008,7 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
         <v>28</v>
@@ -2023,7 +2023,7 @@
         <v>170</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>100</v>
@@ -2038,7 +2038,7 @@
         <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2050,7 +2050,7 @@
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2062,29 +2062,29 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BB8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BE8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2321,22 +2321,22 @@
         <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="K10" t="n">
         <v>3.9</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P10" t="n">
         <v>2.06</v>
@@ -2345,10 +2345,10 @@
         <v>1.84</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T10" t="n">
         <v>1.69</v>
@@ -2357,122 +2357,122 @@
         <v>2.22</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
         <v>16</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA10" t="n">
         <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
         <v>17.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ10" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>13</v>
-      </c>
       <c r="AR10" t="n">
-        <v>6.6</v>
+        <v>26</v>
       </c>
       <c r="AS10" t="n">
-        <v>55</v>
+        <v>10.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="BB10" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC10" t="n">
         <v>18.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
         <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
         <v>21</v>
@@ -2599,7 +2599,7 @@
         <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>160</v>
@@ -2614,13 +2614,13 @@
         <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -2629,10 +2629,10 @@
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX11" t="n">
         <v>9.6</v>
@@ -2641,32 +2641,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB11" t="n">
         <v>4.8</v>
       </c>
-      <c r="BA11" t="n">
+      <c r="BC11" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BE11" t="n">
         <v>5.6</v>
       </c>
-      <c r="BB11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BF11" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BG11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>2.78</v>
       </c>
       <c r="I12" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J12" t="n">
         <v>3</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="G15" t="n">
         <v>2.66</v>
       </c>
       <c r="H15" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I15" t="n">
         <v>3.5</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="G17" t="n">
         <v>2.14</v>
@@ -3676,7 +3676,7 @@
         <v>4.7</v>
       </c>
       <c r="I17" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J17" t="n">
         <v>3.1</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 15:28:18</t>
+          <t>2026-03-30 17:34:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH19"/>
+  <dimension ref="A1:BH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,7 +781,7 @@
         <v>1.1</v>
       </c>
       <c r="N2" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O2" t="n">
         <v>1.47</v>
@@ -796,7 +796,7 @@
         <v>1.21</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="T2" t="n">
         <v>2.24</v>
@@ -805,7 +805,7 @@
         <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W2" t="n">
         <v>1.14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.59</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.17</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -1253,13 +1253,13 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.4</v>
+        <v>1.47</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.4</v>
+        <v>1.16</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AS4" t="n">
         <v>1.2</v>
@@ -1268,19 +1268,19 @@
         <v>1.68</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.48</v>
+        <v>1.31</v>
       </c>
       <c r="AV4" t="n">
-        <v>22</v>
+        <v>2.26</v>
       </c>
       <c r="AW4" t="n">
         <v>1.68</v>
       </c>
       <c r="AX4" t="n">
-        <v>2.26</v>
+        <v>1.31</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AZ4" t="n">
         <v>2.26</v>
@@ -1289,13 +1289,13 @@
         <v>1.2</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="BE4" t="n">
         <v>1.2</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -1533,13 +1533,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="G6" t="n">
         <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -1945,13 +1945,13 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O8" t="n">
         <v>1.46</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
         <v>2.42</v>
@@ -1960,7 +1960,7 @@
         <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
         <v>2.04</v>
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
         <v>30</v>
@@ -2038,7 +2038,7 @@
         <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2050,7 +2050,7 @@
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2062,7 +2062,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB8" t="n">
         <v>23</v>
@@ -2071,20 +2071,20 @@
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -2115,13 +2115,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
         <v>6.2</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
         <v>2.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -2324,7 +2324,7 @@
         <v>3.7</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2333,7 +2333,7 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="O10" t="n">
         <v>1.27</v>
@@ -2357,7 +2357,7 @@
         <v>2.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
         <v>1.9</v>
@@ -2444,7 +2444,7 @@
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ10" t="n">
         <v>15.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2647,7 @@
         <v>5.4</v>
       </c>
       <c r="BB11" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC11" t="n">
         <v>4.8</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -2709,22 +2709,22 @@
         <v>2.96</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
         <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="P12" t="n">
         <v>1.56</v>
@@ -2733,134 +2733,134 @@
         <v>2.56</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -2909,16 +2909,16 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
         <v>1.24</v>
@@ -2927,134 +2927,134 @@
         <v>1.01</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="G14" t="n">
         <v>1.97</v>
@@ -3094,25 +3094,25 @@
         <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P14" t="n">
         <v>1.64</v>
@@ -3121,134 +3121,134 @@
         <v>2.36</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -3297,16 +3297,16 @@
         <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="P15" t="n">
         <v>1.65</v>
@@ -3315,134 +3315,134 @@
         <v>2.34</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G17" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U17" t="n">
         <v>1.98</v>
       </c>
-      <c r="G17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,378 +3847,1348 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.62</v>
+        <v>2.22</v>
       </c>
       <c r="G18" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="I18" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 17:34:08</t>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>CA Platense</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Athletico-PR</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Cruzeiro MG</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EC Vitoria Salvador</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H21" t="n">
+        <v>7</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>300</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>160</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>10</v>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Coritiba</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S22" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Santa Fe</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Llaneros FC</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:40:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Sportivo Trinidense</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Olimpia</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>2026-03-30 17:34:08</t>
+      <c r="Q24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>2026-03-30 19:40:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,91 +757,91 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="G2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="H2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="V2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X2" t="n">
-        <v>11.5</v>
-      </c>
       <c r="Y2" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="Z2" t="n">
         <v>9</v>
       </c>
       <c r="AA2" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AB2" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
         <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
@@ -862,65 +862,65 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>19.5</v>
+        <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>5</v>
+        <v>3.85</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW2" t="n">
         <v>5.8</v>
       </c>
-      <c r="AU2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AW2" t="n">
+      <c r="AX2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA2" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY2" t="n">
+      <c r="BB2" t="n">
         <v>6.8</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BC2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE2" t="n">
         <v>6.8</v>
       </c>
-      <c r="BA2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF2" t="n">
-        <v>8.6</v>
+        <v>6.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="G3" t="n">
-        <v>1.88</v>
+        <v>2.3</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="I3" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
         <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="N3" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="P3" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Q3" t="n">
         <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" t="n">
         <v>3.45</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="X3" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AV3" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="BB3" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.65</v>
+        <v>5.3</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
@@ -1211,7 +1211,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
         <v>1000</v>
@@ -1226,7 +1226,7 @@
         <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
         <v>1000</v>
@@ -1235,7 +1235,7 @@
         <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.26</v>
+        <v>1.05</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.31</v>
+        <v>1.04</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2.26</v>
+        <v>1.05</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.15</v>
+        <v>1.04</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.47</v>
+        <v>1.04</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.37</v>
+        <v>1.04</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.68</v>
+        <v>1.04</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1339,46 +1339,46 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.03</v>
+        <v>1.99</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="J5" t="n">
-        <v>1.09</v>
+        <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N5" t="n">
         <v>1.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.35</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S5" t="n">
-        <v>1.36</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1387,10 +1387,10 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.74</v>
       </c>
       <c r="H6" t="n">
-        <v>1.02</v>
+        <v>2.86</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>2.96</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="P6" t="n">
-        <v>1.25</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V6" t="n">
         <v>1.31</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G7" t="n">
         <v>2.5</v>
@@ -1736,13 +1736,13 @@
         <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1760,7 +1760,7 @@
         <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
@@ -1775,10 +1775,10 @@
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1814,10 +1814,10 @@
         <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -1829,7 +1829,7 @@
         <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>34</v>
@@ -1841,10 +1841,10 @@
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
@@ -1868,7 +1868,7 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
@@ -1883,14 +1883,14 @@
         <v>13</v>
       </c>
       <c r="BF7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
         <v>24</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
         <v>2.04</v>
@@ -1987,25 +1987,25 @@
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
         <v>90</v>
@@ -2014,7 +2014,7 @@
         <v>28</v>
       </c>
       <c r="AK8" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2035,10 +2035,10 @@
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
         <v>6.8</v>
@@ -2050,7 +2050,7 @@
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2062,7 +2062,7 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BB8" t="n">
         <v>23</v>
@@ -2071,20 +2071,20 @@
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>8.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BE8" t="n">
-        <v>9.4</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
         <v>20</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="H9" t="n">
         <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
         <v>3.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
         <v>2.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W10" t="n">
         <v>1.9</v>
@@ -2366,7 +2366,7 @@
         <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
         <v>30</v>
@@ -2381,13 +2381,13 @@
         <v>8.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
@@ -2411,13 +2411,13 @@
         <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO10" t="n">
         <v>44</v>
       </c>
       <c r="AP10" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
         <v>14.5</v>
@@ -2426,7 +2426,7 @@
         <v>26</v>
       </c>
       <c r="AS10" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
         <v>9.199999999999999</v>
@@ -2438,7 +2438,7 @@
         <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
@@ -2450,10 +2450,10 @@
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC10" t="n">
         <v>18.5</v>
@@ -2462,7 +2462,7 @@
         <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF10" t="n">
         <v>12</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2554,7 +2554,7 @@
         <v>1.29</v>
       </c>
       <c r="W11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X11" t="n">
         <v>13.5</v>
@@ -2572,7 +2572,7 @@
         <v>8.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD11" t="n">
         <v>21</v>
@@ -2599,13 +2599,13 @@
         <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
         <v>160</v>
       </c>
       <c r="AN11" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AR11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -2629,10 +2629,10 @@
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX11" t="n">
         <v>9.6</v>
@@ -2641,32 +2641,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BB11" t="n">
         <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2715,10 +2715,10 @@
         <v>3.25</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
         <v>2.66</v>
@@ -2739,7 +2739,7 @@
         <v>5.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="U12" t="n">
         <v>1.82</v>
@@ -2757,7 +2757,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA12" t="n">
         <v>55</v>
@@ -2784,16 +2784,16 @@
         <v>23</v>
       </c>
       <c r="AI12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK12" t="n">
         <v>44</v>
       </c>
       <c r="AL12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
@@ -2814,7 +2814,7 @@
         <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT12" t="n">
         <v>7.8</v>
@@ -2826,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -2838,29 +2838,29 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BB12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD12" t="n">
         <v>9.6</v>
       </c>
-      <c r="BC12" t="n">
+      <c r="BE12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BD12" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>36</v>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -2999,52 +2999,52 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS13" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AT13" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW13" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY13" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB13" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BC13" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BD13" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE13" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BF13" t="n">
         <v>1.01</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3103,16 +3103,16 @@
         <v>3.65</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>1.64</v>
+        <v>2.88</v>
       </c>
       <c r="O14" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="P14" t="n">
         <v>1.64</v>
@@ -3121,16 +3121,16 @@
         <v>2.36</v>
       </c>
       <c r="R14" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
         <v>1.24</v>
@@ -3139,116 +3139,116 @@
         <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AC14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>170</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ14" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>2.14</v>
-      </c>
       <c r="AR14" t="n">
-        <v>2.3</v>
+        <v>5.7</v>
       </c>
       <c r="AS14" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.94</v>
+        <v>6.2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.99</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.22</v>
+        <v>5.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="AX14" t="n">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY14" t="n">
-        <v>2.08</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.26</v>
+        <v>5.4</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>2.24</v>
+        <v>5.3</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.26</v>
+        <v>5.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>2.32</v>
+        <v>6</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.4</v>
+        <v>14</v>
       </c>
       <c r="BG14" t="n">
-        <v>2.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3297,16 +3297,16 @@
         <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>1.65</v>
+        <v>2.94</v>
       </c>
       <c r="O15" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="P15" t="n">
         <v>1.65</v>
@@ -3315,16 +3315,16 @@
         <v>2.34</v>
       </c>
       <c r="R15" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V15" t="n">
         <v>1.4</v>
@@ -3333,116 +3333,116 @@
         <v>1.6</v>
       </c>
       <c r="X15" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y15" t="n">
         <v>12.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA15" t="n">
         <v>75</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AF15" t="n">
         <v>18</v>
       </c>
-      <c r="AE15" t="n">
-        <v>55</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>19</v>
-      </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
         <v>75</v>
       </c>
       <c r="AJ15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK15" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL15" t="n">
         <v>65</v>
       </c>
       <c r="AM15" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN15" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.88</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>2.88</v>
+        <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="AT15" t="n">
-        <v>2.76</v>
+        <v>7.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>30</v>
+        <v>5.3</v>
       </c>
       <c r="AX15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AY15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.2</v>
+        <v>17.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>3.55</v>
+        <v>5.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>27</v>
+        <v>5.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>22</v>
+        <v>5.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>38</v>
+        <v>5.4</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.75</v>
+        <v>5.3</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3670,13 +3670,13 @@
         <v>2.22</v>
       </c>
       <c r="G17" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
@@ -3694,16 +3694,16 @@
         <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="S17" t="n">
         <v>4.1</v>
@@ -3712,25 +3712,25 @@
         <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="V17" t="n">
         <v>1.37</v>
       </c>
       <c r="W17" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X17" t="n">
         <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z17" t="n">
         <v>26</v>
       </c>
       <c r="AA17" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
         <v>9</v>
@@ -3754,7 +3754,7 @@
         <v>22</v>
       </c>
       <c r="AI17" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
         <v>32</v>
@@ -3763,7 +3763,7 @@
         <v>28</v>
       </c>
       <c r="AL17" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
         <v>150</v>
@@ -3784,7 +3784,7 @@
         <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
@@ -3796,7 +3796,7 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
         <v>11.5</v>
@@ -3808,7 +3808,7 @@
         <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
@@ -3817,20 +3817,20 @@
         <v>19</v>
       </c>
       <c r="BD17" t="n">
-        <v>36</v>
+        <v>7.6</v>
       </c>
       <c r="BE17" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -3870,10 +3870,10 @@
         <v>3.55</v>
       </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
         <v>3.5</v>
@@ -3882,149 +3882,149 @@
         <v>1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N18" t="n">
-        <v>1.61</v>
+        <v>3.15</v>
       </c>
       <c r="O18" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W18" t="n">
         <v>1.71</v>
       </c>
       <c r="X18" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG18" t="n">
         <v>12</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AH18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>10</v>
       </c>
-      <c r="AD18" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AR18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF18" t="n">
         <v>18</v>
       </c>
-      <c r="AS18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>2.78</v>
-      </c>
       <c r="BG18" t="n">
-        <v>2.78</v>
+        <v>7.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -4055,34 +4055,34 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H19" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I19" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
         <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="P19" t="n">
         <v>1.44</v>
@@ -4091,134 +4091,134 @@
         <v>2.86</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I20" t="n">
         <v>5.4</v>
@@ -4264,155 +4264,155 @@
         <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L20" t="n">
         <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O20" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P20" t="n">
         <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="R20" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S20" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U20" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="X20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>18.5</v>
       </c>
-      <c r="Y20" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="BA20" t="n">
-        <v>2.66</v>
+        <v>10.5</v>
       </c>
       <c r="BB20" t="n">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.5</v>
+        <v>18</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>2.72</v>
+        <v>11.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>2.7</v>
+        <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>2.7</v>
+        <v>11</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.57</v>
       </c>
       <c r="G21" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H21" t="n">
         <v>7</v>
@@ -4455,7 +4455,7 @@
         <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
@@ -4473,7 +4473,7 @@
         <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q21" t="n">
         <v>2.1</v>
@@ -4482,7 +4482,7 @@
         <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
         <v>2.12</v>
@@ -4494,19 +4494,19 @@
         <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y21" t="n">
         <v>21</v>
       </c>
       <c r="Z21" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AA21" t="n">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="AB21" t="n">
         <v>7</v>
@@ -4518,10 +4518,10 @@
         <v>29</v>
       </c>
       <c r="AE21" t="n">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="AF21" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
@@ -4530,61 +4530,61 @@
         <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>17.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AS21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="AT21" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AW21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX21" t="n">
         <v>7.6</v>
       </c>
       <c r="AY21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BB21" t="n">
         <v>13.5</v>
@@ -4593,20 +4593,20 @@
         <v>16.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BF21" t="n">
         <v>10</v>
       </c>
       <c r="BG21" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -4661,10 +4661,10 @@
         <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
         <v>1.7</v>
@@ -4685,25 +4685,25 @@
         <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W22" t="n">
         <v>1.56</v>
       </c>
       <c r="X22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y22" t="n">
         <v>12</v>
       </c>
       <c r="Z22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AC22" t="n">
         <v>9</v>
@@ -4715,13 +4715,13 @@
         <v>42</v>
       </c>
       <c r="AF22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AG22" t="n">
         <v>15</v>
       </c>
       <c r="AH22" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>60</v>
@@ -4730,19 +4730,19 @@
         <v>50</v>
       </c>
       <c r="AK22" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AL22" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AM22" t="n">
         <v>160</v>
       </c>
       <c r="AN22" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="AO22" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AP22" t="n">
         <v>9.6</v>
@@ -4751,10 +4751,10 @@
         <v>8.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT22" t="n">
         <v>7.8</v>
@@ -4766,7 +4766,7 @@
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="AX22" t="n">
         <v>14</v>
@@ -4778,29 +4778,29 @@
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF22" t="n">
         <v>24</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -4843,158 +4843,158 @@
         <v>8.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
         <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P23" t="n">
         <v>1.69</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>
@@ -5043,152 +5043,152 @@
         <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P24" t="n">
         <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-30 19:40:07</t>
+          <t>2026-03-30 21:45:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.7</v>
+        <v>4.1</v>
       </c>
       <c r="G2" t="n">
-        <v>7.8</v>
+        <v>5.3</v>
       </c>
       <c r="H2" t="n">
-        <v>1.73</v>
+        <v>1.95</v>
       </c>
       <c r="I2" t="n">
-        <v>1.92</v>
+        <v>2.22</v>
       </c>
       <c r="J2" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="P2" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T2" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.52</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
-        <v>2.08</v>
+        <v>1.82</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="X2" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>210</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>430</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>350</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>550</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>340</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="Y2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>32</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AZ2" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>5.6</v>
+        <v>15.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -951,25 +951,25 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="H3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.16</v>
@@ -996,13 +996,13 @@
         <v>2.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,13 +1059,13 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
         <v>5.4</v>
@@ -1074,47 +1074,47 @@
         <v>3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="AY3" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AZ3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BC3" t="n">
         <v>4.8</v>
       </c>
-      <c r="BA3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB3" t="n">
+      <c r="BD3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF3" t="n">
         <v>4.8</v>
       </c>
-      <c r="BC3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD3" t="n">
+      <c r="BG3" t="n">
         <v>5.3</v>
       </c>
-      <c r="BE3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1357,16 +1357,16 @@
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M5" t="n">
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>2.78</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="P5" t="n">
         <v>1.68</v>
@@ -1375,16 +1375,16 @@
         <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S5" t="n">
         <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V5" t="n">
         <v>1.29</v>
@@ -1405,10 +1405,10 @@
         <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1641,7 +1641,7 @@
         <v>48</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ6" t="n">
         <v>3.35</v>
@@ -1659,7 +1659,7 @@
         <v>2.96</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AW6" t="n">
         <v>3.9</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.48</v>
-      </c>
-      <c r="G7" t="n">
-        <v>2.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.1</v>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
@@ -1751,7 +1751,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.32</v>
@@ -1775,10 +1775,10 @@
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1817,7 +1817,7 @@
         <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>1.97</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
         <v>5.2</v>
@@ -3100,7 +3100,7 @@
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L14" t="n">
         <v>1.01</v>
@@ -3187,7 +3187,7 @@
         <v>230</v>
       </c>
       <c r="AN14" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AO14" t="n">
         <v>170</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G15" t="n">
         <v>2.66</v>
@@ -3318,13 +3318,13 @@
         <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T15" t="n">
         <v>1.93</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V15" t="n">
         <v>1.4</v>
@@ -3342,10 +3342,10 @@
         <v>25</v>
       </c>
       <c r="AA15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB15" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
         <v>8.4</v>
@@ -3366,10 +3366,10 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ15" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AK15" t="n">
         <v>36</v>
@@ -3396,7 +3396,7 @@
         <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -3408,7 +3408,7 @@
         <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX15" t="n">
         <v>13</v>
@@ -3420,29 +3420,29 @@
         <v>17.5</v>
       </c>
       <c r="BA15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC15" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BD15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF15" t="n">
         <v>5.4</v>
       </c>
-      <c r="BE15" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>5</v>
-      </c>
       <c r="BG15" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G17" t="n">
         <v>2.34</v>
@@ -3706,7 +3706,7 @@
         <v>1.26</v>
       </c>
       <c r="S17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T17" t="n">
         <v>1.9</v>
@@ -3724,7 +3724,7 @@
         <v>14</v>
       </c>
       <c r="Y17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z17" t="n">
         <v>26</v>
@@ -3784,7 +3784,7 @@
         <v>21</v>
       </c>
       <c r="AS17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
@@ -3796,7 +3796,7 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AX17" t="n">
         <v>11.5</v>
@@ -3808,7 +3808,7 @@
         <v>17.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB17" t="n">
         <v>21</v>
@@ -3817,20 +3817,20 @@
         <v>19</v>
       </c>
       <c r="BD17" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
         <v>17.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
         <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="V18" t="n">
         <v>1.33</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G19" t="n">
         <v>2.18</v>
@@ -4100,7 +4100,7 @@
         <v>2.34</v>
       </c>
       <c r="U19" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="V19" t="n">
         <v>1.22</v>
@@ -4142,7 +4142,7 @@
         <v>36</v>
       </c>
       <c r="AI19" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ19" t="n">
         <v>34</v>
@@ -4154,13 +4154,13 @@
         <v>80</v>
       </c>
       <c r="AM19" t="n">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AN19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO19" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP19" t="n">
         <v>6.8</v>
@@ -4169,7 +4169,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS19" t="n">
         <v>6</v>
@@ -4184,7 +4184,7 @@
         <v>18.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX19" t="n">
         <v>9.199999999999999</v>
@@ -4199,16 +4199,16 @@
         <v>6</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BC19" t="n">
         <v>5.4</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF19" t="n">
         <v>5.4</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
         <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
@@ -4282,7 +4282,7 @@
         <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.97</v>
+        <v>2.06</v>
       </c>
       <c r="R20" t="n">
         <v>1.31</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G21" t="n">
         <v>1.63</v>
@@ -4461,7 +4461,7 @@
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -4834,13 +4834,13 @@
         <v>1.62</v>
       </c>
       <c r="G23" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="H23" t="n">
         <v>6.4</v>
       </c>
       <c r="I23" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J23" t="n">
         <v>3.65</v>
@@ -4864,7 +4864,7 @@
         <v>1.69</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
@@ -4876,13 +4876,13 @@
         <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="V23" t="n">
         <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X23" t="n">
         <v>11.5</v>
@@ -4945,7 +4945,7 @@
         <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS23" t="n">
         <v>6.2</v>
@@ -4960,7 +4960,7 @@
         <v>5.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX23" t="n">
         <v>7.8</v>
@@ -4972,7 +4972,7 @@
         <v>5.3</v>
       </c>
       <c r="BA23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB23" t="n">
         <v>14.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-30 21:45:59</t>
+          <t>2026-03-30 23:51:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH24"/>
+  <dimension ref="A1:BH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="I2" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="J2" t="n">
-        <v>2.96</v>
+        <v>2.74</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,16 +781,16 @@
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
         <v>1.15</v>
@@ -805,13 +805,13 @@
         <v>1.59</v>
       </c>
       <c r="V2" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="W2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y2" t="n">
         <v>5.9</v>
@@ -820,13 +820,13 @@
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="AB2" t="n">
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
@@ -835,10 +835,10 @@
         <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="AH2" t="n">
         <v>36</v>
@@ -847,80 +847,80 @@
         <v>210</v>
       </c>
       <c r="AJ2" t="n">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="AK2" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AL2" t="n">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN2" t="n">
-        <v>340</v>
+        <v>990</v>
       </c>
       <c r="AO2" t="n">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="AP2" t="n">
         <v>4.9</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AR2" t="n">
         <v>7.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
         <v>9.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AV2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW2" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA2" t="n">
+      <c r="BD2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE2" t="n">
         <v>11</v>
       </c>
-      <c r="BB2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>12</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -951,40 +951,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G3" t="n">
-        <v>2.24</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="I3" t="n">
         <v>6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="O3" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="P3" t="n">
         <v>1.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="R3" t="n">
         <v>1.13</v>
@@ -993,16 +993,16 @@
         <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="V3" t="n">
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.15</v>
+        <v>4.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>2.72</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.4</v>
+        <v>2.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.4</v>
+        <v>2.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.4</v>
+        <v>2.62</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.2</v>
+        <v>2.84</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.85</v>
+        <v>2.28</v>
       </c>
       <c r="AY3" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>4.7</v>
+        <v>2.68</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.2</v>
+        <v>2.26</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.7</v>
+        <v>2.64</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.1</v>
+        <v>2.82</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>2.26</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.3</v>
+        <v>2.26</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="I5" t="n">
         <v>4.4</v>
@@ -1354,7 +1354,7 @@
         <v>2.9</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.36</v>
@@ -1363,16 +1363,16 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="O5" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P5" t="n">
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1381,16 +1381,16 @@
         <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V5" t="n">
         <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1548,10 +1548,10 @@
         <v>2.96</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1560,25 +1560,25 @@
         <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q6" t="n">
         <v>1.89</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.78</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V6" t="n">
         <v>1.31</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.1</v>
@@ -1778,7 +1778,7 @@
         <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1817,7 +1817,7 @@
         <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -1939,13 +1939,13 @@
         <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="O8" t="n">
         <v>1.46</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
         <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
         <v>1.27</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3076,179 +3076,179 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I14" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J14" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="G16" t="n">
-        <v>2.16</v>
+        <v>1.97</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
         <v>3.35</v>
       </c>
       <c r="I17" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J17" t="n">
         <v>3.5</v>
@@ -3694,7 +3694,7 @@
         <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
         <v>1.75</v>
@@ -3703,7 +3703,7 @@
         <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S17" t="n">
         <v>4.2</v>
@@ -3781,7 +3781,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS17" t="n">
         <v>8.199999999999999</v>
@@ -3790,7 +3790,7 @@
         <v>7.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV17" t="n">
         <v>12.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -3900,7 +3900,7 @@
         <v>1.26</v>
       </c>
       <c r="S18" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T18" t="n">
         <v>1.89</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G19" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="H19" t="n">
         <v>4.5</v>
@@ -4106,7 +4106,7 @@
         <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="X19" t="n">
         <v>9</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="G20" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="H20" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.58</v>
       </c>
       <c r="G21" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H21" t="n">
         <v>7</v>
@@ -4494,7 +4494,7 @@
         <v>1.14</v>
       </c>
       <c r="W21" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="X21" t="n">
         <v>14</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
         <v>1.1</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1.62</v>
       </c>
       <c r="G23" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="H23" t="n">
         <v>6.4</v>
@@ -4882,7 +4882,7 @@
         <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="X23" t="n">
         <v>11.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,977 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-30 23:51:26</t>
+          <t>2026-03-31 01:58:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>21:00:00</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ponte Preta</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Ceara SC Fortaleza</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>2026-03-31 01:58:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Brazilian Serie A</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fluminense</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>140</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-03-31 01:58:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-03-31 01:58:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="W28" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-03-31 01:58:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11</v>
+      </c>
+      <c r="I29" t="n">
+        <v>17</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>29</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>370</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-31 01:58:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.92</v>
       </c>
       <c r="I2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
@@ -784,13 +784,13 @@
         <v>2.16</v>
       </c>
       <c r="O2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="P2" t="n">
         <v>1.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R2" t="n">
         <v>1.15</v>
@@ -805,7 +805,7 @@
         <v>1.59</v>
       </c>
       <c r="V2" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="W2" t="n">
         <v>1.22</v>
@@ -820,13 +820,13 @@
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AB2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>12</v>
@@ -835,10 +835,10 @@
         <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AG2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AH2" t="n">
         <v>36</v>
@@ -847,80 +847,80 @@
         <v>210</v>
       </c>
       <c r="AJ2" t="n">
-        <v>410</v>
+        <v>190</v>
       </c>
       <c r="AK2" t="n">
         <v>340</v>
       </c>
       <c r="AL2" t="n">
-        <v>530</v>
+        <v>210</v>
       </c>
       <c r="AM2" t="n">
         <v>360</v>
       </c>
       <c r="AN2" t="n">
-        <v>990</v>
+        <v>310</v>
       </c>
       <c r="AO2" t="n">
         <v>150</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AQ2" t="n">
         <v>5.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
         <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AV2" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.8</v>
+        <v>18.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="BA2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB2" t="n">
         <v>10</v>
       </c>
-      <c r="BB2" t="n">
-        <v>11</v>
-      </c>
       <c r="BC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE2" t="n">
         <v>10.5</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BF2" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>11</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>11</v>
       </c>
       <c r="BG2" t="n">
         <v>16.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="H3" t="n">
         <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="O3" t="n">
         <v>1.71</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q3" t="n">
         <v>2.74</v>
@@ -1002,7 +1002,7 @@
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1065,34 +1065,34 @@
         <v>2.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="AT3" t="n">
         <v>4.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="AY3" t="n">
         <v>2.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BB3" t="n">
         <v>2.64</v>
@@ -1101,20 +1101,20 @@
         <v>2.7</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.82</v>
+        <v>2.26</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BF3" t="n">
         <v>2.7</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K5" t="n">
         <v>3.85</v>
@@ -1363,7 +1363,7 @@
         <v>1.07</v>
       </c>
       <c r="N5" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="O5" t="n">
         <v>1.33</v>
@@ -1372,7 +1372,7 @@
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
         <v>1.3</v>
@@ -1390,7 +1390,7 @@
         <v>1.29</v>
       </c>
       <c r="W5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,52 +1447,52 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AS5" t="n">
         <v>4.1</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AW5" t="n">
         <v>4</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BA5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD5" t="n">
         <v>4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BE5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF5" t="n">
         <v>3.65</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.89</v>
+        <v>1.78</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1730,22 +1730,22 @@
         <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I7" t="n">
         <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1757,28 +1757,28 @@
         <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
         <v>2.16</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1817,7 +1817,7 @@
         <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -1841,7 +1841,7 @@
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS7" t="n">
         <v>12</v>
@@ -1877,7 +1877,7 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
         <v>13</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -1930,7 +1930,7 @@
         <v>4.1</v>
       </c>
       <c r="I8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -1945,31 +1945,31 @@
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
         <v>1.83</v>
@@ -2008,7 +2008,7 @@
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>28</v>
@@ -2020,13 +2020,13 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AN8" t="n">
         <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP8" t="n">
         <v>8.800000000000001</v>
@@ -2041,7 +2041,7 @@
         <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
         <v>6.6</v>
@@ -2077,14 +2077,14 @@
         <v>13.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
         <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
         <v>5.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
         <v>3.85</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
@@ -2342,7 +2342,7 @@
         <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R10" t="n">
         <v>1.41</v>
@@ -2438,22 +2438,22 @@
         <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AX10" t="n">
         <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BC10" t="n">
         <v>18.5</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>2.14</v>
       </c>
       <c r="H11" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
@@ -2536,16 +2536,16 @@
         <v>1.72</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R11" t="n">
         <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
         <v>1.92</v>
@@ -2569,7 +2569,7 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC11" t="n">
         <v>8.199999999999999</v>
@@ -2581,7 +2581,7 @@
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
@@ -2593,16 +2593,16 @@
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
         <v>28</v>
       </c>
       <c r="AL11" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
@@ -2614,13 +2614,13 @@
         <v>10</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -2629,10 +2629,10 @@
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AX11" t="n">
         <v>9.6</v>
@@ -2641,32 +2641,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BB11" t="n">
         <v>6.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
         <v>3.1</v>
       </c>
       <c r="H12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I12" t="n">
         <v>2.96</v>
@@ -2721,13 +2721,13 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O12" t="n">
         <v>1.53</v>
       </c>
       <c r="P12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q12" t="n">
         <v>2.56</v>
@@ -2769,10 +2769,10 @@
         <v>7.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
         <v>18.5</v>
@@ -2799,7 +2799,7 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO12" t="n">
         <v>60</v>
@@ -2814,7 +2814,7 @@
         <v>13.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
         <v>7.8</v>
@@ -2826,7 +2826,7 @@
         <v>12</v>
       </c>
       <c r="AW12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX12" t="n">
         <v>16</v>
@@ -2838,29 +2838,29 @@
         <v>19.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB12" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BD12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BC12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BE12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF12" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>3.2</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J15" t="n">
         <v>3.05</v>
@@ -3312,10 +3312,10 @@
         <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
         <v>4.4</v>
@@ -3327,7 +3327,7 @@
         <v>1.92</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
         <v>1.6</v>
@@ -3354,7 +3354,7 @@
         <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF15" t="n">
         <v>18</v>
@@ -3366,7 +3366,7 @@
         <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
         <v>42</v>
@@ -3375,7 +3375,7 @@
         <v>36</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM15" t="n">
         <v>160</v>
@@ -3396,7 +3396,7 @@
         <v>18.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
         <v>7.4</v>
@@ -3423,26 +3423,26 @@
         <v>5.9</v>
       </c>
       <c r="BB15" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC15" t="n">
         <v>5.6</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>5.4</v>
       </c>
       <c r="BD15" t="n">
         <v>5.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>1.96</v>
       </c>
       <c r="G16" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H16" t="n">
         <v>4.8</v>
@@ -3491,7 +3491,7 @@
         <v>3.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
@@ -3518,7 +3518,7 @@
         <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V16" t="n">
         <v>1.24</v>
@@ -3530,13 +3530,13 @@
         <v>13</v>
       </c>
       <c r="Y16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z16" t="n">
         <v>38</v>
       </c>
       <c r="AA16" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB16" t="n">
         <v>7</v>
@@ -3545,10 +3545,10 @@
         <v>970</v>
       </c>
       <c r="AD16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF16" t="n">
         <v>970</v>
@@ -3572,13 +3572,13 @@
         <v>65</v>
       </c>
       <c r="AM16" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN16" t="n">
         <v>970</v>
       </c>
       <c r="AO16" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP16" t="n">
         <v>9.199999999999999</v>
@@ -3587,10 +3587,10 @@
         <v>11.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT16" t="n">
         <v>6.2</v>
@@ -3599,10 +3599,10 @@
         <v>7.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX16" t="n">
         <v>9.199999999999999</v>
@@ -3611,32 +3611,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ16" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC16" t="n">
         <v>5.4</v>
       </c>
-      <c r="BA16" t="n">
+      <c r="BD16" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB16" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>6</v>
-      </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF16" t="n">
         <v>14</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3667,25 +3667,25 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G17" t="n">
         <v>2.34</v>
       </c>
       <c r="H17" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K17" t="n">
         <v>3.65</v>
       </c>
-      <c r="J17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K17" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M17" t="n">
         <v>1.08</v>
@@ -3694,7 +3694,7 @@
         <v>3.15</v>
       </c>
       <c r="O17" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P17" t="n">
         <v>1.75</v>
@@ -3703,7 +3703,7 @@
         <v>2.18</v>
       </c>
       <c r="R17" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S17" t="n">
         <v>4.2</v>
@@ -3712,10 +3712,10 @@
         <v>1.9</v>
       </c>
       <c r="U17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V17" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W17" t="n">
         <v>1.74</v>
@@ -3784,7 +3784,7 @@
         <v>20</v>
       </c>
       <c r="AS17" t="n">
-        <v>8.199999999999999</v>
+        <v>50</v>
       </c>
       <c r="AT17" t="n">
         <v>7.4</v>
@@ -3796,7 +3796,7 @@
         <v>12.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>7.8</v>
+        <v>34</v>
       </c>
       <c r="AX17" t="n">
         <v>11.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>3.55</v>
       </c>
       <c r="I18" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="J18" t="n">
         <v>3.2</v>
@@ -3879,7 +3879,7 @@
         <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M18" t="n">
         <v>1.09</v>
@@ -3891,13 +3891,13 @@
         <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q18" t="n">
         <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -3906,10 +3906,10 @@
         <v>1.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="V18" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W18" t="n">
         <v>1.71</v>
@@ -3963,7 +3963,7 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
@@ -4002,7 +4002,7 @@
         <v>6</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB18" t="n">
         <v>6.8</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.99</v>
       </c>
       <c r="G19" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H19" t="n">
         <v>4.5</v>
@@ -4106,7 +4106,7 @@
         <v>1.22</v>
       </c>
       <c r="W19" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X19" t="n">
         <v>9</v>
@@ -4145,7 +4145,7 @@
         <v>160</v>
       </c>
       <c r="AJ19" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK19" t="n">
         <v>40</v>
@@ -4169,10 +4169,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT19" t="n">
         <v>5.5</v>
@@ -4184,7 +4184,7 @@
         <v>18.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX19" t="n">
         <v>9.199999999999999</v>
@@ -4193,32 +4193,32 @@
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BB19" t="n">
         <v>5.3</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BG19" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="G20" t="n">
         <v>1.85</v>
@@ -4267,7 +4267,7 @@
         <v>3.95</v>
       </c>
       <c r="L20" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
@@ -4282,19 +4282,19 @@
         <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="R20" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="T20" t="n">
         <v>1.92</v>
       </c>
       <c r="U20" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
         <v>1.23</v>
@@ -4315,13 +4315,13 @@
         <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="AC20" t="n">
         <v>8.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE20" t="n">
         <v>1000</v>
@@ -4354,7 +4354,7 @@
         <v>14.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP20" t="n">
         <v>11.5</v>
@@ -4363,10 +4363,10 @@
         <v>14</v>
       </c>
       <c r="AR20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS20" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>11.5</v>
       </c>
       <c r="AT20" t="n">
         <v>7</v>
@@ -4378,7 +4378,7 @@
         <v>17.5</v>
       </c>
       <c r="AW20" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AX20" t="n">
         <v>9.6</v>
@@ -4387,10 +4387,10 @@
         <v>9</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA20" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="BB20" t="n">
         <v>18</v>
@@ -4399,20 +4399,20 @@
         <v>18</v>
       </c>
       <c r="BD20" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE20" t="n">
         <v>9.6</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>11.5</v>
       </c>
       <c r="BF20" t="n">
         <v>10.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -4455,13 +4455,13 @@
         <v>8</v>
       </c>
       <c r="J21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K21" t="n">
         <v>4.3</v>
       </c>
       <c r="L21" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
@@ -4476,7 +4476,7 @@
         <v>1.77</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
         <v>1.29</v>
@@ -4497,7 +4497,7 @@
         <v>2.66</v>
       </c>
       <c r="X21" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
         <v>21</v>
@@ -4515,10 +4515,10 @@
         <v>9.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE21" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AF21" t="n">
         <v>8.6</v>
@@ -4530,37 +4530,37 @@
         <v>27</v>
       </c>
       <c r="AI21" t="n">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AJ21" t="n">
         <v>15</v>
       </c>
       <c r="AK21" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL21" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AM21" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AO21" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
         <v>17.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT21" t="n">
         <v>6.2</v>
@@ -4569,10 +4569,10 @@
         <v>8.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>7.6</v>
@@ -4584,7 +4584,7 @@
         <v>23</v>
       </c>
       <c r="BA21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB21" t="n">
         <v>13.5</v>
@@ -4593,7 +4593,7 @@
         <v>16.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
         <v>12.5</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -4685,13 +4685,13 @@
         <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W22" t="n">
         <v>1.56</v>
       </c>
       <c r="X22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y22" t="n">
         <v>12</v>
@@ -4700,13 +4700,13 @@
         <v>24</v>
       </c>
       <c r="AA22" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB22" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AD22" t="n">
         <v>16</v>
@@ -4715,7 +4715,7 @@
         <v>42</v>
       </c>
       <c r="AF22" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG22" t="n">
         <v>15</v>
@@ -4730,7 +4730,7 @@
         <v>50</v>
       </c>
       <c r="AK22" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="n">
         <v>65</v>
@@ -4754,7 +4754,7 @@
         <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AT22" t="n">
         <v>7.8</v>
@@ -4766,7 +4766,7 @@
         <v>11</v>
       </c>
       <c r="AW22" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AX22" t="n">
         <v>14</v>
@@ -4778,29 +4778,29 @@
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>24</v>
+        <v>5.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -4849,7 +4849,7 @@
         <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -4909,7 +4909,7 @@
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG23" t="n">
         <v>10.5</v>
@@ -4927,7 +4927,7 @@
         <v>21</v>
       </c>
       <c r="AL23" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4945,10 +4945,10 @@
         <v>16</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AS23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT23" t="n">
         <v>5.8</v>
@@ -4957,10 +4957,10 @@
         <v>7.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX23" t="n">
         <v>7.8</v>
@@ -4969,7 +4969,7 @@
         <v>9</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BA23" t="n">
         <v>6.2</v>
@@ -4981,20 +4981,20 @@
         <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF23" t="n">
         <v>10.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
         <v>3.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M25" t="n">
         <v>1.11</v>
@@ -5249,7 +5249,7 @@
         <v>1.51</v>
       </c>
       <c r="P25" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q25" t="n">
         <v>2.48</v>
@@ -5288,7 +5288,7 @@
         <v>12</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD25" t="n">
         <v>12</v>
@@ -5324,10 +5324,10 @@
         <v>110</v>
       </c>
       <c r="AO25" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ25" t="n">
         <v>6.2</v>
@@ -5351,7 +5351,7 @@
         <v>7</v>
       </c>
       <c r="AX25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY25" t="n">
         <v>15</v>
@@ -5360,29 +5360,29 @@
         <v>19.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB25" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD25" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BC25" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>8</v>
-      </c>
       <c r="BE25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF25" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>8.199999999999999</v>
       </c>
       <c r="BG25" t="n">
         <v>21</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
@@ -5431,7 +5431,7 @@
         <v>3.55</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
@@ -5440,16 +5440,16 @@
         <v>2.82</v>
       </c>
       <c r="O26" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
         <v>1.62</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R26" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S26" t="n">
         <v>4.8</v>
@@ -5458,7 +5458,7 @@
         <v>2.14</v>
       </c>
       <c r="U26" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
         <v>1.24</v>
@@ -5473,10 +5473,10 @@
         <v>15.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA26" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB26" t="n">
         <v>7.8</v>
@@ -5509,10 +5509,10 @@
         <v>30</v>
       </c>
       <c r="AL26" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN26" t="n">
         <v>25</v>
@@ -5521,16 +5521,16 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
         <v>11.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT26" t="n">
         <v>6</v>
@@ -5539,10 +5539,10 @@
         <v>7</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX26" t="n">
         <v>9.6</v>
@@ -5554,29 +5554,29 @@
         <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC26" t="n">
         <v>19</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF26" t="n">
         <v>16.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G27" t="n">
         <v>1.91</v>
       </c>
       <c r="H27" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I27" t="n">
         <v>5.5</v>
@@ -5625,7 +5625,7 @@
         <v>3.95</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M27" t="n">
         <v>1.08</v>
@@ -5670,7 +5670,7 @@
         <v>40</v>
       </c>
       <c r="AA27" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB27" t="n">
         <v>8</v>
@@ -5700,7 +5700,7 @@
         <v>21</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>42</v>
@@ -5709,7 +5709,7 @@
         <v>150</v>
       </c>
       <c r="AN27" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
@@ -5718,13 +5718,13 @@
         <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AT27" t="n">
         <v>7</v>
@@ -5733,10 +5733,10 @@
         <v>7.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>7.6</v>
+        <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX27" t="n">
         <v>9.4</v>
@@ -5745,32 +5745,32 @@
         <v>9</v>
       </c>
       <c r="AZ27" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="BA27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE27" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>11</v>
       </c>
       <c r="BF27" t="n">
         <v>10.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G28" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="H28" t="n">
         <v>5.8</v>
       </c>
       <c r="I28" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
         <v>3.5</v>
@@ -5819,152 +5819,152 @@
         <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.63</v>
+        <v>2.92</v>
       </c>
       <c r="O28" t="n">
-        <v>1.02</v>
+        <v>1.45</v>
       </c>
       <c r="P28" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.45</v>
+        <v>2.28</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="U28" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="V28" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="W28" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X28" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y28" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK28" t="n">
         <v>23</v>
       </c>
-      <c r="Z28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AL28" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF28" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BG28" t="n">
-        <v>2.58</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6004,7 @@
         <v>11</v>
       </c>
       <c r="I29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
         <v>6</v>
@@ -6013,7 +6013,7 @@
         <v>7.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M29" t="n">
         <v>1.03</v>
@@ -6022,19 +6022,19 @@
         <v>5.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="R29" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="S29" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="T29" t="n">
         <v>2.1</v>
@@ -6049,7 +6049,7 @@
         <v>4.2</v>
       </c>
       <c r="X29" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Y29" t="n">
         <v>48</v>
@@ -6097,22 +6097,22 @@
         <v>210</v>
       </c>
       <c r="AN29" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AO29" t="n">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AP29" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AQ29" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AT29" t="n">
         <v>8.6</v>
@@ -6121,10 +6121,10 @@
         <v>13</v>
       </c>
       <c r="AV29" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX29" t="n">
         <v>7.2</v>
@@ -6133,10 +6133,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB29" t="n">
         <v>8.800000000000001</v>
@@ -6145,20 +6145,20 @@
         <v>12</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 01:58:00</t>
+          <t>2026-03-31 04:04:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH29"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,22 +769,22 @@
         <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="P2" t="n">
         <v>1.44</v>
@@ -796,13 +796,13 @@
         <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>3.45</v>
+        <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="U2" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
         <v>1.9</v>
@@ -814,13 +814,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
         <v>12</v>
@@ -835,7 +835,7 @@
         <v>65</v>
       </c>
       <c r="AF2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
         <v>24</v>
@@ -856,7 +856,7 @@
         <v>210</v>
       </c>
       <c r="AM2" t="n">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="AN2" t="n">
         <v>310</v>
@@ -865,62 +865,62 @@
         <v>150</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="AS2" t="n">
         <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX2" t="n">
         <v>8.199999999999999</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8.4</v>
       </c>
       <c r="AY2" t="n">
         <v>18.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BA2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC2" t="n">
         <v>9.6</v>
       </c>
-      <c r="BB2" t="n">
+      <c r="BD2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE2" t="n">
         <v>10</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BF2" t="n">
         <v>10</v>
       </c>
-      <c r="BD2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG2" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="H3" t="n">
         <v>4.7</v>
@@ -963,10 +963,10 @@
         <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.58</v>
@@ -1002,7 +1002,7 @@
         <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.02</v>
+        <v>1.02</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="U5" t="n">
-        <v>2</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
+      <c r="AY5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW5" t="n">
+      <c r="BA5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF5" t="n">
         <v>4</v>
       </c>
-      <c r="AX5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE5" t="n">
+      <c r="BG5" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF5" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4</v>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="G6" t="n">
-        <v>2.74</v>
+        <v>2.36</v>
       </c>
       <c r="H6" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
         <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O6" t="n">
         <v>1.39</v>
       </c>
-      <c r="M6" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="P6" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.78</v>
+        <v>2.08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="T6" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="X6" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="Y6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AE6" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF6" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
         <v>32</v>
       </c>
       <c r="AL6" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.45</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.35</v>
+        <v>9.4</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.7</v>
+        <v>19</v>
       </c>
       <c r="AS6" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.96</v>
+        <v>5.8</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.45</v>
+        <v>11.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.45</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.25</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.55</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>3.85</v>
+        <v>21</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.75</v>
+        <v>18.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1745,7 +1745,7 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1754,22 +1754,22 @@
         <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>1.29</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
         <v>2.16</v>
@@ -1784,7 +1784,7 @@
         <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -1793,7 +1793,7 @@
         <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -1829,22 +1829,22 @@
         <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.5</v>
+        <v>8.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
@@ -1853,10 +1853,10 @@
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>6.8</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1868,29 +1868,29 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>30</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BF7" t="n">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="BG7" t="n">
-        <v>24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
@@ -1942,28 +1942,28 @@
         <v>1.45</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O8" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P8" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
         <v>1.87</v>
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z8" t="n">
         <v>30</v>
@@ -1987,25 +1987,25 @@
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
         <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
@@ -2023,22 +2023,22 @@
         <v>160</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
         <v>90</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>3.25</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2047,10 +2047,10 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>3.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>3.25</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2059,32 +2059,32 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.5</v>
+        <v>3.25</v>
       </c>
       <c r="BB8" t="n">
-        <v>23</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>12</v>
+        <v>3.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>13.5</v>
+        <v>2.34</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
-        <v>12.5</v>
+        <v>3.25</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="K9" t="n">
         <v>3.4</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -2309,25 +2309,25 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M10" t="n">
         <v>1.06</v>
@@ -2336,49 +2336,49 @@
         <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P10" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S10" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
         <v>1.31</v>
       </c>
       <c r="W10" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
         <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
         <v>16.5</v>
@@ -2387,16 +2387,16 @@
         <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ10" t="n">
         <v>25</v>
@@ -2408,78 +2408,78 @@
         <v>34</v>
       </c>
       <c r="AM10" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO10" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ10" t="n">
         <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>26</v>
+        <v>4.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.5</v>
+        <v>3.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>4</v>
       </c>
       <c r="AW10" t="n">
-        <v>10.5</v>
+        <v>4.7</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>3.75</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>3.55</v>
       </c>
       <c r="AZ10" t="n">
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.5</v>
+        <v>3.3</v>
       </c>
       <c r="BB10" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="BC10" t="n">
-        <v>18.5</v>
+        <v>8.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="BE10" t="n">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,78 +2489,78 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.04</v>
       </c>
       <c r="G11" t="n">
-        <v>2.14</v>
+        <v>1000</v>
       </c>
       <c r="H11" t="n">
-        <v>4.1</v>
+        <v>1.04</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>1.02</v>
       </c>
       <c r="K11" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>1.08</v>
       </c>
       <c r="O11" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.72</v>
+        <v>1.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.18</v>
+        <v>1.49</v>
       </c>
       <c r="R11" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="S11" t="n">
-        <v>3.9</v>
+        <v>1.49</v>
       </c>
       <c r="T11" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W11" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,25 +2569,25 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2596,13 +2596,13 @@
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
@@ -2611,69 +2611,69 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.86</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>3.1</v>
+        <v>2.14</v>
       </c>
       <c r="H12" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>2.96</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>2.68</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>1.72</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1</v>
+        <v>3.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="U12" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="V12" t="n">
-        <v>1.51</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.47</v>
+        <v>1.89</v>
       </c>
       <c r="X12" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="Z12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD12" t="n">
         <v>21</v>
       </c>
-      <c r="AA12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>14</v>
-      </c>
       <c r="AE12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="AL12" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>7.6</v>
+        <v>4.9</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW12" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8.6</v>
-      </c>
       <c r="AX12" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="AY12" t="n">
-        <v>12</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.199999999999999</v>
+        <v>6.4</v>
       </c>
       <c r="BB12" t="n">
-        <v>9</v>
+        <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="BD12" t="n">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>10</v>
+        <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>9</v>
+        <v>5.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>9</v>
+        <v>6.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P13" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,184 +3071,184 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P14" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -3270,179 +3270,179 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K15" t="n">
         <v>3.45</v>
       </c>
-      <c r="J15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="R15" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BE15" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.96</v>
+        <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>1.98</v>
+        <v>2.66</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>5.2</v>
+        <v>3.45</v>
       </c>
       <c r="J16" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
         <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="O16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="U16" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="V16" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="W16" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="X16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.26</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="H17" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="J17" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N17" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="O17" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.18</v>
+        <v>2.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="W17" t="n">
-        <v>1.74</v>
+        <v>2.02</v>
       </c>
       <c r="X17" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>170</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>100</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>160</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF17" t="n">
         <v>14</v>
       </c>
-      <c r="Y17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>26</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>28</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>60</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>17.5</v>
-      </c>
       <c r="BG17" t="n">
-        <v>8</v>
+        <v>6.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -3852,37 +3852,37 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="G18" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I18" t="n">
         <v>3.55</v>
       </c>
-      <c r="I18" t="n">
-        <v>3.9</v>
-      </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
         <v>1.47</v>
       </c>
       <c r="M18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N18" t="n">
         <v>3.15</v>
@@ -3891,106 +3891,106 @@
         <v>1.39</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
         <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V18" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA18" t="n">
         <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC18" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG18" t="n">
         <v>12</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI18" t="n">
         <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
         <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ18" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>10</v>
-      </c>
       <c r="AR18" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="AX18" t="n">
         <v>11.5</v>
@@ -3999,39 +3999,39 @@
         <v>9.6</v>
       </c>
       <c r="AZ18" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB18" t="n">
-        <v>6.8</v>
+        <v>21</v>
       </c>
       <c r="BC18" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BD18" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BG18" t="n">
         <v>8</v>
       </c>
-      <c r="BF18" t="n">
-        <v>18</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F19" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S19" t="n">
+        <v>4</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U19" t="n">
         <v>1.99</v>
       </c>
-      <c r="G19" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H19" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="I19" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="N19" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S19" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.61</v>
-      </c>
       <c r="V19" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="W19" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="X19" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN19" t="n">
         <v>27</v>
       </c>
-      <c r="AE19" t="n">
-        <v>130</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>38</v>
-      </c>
       <c r="AO19" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR19" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AU19" t="n">
         <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BC19" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BD19" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
-        <v>5.6</v>
+        <v>18</v>
       </c>
       <c r="BG19" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.82</v>
+        <v>1.99</v>
       </c>
       <c r="G20" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="I20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X20" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>130</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>330</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>230</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB20" t="n">
         <v>5.3</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="X20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>18</v>
-      </c>
       <c r="BC20" t="n">
-        <v>18</v>
+        <v>5.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>8.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="BE20" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG20" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="G21" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="H21" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="J21" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="L21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="M21" t="n">
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P21" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="T21" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="V21" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="W21" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="X21" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Z21" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AA21" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="AE21" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AG21" t="n">
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AK21" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV21" t="n">
         <v>17.5</v>
       </c>
-      <c r="AR21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>25</v>
-      </c>
       <c r="AW21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AX21" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY21" t="n">
         <v>9</v>
       </c>
       <c r="AZ21" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BB21" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BC21" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD21" t="n">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE21" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="G22" t="n">
-        <v>2.78</v>
+        <v>1.6</v>
       </c>
       <c r="H22" t="n">
-        <v>2.92</v>
+        <v>7</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>8</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="L22" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P22" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.9</v>
+        <v>2.12</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="V22" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="W22" t="n">
-        <v>1.56</v>
+        <v>2.66</v>
       </c>
       <c r="X22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB22" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y22" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK22" t="n">
+      <c r="BC22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD22" t="n">
         <v>36</v>
       </c>
-      <c r="AL22" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE22" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF22" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BG22" t="n">
-        <v>5.1</v>
+        <v>12.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,49 +4822,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.62</v>
+        <v>2.58</v>
       </c>
       <c r="G23" t="n">
-        <v>1.68</v>
+        <v>2.78</v>
       </c>
       <c r="H23" t="n">
-        <v>6.4</v>
+        <v>2.92</v>
       </c>
       <c r="I23" t="n">
-        <v>8.4</v>
+        <v>3.15</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M23" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
         <v>1.42</v>
       </c>
       <c r="P23" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="R23" t="n">
         <v>1.25</v>
@@ -4873,135 +4873,135 @@
         <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>2.16</v>
+        <v>1.9</v>
       </c>
       <c r="U23" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="V23" t="n">
-        <v>1.13</v>
+        <v>1.46</v>
       </c>
       <c r="W23" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="X23" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y23" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH23" t="n">
         <v>21</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AI23" t="n">
         <v>60</v>
       </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC23" t="n">
+      <c r="AJ23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV23" t="n">
+      <c r="AZ23" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BE23" t="n">
         <v>5.5</v>
       </c>
-      <c r="AW23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BF23" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BG23" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,55 +5016,55 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M24" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P24" t="n">
         <v>1.25</v>
       </c>
-      <c r="O24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Q24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5073,129 +5073,129 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="X24" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG24" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK24" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM24" t="n">
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO24" t="n">
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT24" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="P25" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="R25" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>4.8</v>
+        <v>1.36</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>2.14</v>
       </c>
       <c r="I26" t="n">
-        <v>5.2</v>
+        <v>2.34</v>
       </c>
       <c r="J26" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K26" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L26" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="M26" t="n">
         <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="O26" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P26" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="R26" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S26" t="n">
         <v>4.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U26" t="n">
         <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="W26" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y26" t="n">
-        <v>15.5</v>
+        <v>7.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>42</v>
+        <v>13.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>130</v>
+        <v>32</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.8</v>
+        <v>12</v>
       </c>
       <c r="AC26" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH26" t="n">
         <v>24</v>
       </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>28</v>
-      </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="AK26" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO26" t="n">
         <v>30</v>
       </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP26" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AT26" t="n">
-        <v>6</v>
+        <v>9.6</v>
       </c>
       <c r="AU26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW26" t="n">
         <v>7</v>
       </c>
-      <c r="AV26" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>5.1</v>
-      </c>
       <c r="AX26" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="AY26" t="n">
-        <v>9.6</v>
+        <v>15</v>
       </c>
       <c r="AZ26" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>5.2</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF26" t="n">
-        <v>16.5</v>
+        <v>8.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.8</v>
       </c>
-      <c r="G27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="H27" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="I27" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K27" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.92</v>
-      </c>
       <c r="V27" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W27" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="X27" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="Y27" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>19</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF27" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z27" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG27" t="n">
-        <v>10</v>
+        <v>5.2</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
@@ -5792,373 +5792,567 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="G28" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="H28" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K28" t="n">
         <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N28" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="O28" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.65</v>
+        <v>1.81</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.28</v>
+        <v>2.04</v>
       </c>
       <c r="R28" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.16</v>
+        <v>1.92</v>
       </c>
       <c r="U28" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="V28" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="W28" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Y28" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>21</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV28" t="n">
         <v>17</v>
       </c>
-      <c r="Z28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AC28" t="n">
+      <c r="AW28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BD28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AD28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BE28" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 04:04:26</t>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="H29" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S29" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X29" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>250</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:11:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Atletico Nacional Medellin</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Cucuta Deportivo</t>
         </is>
       </c>
-      <c r="F29" t="n">
+      <c r="F30" t="n">
         <v>1.25</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G30" t="n">
         <v>1.31</v>
       </c>
-      <c r="H29" t="n">
-        <v>11</v>
-      </c>
-      <c r="I29" t="n">
+      <c r="H30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I30" t="n">
         <v>16</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>6</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K30" t="n">
         <v>7.4</v>
       </c>
-      <c r="L29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="L30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M30" t="n">
         <v>1.03</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N30" t="n">
         <v>5.7</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O30" t="n">
         <v>1.17</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P30" t="n">
         <v>2.64</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q30" t="n">
         <v>1.51</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>1.67</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>2.28</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>2.1</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>1.77</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V30" t="n">
         <v>1.06</v>
       </c>
-      <c r="W29" t="n">
+      <c r="W30" t="n">
         <v>4.2</v>
       </c>
-      <c r="X29" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>360</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>9</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>13</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BH29" t="inlineStr">
-        <is>
-          <t>2026-03-31 04:04:26</t>
+      <c r="X30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-31 06:11:07</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,13 +763,13 @@
         <v>5.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I2" t="n">
         <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
         <v>3.5</v>
@@ -784,13 +784,13 @@
         <v>2.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="R2" t="n">
         <v>1.15</v>
@@ -799,10 +799,10 @@
         <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.9</v>
@@ -811,13 +811,13 @@
         <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
         <v>6.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA2" t="n">
         <v>26</v>
@@ -826,52 +826,52 @@
         <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AH2" t="n">
         <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
         <v>190</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AL2" t="n">
+        <v>280</v>
+      </c>
+      <c r="AM2" t="n">
         <v>340</v>
       </c>
-      <c r="AL2" t="n">
-        <v>210</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>350</v>
-      </c>
       <c r="AN2" t="n">
-        <v>310</v>
+        <v>440</v>
       </c>
       <c r="AO2" t="n">
-        <v>150</v>
+        <v>42</v>
       </c>
       <c r="AP2" t="n">
         <v>4.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS2" t="n">
         <v>16.5</v>
@@ -886,41 +886,41 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AY2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BA2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BE2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
         <v>18</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
         <v>4.7</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
         <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="N3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="O3" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="P3" t="n">
         <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="R3" t="n">
         <v>1.13</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>3.45</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.9</v>
+        <v>3.25</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.74</v>
+        <v>2.58</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.3</v>
+        <v>2.72</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.24</v>
+        <v>3.5</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.64</v>
+        <v>2.48</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="AX3" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.26</v>
+        <v>2.62</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.7</v>
+        <v>2.52</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.02</v>
+        <v>2.12</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="n">
-        <v>1.02</v>
+        <v>2.4</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>2.72</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="L5" t="n">
         <v>1.3</v>
@@ -1363,34 +1363,34 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="U5" t="n">
         <v>2.24</v>
       </c>
       <c r="V5" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1408,7 +1408,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
         <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV5" t="n">
         <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.5</v>
+        <v>5.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="G6" t="n">
-        <v>2.36</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I6" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N6" t="n">
         <v>3.55</v>
       </c>
-      <c r="I6" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N6" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O6" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.8</v>
+        <v>3.35</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="W6" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="X6" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
         <v>15</v>
       </c>
-      <c r="Z6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>17</v>
-      </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>23</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AK6" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AR6" t="n">
-        <v>19</v>
+        <v>3.85</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AT6" t="n">
         <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BB6" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BC6" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="BF6" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.15</v>
@@ -1745,7 +1745,7 @@
         <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1754,37 +1754,37 @@
         <v>3.9</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P7" t="n">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.29</v>
+        <v>1.94</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>1.29</v>
+        <v>3.4</v>
       </c>
       <c r="T7" t="n">
         <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -1793,7 +1793,7 @@
         <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
         <v>8</v>
@@ -1817,7 +1817,7 @@
         <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
@@ -1829,34 +1829,34 @@
         <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.4</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1868,29 +1868,29 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.800000000000001</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>9.800000000000001</v>
+        <v>26</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -1945,16 +1945,16 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O8" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
@@ -1966,7 +1966,7 @@
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
         <v>1.29</v>
@@ -1978,34 +1978,34 @@
         <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
         <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
@@ -2020,25 +2020,25 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>90</v>
       </c>
       <c r="AP8" t="n">
-        <v>3.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.1</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.3</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2047,10 +2047,10 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>3.8</v>
+        <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.25</v>
+        <v>13</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2059,32 +2059,32 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.6</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>3.25</v>
+        <v>12.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.199999999999999</v>
+        <v>23</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.199999999999999</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.2</v>
+        <v>12</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.34</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.25</v>
+        <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>2.86</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
         <v>3.4</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="G10" t="n">
         <v>2.06</v>
       </c>
       <c r="H10" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
         <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L10" t="n">
         <v>1.32</v>
@@ -2342,7 +2342,7 @@
         <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R10" t="n">
         <v>1.43</v>
@@ -2351,10 +2351,10 @@
         <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V10" t="n">
         <v>1.31</v>
@@ -2363,22 +2363,22 @@
         <v>1.94</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA10" t="n">
         <v>80</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD10" t="n">
         <v>16.5</v>
@@ -2387,19 +2387,19 @@
         <v>46</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>17</v>
       </c>
       <c r="AI10" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
         <v>21</v>
@@ -2423,10 +2423,10 @@
         <v>14.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.4</v>
+        <v>27</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT10" t="n">
         <v>9.6</v>
@@ -2435,44 +2435,44 @@
         <v>7.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>4</v>
+        <v>14.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.75</v>
+        <v>12</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.55</v>
+        <v>9.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>15.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.3</v>
+        <v>10.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.4</v>
+        <v>18</v>
       </c>
       <c r="BD10" t="n">
-        <v>4.5</v>
+        <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.7</v>
+        <v>30</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2527,22 +2527,22 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.01</v>
       </c>
       <c r="P11" t="n">
-        <v>1.08</v>
+        <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T11" t="n">
         <v>1.01</v>
@@ -2611,52 +2611,52 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G12" t="n">
         <v>2.14</v>
@@ -2721,7 +2721,7 @@
         <v>1.09</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.4</v>
@@ -2736,7 +2736,7 @@
         <v>1.27</v>
       </c>
       <c r="S12" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T12" t="n">
         <v>1.92</v>
@@ -2751,31 +2751,31 @@
         <v>1.89</v>
       </c>
       <c r="X12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF12" t="n">
         <v>13.5</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13</v>
       </c>
       <c r="AG12" t="n">
         <v>12.5</v>
@@ -2787,19 +2787,19 @@
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK12" t="n">
         <v>28</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM12" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
@@ -2808,13 +2808,13 @@
         <v>10</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4.9</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT12" t="n">
         <v>7</v>
@@ -2823,28 +2823,28 @@
         <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>5.3</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX12" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY12" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB12" t="n">
         <v>6.4</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD12" t="n">
         <v>6.2</v>
@@ -2853,21 +2853,21 @@
         <v>6.8</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG12" t="n">
         <v>6.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Boyaca Patriotas</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>3.1</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1.02</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>950</v>
       </c>
       <c r="L13" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.55</v>
+        <v>1.08</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.58</v>
+        <v>1.08</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="S13" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Y13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AQ13" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV13" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX13" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AY13" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ13" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA13" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BB13" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BC13" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="BD13" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE13" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BF13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG13" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="O14" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="R14" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,184 +3265,184 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P15" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3464,179 +3464,179 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.48</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66</v>
+        <v>2.18</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="n">
         <v>3.45</v>
       </c>
-      <c r="J16" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K16" t="n">
-        <v>3.3</v>
-      </c>
       <c r="L16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>1.98</v>
       </c>
       <c r="H17" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="I17" t="n">
         <v>5.2</v>
@@ -3682,7 +3682,7 @@
         <v>3.4</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.42</v>
@@ -3712,7 +3712,7 @@
         <v>2.1</v>
       </c>
       <c r="U17" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V17" t="n">
         <v>1.24</v>
@@ -3721,31 +3721,31 @@
         <v>2.02</v>
       </c>
       <c r="X17" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>180</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF17" t="n">
         <v>13</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>38</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>970</v>
       </c>
       <c r="AG17" t="n">
         <v>13</v>
@@ -3760,19 +3760,19 @@
         <v>27</v>
       </c>
       <c r="AK17" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL17" t="n">
         <v>65</v>
       </c>
       <c r="AM17" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="AN17" t="n">
-        <v>970</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP17" t="n">
         <v>9.199999999999999</v>
@@ -3781,10 +3781,10 @@
         <v>11.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="AT17" t="n">
         <v>6.2</v>
@@ -3793,10 +3793,10 @@
         <v>7.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
       <c r="AW17" t="n">
-        <v>6.4</v>
+        <v>4.4</v>
       </c>
       <c r="AX17" t="n">
         <v>9.199999999999999</v>
@@ -3805,39 +3805,39 @@
         <v>9.4</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.4</v>
+        <v>4</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BF17" t="n">
         <v>14</v>
       </c>
       <c r="BG17" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,87 +3847,87 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.28</v>
+        <v>2.48</v>
       </c>
       <c r="G18" t="n">
-        <v>2.34</v>
+        <v>2.66</v>
       </c>
       <c r="H18" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="I18" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L18" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
         <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
         <v>8.4</v>
@@ -3936,95 +3936,95 @@
         <v>15.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AK18" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>50</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="AX18" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>8.199999999999999</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>21</v>
+        <v>4.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>19</v>
+        <v>4.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>9</v>
+        <v>5.3</v>
       </c>
       <c r="BF18" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G19" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H19" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
         <v>1.47</v>
@@ -4079,13 +4079,13 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O19" t="n">
         <v>1.39</v>
       </c>
       <c r="P19" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
         <v>2.18</v>
@@ -4097,28 +4097,28 @@
         <v>4</v>
       </c>
       <c r="T19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="V19" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W19" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X19" t="n">
         <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB19" t="n">
         <v>9.199999999999999</v>
@@ -4127,105 +4127,105 @@
         <v>8</v>
       </c>
       <c r="AD19" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR19" t="n">
         <v>21</v>
       </c>
-      <c r="AI19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AS19" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
         <v>13</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="AX19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AY19" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>8</v>
-      </c>
       <c r="BF19" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BG19" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.99</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>2.12</v>
+        <v>2.38</v>
       </c>
       <c r="H20" t="n">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="I20" t="n">
-        <v>5.4</v>
+        <v>3.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="M20" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="N20" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="P20" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>2.34</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>1.61</v>
+        <v>1.98</v>
       </c>
       <c r="V20" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="W20" t="n">
-        <v>1.89</v>
+        <v>1.72</v>
       </c>
       <c r="X20" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
         <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>11.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
         <v>28</v>
       </c>
-      <c r="AK20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>38</v>
-      </c>
       <c r="AO20" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>6.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AU20" t="n">
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>18.5</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BC20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD20" t="n">
         <v>5.6</v>
       </c>
-      <c r="BD20" t="n">
-        <v>6</v>
-      </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG20" t="n">
         <v>5.6</v>
       </c>
-      <c r="BG20" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,179 +4434,179 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="G21" t="n">
-        <v>1.85</v>
+        <v>2.12</v>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I21" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="L21" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="M21" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>1.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.04</v>
+        <v>2.92</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="S21" t="n">
-        <v>3.65</v>
+        <v>6.4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>2.44</v>
       </c>
       <c r="U21" t="n">
-        <v>1.98</v>
+        <v>1.63</v>
       </c>
       <c r="V21" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W21" t="n">
-        <v>2.14</v>
+        <v>1.89</v>
       </c>
       <c r="X21" t="n">
-        <v>13.5</v>
+        <v>7.8</v>
       </c>
       <c r="Y21" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR21" t="n">
         <v>20</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AS21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY21" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AZ21" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC21" t="n">
         <v>21</v>
       </c>
-      <c r="AI21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>18</v>
-      </c>
       <c r="BD21" t="n">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>9.6</v>
+        <v>95</v>
       </c>
       <c r="BF21" t="n">
-        <v>10.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="G22" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="H22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="J22" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K22" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="L22" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
       </c>
       <c r="N22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="T22" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="W22" t="n">
-        <v>2.66</v>
+        <v>2.14</v>
       </c>
       <c r="X22" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG22" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y22" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>290</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AH22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT22" t="n">
         <v>7</v>
       </c>
-      <c r="AC22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="AU22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV22" t="n">
         <v>17.5</v>
       </c>
-      <c r="AR22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>25</v>
-      </c>
       <c r="AW22" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="AX22" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AY22" t="n">
         <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="BA22" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="BB22" t="n">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BC22" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>4.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>12.5</v>
+        <v>4.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>12.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -4817,191 +4817,191 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="G23" t="n">
-        <v>2.78</v>
+        <v>1.63</v>
       </c>
       <c r="H23" t="n">
-        <v>2.92</v>
+        <v>7</v>
       </c>
       <c r="I23" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="R23" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="U23" t="n">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="W23" t="n">
-        <v>1.56</v>
+        <v>2.6</v>
       </c>
       <c r="X23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>290</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB23" t="n">
         <v>13.5</v>
       </c>
-      <c r="Y23" t="n">
-        <v>12</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BC23" t="n">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.5</v>
+        <v>48</v>
       </c>
       <c r="BF23" t="n">
-        <v>5.1</v>
+        <v>10</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.1</v>
+        <v>46</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.62</v>
+        <v>2.58</v>
       </c>
       <c r="G24" t="n">
-        <v>1.68</v>
+        <v>2.78</v>
       </c>
       <c r="H24" t="n">
-        <v>6.4</v>
+        <v>2.94</v>
       </c>
       <c r="I24" t="n">
-        <v>8.4</v>
+        <v>3.15</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S24" t="n">
         <v>4.1</v>
       </c>
-      <c r="L24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S24" t="n">
-        <v>1.37</v>
-      </c>
       <c r="T24" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="W24" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="X24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB24" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AC24" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF24" t="n">
         <v>21</v>
       </c>
-      <c r="Z24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>10</v>
-      </c>
       <c r="AG24" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AI24" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ24" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AL24" t="n">
         <v>55</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN24" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX24" t="n">
         <v>14</v>
       </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>5.5</v>
+        <v>17</v>
       </c>
       <c r="BA24" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>18</v>
+        <v>4.1</v>
       </c>
       <c r="BD24" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>10.5</v>
+        <v>4.1</v>
       </c>
       <c r="BG24" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>1.36</v>
+        <v>3.9</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="P26" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.48</v>
+        <v>1.36</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>4.8</v>
+        <v>1.36</v>
       </c>
       <c r="T26" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.91</v>
+        <v>3.9</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="I27" t="n">
-        <v>5.2</v>
+        <v>2.32</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K27" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M27" t="n">
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>2.74</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="P27" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R27" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
         <v>4.8</v>
       </c>
       <c r="T27" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="U27" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="V27" t="n">
-        <v>1.24</v>
+        <v>1.76</v>
       </c>
       <c r="W27" t="n">
-        <v>2</v>
+        <v>1.28</v>
       </c>
       <c r="X27" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y27" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="Z27" t="n">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="AB27" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC27" t="n">
         <v>7.8</v>
       </c>
-      <c r="AC27" t="n">
-        <v>9</v>
-      </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>13.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF27" t="n">
-        <v>12.5</v>
+        <v>32</v>
       </c>
       <c r="AG27" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AH27" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ27" t="n">
-        <v>28</v>
+        <v>120</v>
       </c>
       <c r="AK27" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AO27" t="n">
         <v>30</v>
       </c>
-      <c r="AL27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP27" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="AS27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX27" t="n">
         <v>5.2</v>
       </c>
-      <c r="AT27" t="n">
+      <c r="AY27" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BE27" t="n">
         <v>6</v>
       </c>
-      <c r="AU27" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BF27" t="n">
-        <v>16.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="G28" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="H28" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="I28" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>3.35</v>
+        <v>2.92</v>
       </c>
       <c r="O28" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="P28" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="R28" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="U28" t="n">
-        <v>1.92</v>
+        <v>1.71</v>
       </c>
       <c r="V28" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="W28" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="X28" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z28" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="AA28" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="AB28" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AE28" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="AF28" t="n">
         <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AH28" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ28" t="n">
         <v>22</v>
       </c>
-      <c r="AI28" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>21</v>
-      </c>
       <c r="AK28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AL28" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="AM28" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="AN28" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AQ28" t="n">
         <v>13.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AS28" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT28" t="n">
-        <v>7</v>
+        <v>5.7</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AW28" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AX28" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17.5</v>
+        <v>4.4</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.4</v>
+        <v>15.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BE28" t="n">
-        <v>10.5</v>
+        <v>5.1</v>
       </c>
       <c r="BF28" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG28" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,373 +5986,567 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G29" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="H29" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>7</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="L29" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P29" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="R29" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T29" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="U29" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="W29" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="X29" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Y29" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>250</v>
+        <v>140</v>
       </c>
       <c r="AB29" t="n">
         <v>6.8</v>
       </c>
       <c r="AC29" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AD29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AG29" t="n">
         <v>11</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ29" t="n">
         <v>19</v>
       </c>
-      <c r="AK29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BA29" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="BB29" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD29" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BF29" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG29" t="n">
         <v>11.5</v>
       </c>
-      <c r="BG29" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 06:11:07</t>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:18:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>Atletico Nacional Medellin</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Cucuta Deportivo</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G30" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="H30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="I30" t="n">
-        <v>16</v>
-      </c>
-      <c r="J30" t="n">
-        <v>6</v>
-      </c>
-      <c r="K30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="F31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="H31" t="n">
+        <v>13</v>
+      </c>
+      <c r="I31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N31" t="n">
         <v>5.7</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O31" t="n">
         <v>1.17</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S30" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V30" t="n">
+      <c r="P31" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V31" t="n">
         <v>1.06</v>
       </c>
-      <c r="W30" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH30" t="inlineStr">
-        <is>
-          <t>2026-03-31 06:11:07</t>
+      <c r="W31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>34</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>60</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>360</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>32</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-31 08:18:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH31"/>
+  <dimension ref="A1:BH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,121 +757,121 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.2</v>
+        <v>1.39</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>1.91</v>
+        <v>1.38</v>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>970</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>2.14</v>
       </c>
       <c r="K2" t="n">
-        <v>3.5</v>
+        <v>6.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="P2" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.62</v>
+        <v>1.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="S2" t="n">
         <v>1.05</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>1.11</v>
       </c>
       <c r="U2" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="V2" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
         <v>8</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AE2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AG2" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH2" t="n">
         <v>34</v>
       </c>
-      <c r="AH2" t="n">
-        <v>36</v>
-      </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AK2" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AL2" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM2" t="n">
         <v>280</v>
       </c>
-      <c r="AM2" t="n">
-        <v>340</v>
-      </c>
       <c r="AN2" t="n">
-        <v>440</v>
+        <v>250</v>
       </c>
       <c r="AO2" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
-        <v>4.6</v>
+        <v>7</v>
       </c>
       <c r="AQ2" t="n">
         <v>5.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>5.4</v>
+        <v>2.94</v>
       </c>
       <c r="AS2" t="n">
         <v>16.5</v>
@@ -880,47 +880,47 @@
         <v>10</v>
       </c>
       <c r="AU2" t="n">
-        <v>4.6</v>
+        <v>2.34</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="AX2" t="n">
-        <v>8.6</v>
+        <v>2.78</v>
       </c>
       <c r="AY2" t="n">
-        <v>7.4</v>
+        <v>2.68</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.800000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="BB2" t="n">
-        <v>10.5</v>
+        <v>2.92</v>
       </c>
       <c r="BC2" t="n">
-        <v>10</v>
+        <v>2.88</v>
       </c>
       <c r="BD2" t="n">
-        <v>10</v>
+        <v>2.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>10.5</v>
+        <v>2.92</v>
       </c>
       <c r="BF2" t="n">
-        <v>10.5</v>
+        <v>2.92</v>
       </c>
       <c r="BG2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -954,167 +954,167 @@
         <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
-        <v>4.7</v>
+        <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>1.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.16</v>
+        <v>1.23</v>
       </c>
       <c r="O3" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="P3" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV3" t="n">
         <v>1.13</v>
       </c>
-      <c r="S3" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.48</v>
-      </c>
       <c r="AW3" t="n">
-        <v>2.66</v>
+        <v>1.18</v>
       </c>
       <c r="AX3" t="n">
-        <v>3.5</v>
+        <v>1.18</v>
       </c>
       <c r="AY3" t="n">
-        <v>2.26</v>
+        <v>1.18</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.52</v>
+        <v>1.15</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.66</v>
+        <v>1.18</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.46</v>
+        <v>1.13</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.52</v>
+        <v>1.15</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.62</v>
+        <v>1.18</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.66</v>
+        <v>1.18</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.52</v>
+        <v>1.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.66</v>
+        <v>1.18</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="I5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="K5" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="O5" t="n">
         <v>1.26</v>
       </c>
       <c r="P5" t="n">
-        <v>1.97</v>
+        <v>1.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>1.45</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S5" t="n">
-        <v>2.96</v>
+        <v>2.24</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>2.24</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV5" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AX5" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.91</v>
+        <v>1.02</v>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>3.85</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P6" t="n">
         <v>1.34</v>
       </c>
-      <c r="P6" t="n">
-        <v>1.87</v>
-      </c>
       <c r="Q6" t="n">
-        <v>1.96</v>
+        <v>1.31</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>3.35</v>
+        <v>2.66</v>
       </c>
       <c r="T6" t="n">
-        <v>1.81</v>
+        <v>1.11</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V6" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1727,64 +1727,64 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.48</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="O7" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="R7" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="T7" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -1796,13 +1796,13 @@
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
         <v>16</v>
@@ -1814,83 +1814,83 @@
         <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AJ7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK7" t="n">
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>7</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>4.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>4.6</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>4.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>30</v>
+        <v>4.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>9.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>32</v>
+        <v>4.7</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.5</v>
+        <v>5</v>
       </c>
       <c r="BF7" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>26</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -1927,10 +1927,10 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -1939,7 +1939,7 @@
         <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
@@ -1948,13 +1948,13 @@
         <v>2.92</v>
       </c>
       <c r="O8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
         <v>1.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
         <v>28</v>
@@ -1987,25 +1987,25 @@
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
         <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
@@ -2023,22 +2023,22 @@
         <v>170</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
         <v>90</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.800000000000001</v>
+        <v>5.9</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>4.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="AT8" t="n">
         <v>7</v>
@@ -2047,10 +2047,10 @@
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AW8" t="n">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2059,32 +2059,32 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.5</v>
+        <v>4.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>23</v>
+        <v>9.4</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>9.6</v>
       </c>
       <c r="BD8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BG8" t="n">
         <v>12</v>
       </c>
-      <c r="BE8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>12.5</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2118,7 @@
         <v>1.85</v>
       </c>
       <c r="G9" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H9" t="n">
         <v>5.3</v>
@@ -2127,10 +2127,10 @@
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>1.58</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Fluminense RJ (W)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>EC Juventude (W)</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>2.06</v>
+        <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>3.95</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>3.75</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O10" t="n">
         <v>1.32</v>
       </c>
-      <c r="M10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.28</v>
-      </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.85</v>
+        <v>1.32</v>
       </c>
       <c r="R10" t="n">
-        <v>1.43</v>
+        <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>1.32</v>
       </c>
       <c r="T10" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
         <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR10" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="AS10" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV10" t="n">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW10" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AX10" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY10" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA10" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BC10" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BD10" t="n">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BE10" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>2.08</v>
       </c>
       <c r="H11" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="S11" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="U11" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF11" t="n">
         <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.03</v>
+        <v>3.65</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="G12" t="n">
-        <v>2.14</v>
+        <v>3.35</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="K12" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M12" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>3.1</v>
+        <v>2.16</v>
       </c>
       <c r="O12" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="S12" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="T12" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="W12" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="X12" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Z12" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD12" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE12" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG12" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH12" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AK12" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AS12" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT12" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV12" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AW12" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="AX12" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12" t="n">
-        <v>5.6</v>
+        <v>1.03</v>
       </c>
       <c r="BA12" t="n">
-        <v>6.6</v>
+        <v>1.03</v>
       </c>
       <c r="BB12" t="n">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC12" t="n">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="BD12" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE12" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG12" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,28 +2882,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.26</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -2912,43 +2912,43 @@
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="O13" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="S13" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U13" t="n">
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2963,28 +2963,28 @@
         <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI13" t="n">
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL13" t="n">
         <v>1000</v>
@@ -2993,75 +2993,75 @@
         <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.03</v>
+        <v>1.98</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.03</v>
+        <v>7</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.03</v>
+        <v>2.02</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.03</v>
+        <v>1.91</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.03</v>
+        <v>1.96</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.03</v>
+        <v>2.06</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.03</v>
+        <v>2.08</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Boyaca Patriotas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.86</v>
+        <v>1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>3.05</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.8</v>
+        <v>1.04</v>
       </c>
       <c r="I14" t="n">
-        <v>2.96</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="M14" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N14" t="n">
-        <v>2.72</v>
+        <v>1.67</v>
       </c>
       <c r="O14" t="n">
-        <v>1.51</v>
+        <v>1.07</v>
       </c>
       <c r="P14" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.52</v>
+        <v>1.87</v>
       </c>
       <c r="R14" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="S14" t="n">
-        <v>5.1</v>
+        <v>1.87</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>1.48</v>
+        <v>2.42</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV14" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="AX14" t="n">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AY14" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BB14" t="n">
-        <v>4.8</v>
+        <v>1.03</v>
       </c>
       <c r="BC14" t="n">
-        <v>4.7</v>
+        <v>1.03</v>
       </c>
       <c r="BD14" t="n">
-        <v>4.9</v>
+        <v>1.03</v>
       </c>
       <c r="BE14" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,60 +3265,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="O15" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="T15" t="n">
         <v>1.01</v>
@@ -3327,10 +3327,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,184 +3459,184 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P16" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3658,179 +3658,179 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G17" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>4.7</v>
+        <v>1.41</v>
       </c>
       <c r="I17" t="n">
-        <v>5.2</v>
+        <v>530</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.65</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>1.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -3864,174 +3864,174 @@
         <v>2.48</v>
       </c>
       <c r="G18" t="n">
-        <v>2.66</v>
+        <v>970</v>
       </c>
       <c r="H18" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>3.05</v>
+        <v>1.43</v>
       </c>
       <c r="K18" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.94</v>
+        <v>1.25</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>1.43</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>1.43</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
         <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Z18" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA18" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="AD18" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI18" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ18" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AK18" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM18" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR18" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV18" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW18" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF18" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Botafogo FR</t>
+          <t>EC Bahia (W)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>America MG (W)</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.3</v>
+        <v>1.04</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42</v>
+        <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="I19" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L19" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>3.2</v>
+        <v>1.25</v>
       </c>
       <c r="O19" t="n">
-        <v>1.39</v>
+        <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>1.16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>1.16</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="W19" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y19" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Z19" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA19" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE19" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF19" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG19" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH19" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI19" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ19" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK19" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL19" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM19" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AO19" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP19" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR19" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AS19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT19" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV19" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AW19" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="AX19" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ19" t="n">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="BA19" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="BB19" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BC19" t="n">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="BD19" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF19" t="n">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19:30:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sao Paulo</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>1.96</v>
       </c>
       <c r="G20" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="H20" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>3.9</v>
+        <v>60</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="L20" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="X20" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ20" t="n">
         <v>1.09</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="X20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>18</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>32</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>10</v>
-      </c>
       <c r="AR20" t="n">
-        <v>17.5</v>
+        <v>1.09</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.7</v>
+        <v>1.09</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>1.09</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.4</v>
+        <v>1.09</v>
       </c>
       <c r="AV20" t="n">
-        <v>13</v>
+        <v>1.09</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.6</v>
+        <v>1.09</v>
       </c>
       <c r="AX20" t="n">
-        <v>11.5</v>
+        <v>1.09</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>1.09</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.7</v>
+        <v>1.09</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.2</v>
+        <v>1.09</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.2</v>
+        <v>1.09</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.6</v>
+        <v>1.09</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.9</v>
+        <v>1.09</v>
       </c>
       <c r="BF20" t="n">
-        <v>18</v>
+        <v>1.09</v>
       </c>
       <c r="BG20" t="n">
-        <v>5.6</v>
+        <v>1.09</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,191 +4429,191 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Botafogo FR</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="G21" t="n">
-        <v>2.12</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>4.7</v>
+        <v>1.09</v>
       </c>
       <c r="I21" t="n">
-        <v>5.2</v>
+        <v>110</v>
       </c>
       <c r="J21" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="O21" t="n">
-        <v>1.64</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.46</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.92</v>
+        <v>1.37</v>
       </c>
       <c r="R21" t="n">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="S21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="X21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG21" t="n">
         <v>6.4</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="X21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>350</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>240</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>46</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="G22" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="H22" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="X22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE22" t="n">
         <v>5</v>
       </c>
-      <c r="I22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="S22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="BF22" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG22" t="n">
-        <v>4.7</v>
+        <v>46</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="G23" t="n">
-        <v>1.63</v>
+        <v>1.91</v>
       </c>
       <c r="H23" t="n">
-        <v>7</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="J23" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K23" t="n">
         <v>4.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P23" t="n">
         <v>1.77</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>2.08</v>
       </c>
       <c r="T23" t="n">
-        <v>2.16</v>
+        <v>1.96</v>
       </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="V23" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="W23" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="X23" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y23" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD23" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP23" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH23" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ23" t="n">
+      <c r="AQ23" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC23" t="n">
         <v>15</v>
       </c>
-      <c r="AK23" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
+      <c r="BD23" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF23" t="n">
         <v>11</v>
       </c>
-      <c r="AQ23" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>28</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>25</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>10</v>
-      </c>
       <c r="BG23" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.58</v>
+        <v>1.58</v>
       </c>
       <c r="G24" t="n">
-        <v>2.78</v>
+        <v>1.61</v>
       </c>
       <c r="H24" t="n">
-        <v>2.94</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>3.15</v>
+        <v>7.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O24" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="U24" t="n">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="V24" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="X24" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Z24" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>260</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>200</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>48</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV24" t="n">
         <v>21</v>
       </c>
-      <c r="AA24" t="n">
-        <v>65</v>
-      </c>
-      <c r="AB24" t="n">
+      <c r="AW24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="BC24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BD24" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>48</v>
+      </c>
+      <c r="BF24" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AD24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>42</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BD24" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BE24" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG24" t="n">
-        <v>4.1</v>
+        <v>46</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,186 +5210,186 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.63</v>
+        <v>2.54</v>
       </c>
       <c r="G25" t="n">
-        <v>1.68</v>
+        <v>2.82</v>
       </c>
       <c r="H25" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="I25" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>1.4</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9</v>
+        <v>1.4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.16</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
         <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
         <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
         <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,55 +5404,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.36</v>
+        <v>1.96</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S26" t="n">
-        <v>1.36</v>
+        <v>3.7</v>
       </c>
       <c r="T26" t="n">
         <v>1.01</v>
@@ -5464,7 +5464,7 @@
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="X26" t="n">
         <v>1000</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,184 +5593,184 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>2.74</v>
+        <v>1.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="P27" t="n">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.34</v>
+        <v>1.36</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
-        <v>4.8</v>
+        <v>1.36</v>
       </c>
       <c r="T27" t="n">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="W27" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="X27" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>8.4</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
@@ -5787,191 +5787,191 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="G28" t="n">
-        <v>1.83</v>
+        <v>970</v>
       </c>
       <c r="H28" t="n">
-        <v>5.8</v>
+        <v>1.05</v>
       </c>
       <c r="I28" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="J28" t="n">
-        <v>3.5</v>
+        <v>1.09</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.92</v>
+        <v>1.57</v>
       </c>
       <c r="O28" t="n">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="P28" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.18</v>
+        <v>1.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="T28" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.16</v>
+        <v>1.67</v>
       </c>
       <c r="W28" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,85 +5986,85 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.92</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>2</v>
+        <v>110</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>1.4</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>970</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>1.41</v>
       </c>
       <c r="K29" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>1.64</v>
       </c>
       <c r="O29" t="n">
-        <v>1.48</v>
+        <v>1.1</v>
       </c>
       <c r="P29" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.44</v>
+        <v>1.45</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="S29" t="n">
-        <v>4.8</v>
+        <v>2.16</v>
       </c>
       <c r="T29" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="U29" t="n">
-        <v>1.79</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W29" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="X29" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
         <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>6.8</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
         <v>1000</v>
@@ -6073,10 +6073,10 @@
         <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
         <v>1000</v>
@@ -6094,7 +6094,7 @@
         <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
         <v>1000</v>
@@ -6103,69 +6103,69 @@
         <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,373 +6180,567 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="G30" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I30" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K30" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="P30" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="Q30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W30" t="n">
         <v>2</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X30" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="Z30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE30" t="n">
         <v>46</v>
       </c>
-      <c r="AA30" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>150</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BF30" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>5.3</v>
+        <v>40</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-31 08:18:01</t>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="I31" t="n">
+        <v>970</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K31" t="n">
+        <v>950</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="S31" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:36:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Atletico Nacional Medellin</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>Cucuta Deportivo</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="G31" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="H31" t="n">
-        <v>13</v>
-      </c>
-      <c r="I31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="J31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="F32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M32" t="n">
         <v>1.02</v>
       </c>
-      <c r="N31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="N32" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="X31" t="n">
-        <v>34</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>60</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>200</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>15</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>360</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>2026-03-31 08:18:01</t>
+      <c r="O32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-31 10:36:15</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH32"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.39</v>
+        <v>4.8</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="H2" t="n">
-        <v>1.38</v>
+        <v>1.97</v>
       </c>
       <c r="I2" t="n">
-        <v>970</v>
+        <v>2.08</v>
       </c>
       <c r="J2" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>6.8</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M2" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>1.1</v>
+        <v>2.34</v>
       </c>
       <c r="O2" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="P2" t="n">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.02</v>
+        <v>2.94</v>
       </c>
       <c r="R2" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>1.05</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.11</v>
+        <v>2.42</v>
       </c>
       <c r="U2" t="n">
-        <v>1.11</v>
+        <v>1.6</v>
       </c>
       <c r="V2" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.4</v>
+        <v>5.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF2" t="n">
         <v>38</v>
       </c>
-      <c r="AF2" t="n">
-        <v>48</v>
-      </c>
       <c r="AG2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AJ2" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AK2" t="n">
         <v>140</v>
       </c>
       <c r="AL2" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="AN2" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.94</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>2.34</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.3</v>
+        <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.78</v>
+        <v>10</v>
       </c>
       <c r="AY2" t="n">
-        <v>2.68</v>
+        <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.2</v>
+        <v>26</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.84</v>
+        <v>12</v>
       </c>
       <c r="BB2" t="n">
-        <v>2.92</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.88</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.92</v>
+        <v>12</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.92</v>
+        <v>12</v>
       </c>
       <c r="BG2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -954,55 +954,55 @@
         <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H3" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1.05</v>
+        <v>2.88</v>
       </c>
       <c r="K3" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>1.23</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="P3" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="R3" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.62</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="V3" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.18</v>
+        <v>5.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.18</v>
+        <v>5.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.18</v>
+        <v>1.67</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.18</v>
+        <v>4.1</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.18</v>
+        <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.13</v>
+        <v>1.96</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.18</v>
+        <v>1.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.18</v>
+        <v>4.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.15</v>
+        <v>1.65</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.18</v>
+        <v>1.52</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.15</v>
+        <v>1.99</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.18</v>
+        <v>1.51</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.18</v>
+        <v>1.71</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.15</v>
+        <v>1.64</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.18</v>
+        <v>1.71</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1339,58 +1339,58 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
-        <v>3.15</v>
+        <v>2.68</v>
       </c>
       <c r="H5" t="n">
-        <v>2.48</v>
+        <v>2.72</v>
       </c>
       <c r="I5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>4</v>
       </c>
-      <c r="J5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K5" t="n">
-        <v>950</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>2.86</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="S5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="U5" t="n">
         <v>2.24</v>
       </c>
-      <c r="T5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.11</v>
-      </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.02</v>
+        <v>1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>1000</v>
+        <v>2.14</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>3.9</v>
       </c>
       <c r="I6" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>1.35</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.34</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.31</v>
+        <v>1.98</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>2.66</v>
+        <v>3.4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V6" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI6" t="n">
         <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1727,13 +1727,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
         <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I7" t="n">
         <v>3.3</v>
@@ -1745,34 +1745,34 @@
         <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R7" t="n">
         <v>1.34</v>
       </c>
-      <c r="P7" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.31</v>
-      </c>
       <c r="S7" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="V7" t="n">
         <v>1.43</v>
@@ -1784,7 +1784,7 @@
         <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -1793,7 +1793,7 @@
         <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -1814,7 +1814,7 @@
         <v>17.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
         <v>34</v>
@@ -1829,22 +1829,22 @@
         <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO7" t="n">
         <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.800000000000001</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
@@ -1856,7 +1856,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.6</v>
+        <v>32</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1868,29 +1868,29 @@
         <v>15.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.8</v>
+        <v>13</v>
       </c>
       <c r="BB7" t="n">
-        <v>4.6</v>
+        <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.7</v>
+        <v>36</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>12.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.6</v>
+        <v>25</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -1927,49 +1927,49 @@
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
         <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
         <v>1.83</v>
@@ -1978,7 +1978,7 @@
         <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
         <v>28</v>
@@ -1987,28 +1987,28 @@
         <v>110</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE8" t="n">
         <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AJ8" t="n">
         <v>28</v>
@@ -2017,40 +2017,40 @@
         <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AP8" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.1</v>
+        <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.6</v>
+        <v>13.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
         <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX8" t="n">
         <v>10.5</v>
@@ -2059,32 +2059,32 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>8.800000000000001</v>
+        <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>4.5</v>
+        <v>13</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.4</v>
+        <v>24</v>
       </c>
       <c r="BC8" t="n">
-        <v>9.6</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.4</v>
+        <v>12.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="G9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H9" t="n">
         <v>5.3</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
         <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2309,112 +2309,112 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>1.24</v>
+        <v>2.88</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="P10" t="n">
-        <v>1.24</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.32</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>1.32</v>
+        <v>2.7</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="V10" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>2.5</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
@@ -2465,14 +2465,14 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
         <v>2.08</v>
       </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I11" t="n">
         <v>4.1</v>
@@ -2533,31 +2533,31 @@
         <v>1.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R11" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="U11" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="V11" t="n">
         <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y11" t="n">
         <v>17</v>
@@ -2581,7 +2581,7 @@
         <v>46</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG11" t="n">
         <v>10.5</v>
@@ -2617,10 +2617,10 @@
         <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.65</v>
+        <v>14</v>
       </c>
       <c r="AT11" t="n">
         <v>9.6</v>
@@ -2629,7 +2629,7 @@
         <v>7.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AW11" t="n">
         <v>12.5</v>
@@ -2638,25 +2638,25 @@
         <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>6.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ11" t="n">
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="BC11" t="n">
-        <v>9.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD11" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.8</v>
+        <v>14</v>
       </c>
       <c r="BF11" t="n">
         <v>11.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2697,58 +2697,58 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.26</v>
+        <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="J12" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>5.2</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.16</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.52</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R12" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V12" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2853,14 +2853,14 @@
         <v>1.03</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -2891,64 +2891,64 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
-        <v>1.09</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>110</v>
+        <v>4.7</v>
       </c>
       <c r="J13" t="n">
-        <v>1.09</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="P13" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.38</v>
+        <v>2.18</v>
       </c>
       <c r="R13" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
-        <v>2.18</v>
+        <v>4.1</v>
       </c>
       <c r="T13" t="n">
         <v>1.92</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V13" t="n">
         <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,19 +2957,19 @@
         <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG13" t="n">
         <v>12.5</v>
@@ -2981,19 +2981,19 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3005,10 +3005,10 @@
         <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.98</v>
+        <v>6.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.06</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
         <v>7</v>
@@ -3020,7 +3020,7 @@
         <v>14</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.02</v>
+        <v>7.4</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3029,32 +3029,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.91</v>
+        <v>6.2</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.06</v>
+        <v>7.6</v>
       </c>
       <c r="BB13" t="n">
         <v>6.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.96</v>
+        <v>6.4</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.06</v>
+        <v>7.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.08</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.96</v>
+        <v>6.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.06</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3085,109 +3085,109 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.04</v>
+        <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>1.61</v>
       </c>
       <c r="H14" t="n">
-        <v>1.04</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M14" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.67</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="W14" t="n">
-        <v>2.42</v>
+        <v>2.64</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3205,7 +3205,7 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AU14" t="n">
         <v>1.03</v>
@@ -3241,14 +3241,14 @@
         <v>1.03</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>85</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3279,103 +3279,103 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="I15" t="n">
         <v>2.96</v>
       </c>
       <c r="J15" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="K15" t="n">
         <v>3.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P15" t="n">
         <v>1.58</v>
       </c>
-      <c r="O15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="Q15" t="n">
-        <v>1.5</v>
+        <v>2.52</v>
       </c>
       <c r="R15" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5</v>
+        <v>5.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V15" t="n">
         <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF15" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK15" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
-        <v>1.41</v>
+        <v>4.4</v>
       </c>
       <c r="I17" t="n">
-        <v>530</v>
+        <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>3.45</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3700,7 +3700,7 @@
         <v>1.56</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.5</v>
+        <v>2.26</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -3864,167 +3864,167 @@
         <v>2.48</v>
       </c>
       <c r="G18" t="n">
-        <v>970</v>
+        <v>2.64</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I18" t="n">
         <v>3.45</v>
       </c>
       <c r="J18" t="n">
-        <v>1.43</v>
+        <v>3.05</v>
       </c>
       <c r="K18" t="n">
         <v>3.25</v>
       </c>
       <c r="L18" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M18" t="n">
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>1.25</v>
+        <v>2.94</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.43</v>
+        <v>2.32</v>
       </c>
       <c r="R18" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="S18" t="n">
-        <v>1.43</v>
+        <v>4.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="V18" t="n">
         <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -4252,167 +4252,167 @@
         <v>1.96</v>
       </c>
       <c r="G20" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>4.7</v>
       </c>
       <c r="I20" t="n">
-        <v>60</v>
+        <v>5.3</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="O20" t="n">
-        <v>1.1</v>
+        <v>1.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.44</v>
+        <v>2.36</v>
       </c>
       <c r="R20" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="S20" t="n">
-        <v>1.44</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W20" t="n">
-        <v>1.26</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y20" t="n">
         <v>970</v>
       </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.09</v>
+        <v>9.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.09</v>
+        <v>6.2</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.09</v>
+        <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.09</v>
+        <v>7.8</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.09</v>
+        <v>11</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.09</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.09</v>
+        <v>9.6</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.09</v>
+        <v>11</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.09</v>
+        <v>8</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.09</v>
+        <v>10</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.09</v>
+        <v>14</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.09</v>
+        <v>11.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>110</v>
+        <v>3.5</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
@@ -4461,64 +4461,64 @@
         <v>3.55</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M21" t="n">
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.37</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="X21" t="n">
         <v>12</v>
       </c>
       <c r="Y21" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD21" t="n">
         <v>14.5</v>
       </c>
-      <c r="Z21" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1000</v>
-      </c>
       <c r="AE21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF21" t="n">
         <v>14.5</v>
@@ -4530,90 +4530,90 @@
         <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM21" t="n">
         <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP21" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>10.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="AT21" t="n">
         <v>8</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="AX21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>30</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG21" t="n">
         <v>12</v>
       </c>
-      <c r="AY21" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>9</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,191 +4623,191 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>19:30:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Platense</t>
+          <t>Sao Paulo</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.02</v>
+        <v>2.28</v>
       </c>
       <c r="G22" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>5.1</v>
+        <v>3.85</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M22" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.47</v>
+        <v>1.75</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.94</v>
+        <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.16</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>2.94</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>2.42</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS22" t="n">
         <v>8.4</v>
       </c>
-      <c r="Y22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>36</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC22" t="n">
+      <c r="AT22" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW22" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>26</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>32</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR22" t="n">
+      <c r="AX22" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC22" t="n">
         <v>20</v>
       </c>
-      <c r="AS22" t="n">
-        <v>42</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>38</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>21</v>
-      </c>
       <c r="BD22" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="BE22" t="n">
-        <v>5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG22" t="n">
-        <v>46</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Lanus</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Athletico-PR</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.81</v>
+        <v>2.02</v>
       </c>
       <c r="G23" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M23" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="N23" t="n">
-        <v>3.3</v>
+        <v>2.42</v>
       </c>
       <c r="O23" t="n">
-        <v>1.35</v>
+        <v>1.64</v>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.08</v>
+        <v>2.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="S23" t="n">
-        <v>2.08</v>
+        <v>6.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.96</v>
+        <v>2.42</v>
       </c>
       <c r="U23" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="X23" t="n">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="Y23" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>36</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>350</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>240</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>20</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>19</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>38</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>44</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF23" t="n">
         <v>18.5</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>9</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>44</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>11</v>
-      </c>
       <c r="BG23" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -5016,179 +5016,179 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cruzeiro MG</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>EC Vitoria Salvador</t>
+          <t>Athletico-PR</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="G24" t="n">
-        <v>1.61</v>
+        <v>1.87</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="I24" t="n">
-        <v>7.8</v>
+        <v>5.2</v>
       </c>
       <c r="J24" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>2.16</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.77</v>
+        <v>1.95</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.62</v>
+        <v>2.14</v>
       </c>
       <c r="X24" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y24" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD24" t="n">
         <v>21</v>
       </c>
-      <c r="Z24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>260</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>48</v>
-      </c>
       <c r="AE24" t="n">
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
         <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AJ24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AK24" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>200</v>
+        <v>42</v>
       </c>
       <c r="AM24" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AQ24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR24" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AU24" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AX24" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AY24" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BC24" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>44</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG24" t="n">
         <v>36</v>
       </c>
-      <c r="BE24" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF24" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>46</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -5205,191 +5205,191 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Cruzeiro MG</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>EC Vitoria Salvador</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.54</v>
+        <v>1.58</v>
       </c>
       <c r="G25" t="n">
-        <v>2.82</v>
+        <v>1.61</v>
       </c>
       <c r="H25" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="J25" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.4</v>
+        <v>2.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="X25" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AB25" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE25" t="n">
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG25" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI25" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AK25" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN25" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO25" t="n">
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="G26" t="n">
-        <v>1.68</v>
+        <v>2.74</v>
       </c>
       <c r="H26" t="n">
-        <v>2.54</v>
+        <v>2.96</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
-        <v>2.52</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="M26" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
+        <v>3</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R26" t="n">
         <v>1.24</v>
       </c>
-      <c r="O26" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.21</v>
-      </c>
       <c r="S26" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>2.46</v>
+        <v>1.57</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O27" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.36</v>
+        <v>2.08</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S27" t="n">
-        <v>1.36</v>
+        <v>3.9</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,60 +5787,60 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="O28" t="n">
-        <v>1.1</v>
+        <v>1.36</v>
       </c>
       <c r="P28" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
       <c r="R28" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.67</v>
+        <v>1.84</v>
       </c>
       <c r="W28" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>3.9</v>
       </c>
       <c r="G29" t="n">
-        <v>110</v>
+        <v>4.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1.4</v>
+        <v>2.12</v>
       </c>
       <c r="I29" t="n">
-        <v>970</v>
+        <v>2.32</v>
       </c>
       <c r="J29" t="n">
-        <v>1.41</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>3.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M29" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>1.64</v>
+        <v>2.74</v>
       </c>
       <c r="O29" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.45</v>
+        <v>2.46</v>
       </c>
       <c r="R29" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>2.16</v>
+        <v>4.8</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="W29" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.94</v>
+        <v>1.7</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H30" t="n">
-        <v>4.7</v>
+        <v>5.8</v>
       </c>
       <c r="I30" t="n">
-        <v>5.4</v>
+        <v>7</v>
       </c>
       <c r="J30" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M30" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="O30" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P30" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.38</v>
+        <v>2.18</v>
       </c>
       <c r="R30" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>4.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="U30" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="X30" t="n">
         <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AB30" t="n">
         <v>7.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="AD30" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF30" t="n">
         <v>11</v>
       </c>
       <c r="AG30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ30" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AK30" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AN30" t="n">
-        <v>26</v>
+        <v>18.5</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AQ30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF30" t="n">
         <v>12</v>
       </c>
-      <c r="AR30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG30" t="n">
-        <v>40</v>
+        <v>5.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,373 +6374,567 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.09</v>
+        <v>1.94</v>
       </c>
       <c r="G31" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="H31" t="n">
-        <v>1.09</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>970</v>
+        <v>5.1</v>
       </c>
       <c r="J31" t="n">
-        <v>1.33</v>
+        <v>3.3</v>
       </c>
       <c r="K31" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="P31" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.36</v>
+        <v>2.42</v>
       </c>
       <c r="R31" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="S31" t="n">
-        <v>1.92</v>
+        <v>4.7</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W31" t="n">
-        <v>1.3</v>
+        <v>1.99</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-31 10:36:15</t>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Avai</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M32" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X32" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>19</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:43:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Colombian Primera A</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>22:30:00</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>Atletico Nacional Medellin</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>Cucuta Deportivo</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="G32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="K32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="F33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13</v>
+      </c>
+      <c r="I33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="M33" t="n">
         <v>1.02</v>
       </c>
-      <c r="N32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="T32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH32" t="inlineStr">
-        <is>
-          <t>2026-03-31 10:36:15</t>
+      <c r="N33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X33" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>200</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>360</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-31 12:43:31</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="I2" t="n">
         <v>2.08</v>
@@ -772,7 +772,7 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
         <v>1.58</v>
@@ -808,7 +808,7 @@
         <v>1.92</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
         <v>7.6</v>
@@ -835,7 +835,7 @@
         <v>34</v>
       </c>
       <c r="AF2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
         <v>26</v>
@@ -862,7 +862,7 @@
         <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP2" t="n">
         <v>6.6</v>
@@ -889,7 +889,7 @@
         <v>25</v>
       </c>
       <c r="AX2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY2" t="n">
         <v>19</v>
@@ -907,20 +907,20 @@
         <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BG2" t="n">
         <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G3" t="n">
         <v>1.98</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I3" t="n">
         <v>6.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="K3" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
         <v>1.58</v>
@@ -975,7 +975,7 @@
         <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
         <v>1.69</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="I5" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L5" t="n">
         <v>1.3</v>
@@ -1369,28 +1369,28 @@
         <v>1.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S5" t="n">
         <v>2.94</v>
       </c>
       <c r="T5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1450,7 +1450,7 @@
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR5" t="n">
         <v>5.6</v>
@@ -1468,10 +1468,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY5" t="n">
         <v>8.6</v>
@@ -1489,10 +1489,10 @@
         <v>6</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1533,67 +1533,67 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.96</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.14</v>
+        <v>2.42</v>
       </c>
       <c r="H6" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="I6" t="n">
-        <v>4.7</v>
+        <v>3.85</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P6" t="n">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R6" t="n">
         <v>1.33</v>
       </c>
       <c r="S6" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="X6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>18</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1602,10 +1602,10 @@
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>70</v>
@@ -1617,13 +1617,13 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ6" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1647,25 +1647,25 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT6" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="AV6" t="n">
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AY6" t="n">
         <v>7.8</v>
@@ -1674,7 +1674,7 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BB6" t="n">
         <v>17.5</v>
@@ -1683,20 +1683,20 @@
         <v>19</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF6" t="n">
         <v>13.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1754,19 +1754,19 @@
         <v>3.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
         <v>1.79</v>
@@ -1775,7 +1775,7 @@
         <v>2.12</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.67</v>
@@ -1799,7 +1799,7 @@
         <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
         <v>38</v>
@@ -1811,10 +1811,10 @@
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ7" t="n">
         <v>34</v>
@@ -1826,7 +1826,7 @@
         <v>42</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN7" t="n">
         <v>28</v>
@@ -1835,7 +1835,7 @@
         <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>11</v>
@@ -1850,7 +1850,7 @@
         <v>9.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
@@ -1886,11 +1886,11 @@
         <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -1945,19 +1945,19 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="O8" t="n">
         <v>1.48</v>
       </c>
       <c r="P8" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q8" t="n">
         <v>2.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S8" t="n">
         <v>5.1</v>
@@ -1972,7 +1972,7 @@
         <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X8" t="n">
         <v>10</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
         <v>110</v>
@@ -1996,7 +1996,7 @@
         <v>18</v>
       </c>
       <c r="AE8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
         <v>11.5</v>
@@ -2005,7 +2005,7 @@
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>95</v>
@@ -2026,7 +2026,7 @@
         <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AP8" t="n">
         <v>8.6</v>
@@ -2038,10 +2038,10 @@
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.6</v>
@@ -2050,10 +2050,10 @@
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2062,7 +2062,7 @@
         <v>21</v>
       </c>
       <c r="BA8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB8" t="n">
         <v>24</v>
@@ -2071,7 +2071,7 @@
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BE8" t="n">
         <v>13.5</v>
@@ -2080,11 +2080,11 @@
         <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -2118,13 +2118,13 @@
         <v>1.88</v>
       </c>
       <c r="G9" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H9" t="n">
         <v>5.3</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
         <v>3.2</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -2348,13 +2348,13 @@
         <v>1.29</v>
       </c>
       <c r="S10" t="n">
-        <v>2.7</v>
+        <v>1.05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="V10" t="n">
         <v>1.13</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G11" t="n">
         <v>2.08</v>
@@ -2533,10 +2533,10 @@
         <v>1.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R11" t="n">
         <v>1.43</v>
@@ -2560,7 +2560,7 @@
         <v>16.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z11" t="n">
         <v>30</v>
@@ -2590,7 +2590,7 @@
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
@@ -2605,7 +2605,7 @@
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO11" t="n">
         <v>44</v>
@@ -2620,19 +2620,19 @@
         <v>27</v>
       </c>
       <c r="AS11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT11" t="n">
         <v>9.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
         <v>14.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX11" t="n">
         <v>12</v>
@@ -2644,7 +2644,7 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB11" t="n">
         <v>22</v>
@@ -2656,17 +2656,17 @@
         <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BF11" t="n">
         <v>11.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="H12" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L12" t="n">
         <v>1.5</v>
@@ -2742,10 +2742,10 @@
         <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W12" t="n">
         <v>1.52</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -2894,13 +2894,13 @@
         <v>2.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.3</v>
@@ -2918,22 +2918,22 @@
         <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="R13" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
         <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U13" t="n">
         <v>1.92</v>
@@ -2942,10 +2942,10 @@
         <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y13" t="n">
         <v>15</v>
@@ -2960,7 +2960,7 @@
         <v>7.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
@@ -3002,13 +3002,13 @@
         <v>10</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
         <v>7</v>
@@ -3017,10 +3017,10 @@
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>14</v>
+        <v>5.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3029,32 +3029,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB13" t="n">
         <v>6.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.5</v>
       </c>
       <c r="G14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H14" t="n">
         <v>7</v>
@@ -3100,7 +3100,7 @@
         <v>3.85</v>
       </c>
       <c r="K14" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L14" t="n">
         <v>1.36</v>
@@ -3118,7 +3118,7 @@
         <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
         <v>1.29</v>
@@ -3157,7 +3157,7 @@
         <v>11.5</v>
       </c>
       <c r="AD14" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
@@ -3205,7 +3205,7 @@
         <v>1.03</v>
       </c>
       <c r="AT14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU14" t="n">
         <v>1.03</v>
@@ -3244,11 +3244,11 @@
         <v>7.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -3282,100 +3282,100 @@
         <v>2.9</v>
       </c>
       <c r="G15" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H15" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="I15" t="n">
         <v>2.96</v>
       </c>
       <c r="J15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="L15" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M15" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.72</v>
+        <v>2.4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="P15" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.52</v>
+        <v>2.86</v>
       </c>
       <c r="R15" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="S15" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="T15" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="U15" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
         <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB15" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AE15" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AF15" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AI15" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK15" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AL15" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AR15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS15" t="n">
         <v>8</v>
       </c>
       <c r="AT15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW15" t="n">
         <v>7.8</v>
       </c>
-      <c r="AU15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AX15" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>19</v>
+        <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB15" t="n">
         <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF15" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BE15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BG15" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.4</v>
@@ -3512,13 +3512,13 @@
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3670,7 @@
         <v>2</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
         <v>4.4</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -3897,10 +3897,10 @@
         <v>2.32</v>
       </c>
       <c r="R18" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="S18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T18" t="n">
         <v>1.9</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -4079,13 +4079,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O19" t="n">
         <v>1.16</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q19" t="n">
         <v>1.16</v>
@@ -4097,10 +4097,10 @@
         <v>1.16</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V19" t="n">
         <v>1.01</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -4264,7 +4264,7 @@
         <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
         <v>1.42</v>
@@ -4285,7 +4285,7 @@
         <v>2.36</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
         <v>4.7</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -4455,10 +4455,10 @@
         <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L21" t="n">
         <v>1.47</v>
@@ -4476,31 +4476,31 @@
         <v>1.77</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
         <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V21" t="n">
         <v>1.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X21" t="n">
         <v>12</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
         <v>23</v>
@@ -4509,7 +4509,7 @@
         <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
         <v>7.6</v>
@@ -4527,10 +4527,10 @@
         <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ21" t="n">
         <v>34</v>
@@ -4539,7 +4539,7 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
         <v>130</v>
@@ -4560,7 +4560,7 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT21" t="n">
         <v>8</v>
@@ -4569,7 +4569,7 @@
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AW21" t="n">
         <v>32</v>
@@ -4584,7 +4584,7 @@
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB21" t="n">
         <v>28</v>
@@ -4596,17 +4596,17 @@
         <v>30</v>
       </c>
       <c r="BE21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BF21" t="n">
         <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.28</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H22" t="n">
         <v>3.75</v>
@@ -4649,7 +4649,7 @@
         <v>3.85</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
         <v>3.4</v>
@@ -4688,7 +4688,7 @@
         <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="X22" t="n">
         <v>11.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -4867,7 +4867,7 @@
         <v>2.94</v>
       </c>
       <c r="R23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S23" t="n">
         <v>6.4</v>
@@ -4891,7 +4891,7 @@
         <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA23" t="n">
         <v>190</v>
@@ -4930,7 +4930,7 @@
         <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="AN23" t="n">
         <v>32</v>
@@ -4966,7 +4966,7 @@
         <v>9</v>
       </c>
       <c r="AY23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ23" t="n">
         <v>21</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.84</v>
       </c>
       <c r="G24" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="H24" t="n">
         <v>4.9</v>
@@ -5043,7 +5043,7 @@
         <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
@@ -5052,7 +5052,7 @@
         <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
         <v>1.83</v>
@@ -5076,7 +5076,7 @@
         <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X24" t="n">
         <v>13</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.39</v>
@@ -5249,19 +5249,19 @@
         <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q25" t="n">
         <v>2.16</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U25" t="n">
         <v>1.77</v>
@@ -5270,7 +5270,7 @@
         <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="X25" t="n">
         <v>12.5</v>
@@ -5285,10 +5285,10 @@
         <v>260</v>
       </c>
       <c r="AB25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD25" t="n">
         <v>29</v>
@@ -5297,7 +5297,7 @@
         <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
@@ -5312,7 +5312,7 @@
         <v>15</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AL25" t="n">
         <v>48</v>
@@ -5330,10 +5330,10 @@
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AS25" t="n">
         <v>48</v>
@@ -5342,16 +5342,16 @@
         <v>6.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>40</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY25" t="n">
         <v>9.4</v>
@@ -5372,7 +5372,7 @@
         <v>36</v>
       </c>
       <c r="BE25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF25" t="n">
         <v>10</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -5416,19 +5416,19 @@
         <v>2.66</v>
       </c>
       <c r="G26" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="H26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.4</v>
       </c>
       <c r="L26" t="n">
         <v>1.41</v>
@@ -5440,28 +5440,28 @@
         <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R26" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U26" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W26" t="n">
         <v>1.57</v>
@@ -5479,7 +5479,7 @@
         <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
         <v>8</v>
@@ -5521,62 +5521,62 @@
         <v>46</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR26" t="n">
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW26" t="n">
         <v>7.2</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>6.8</v>
       </c>
       <c r="AX26" t="n">
         <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
         <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB26" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC26" t="n">
         <v>7</v>
       </c>
-      <c r="BC26" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BD26" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF26" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BG26" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -5613,46 +5613,46 @@
         <v>1.68</v>
       </c>
       <c r="H27" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="O27" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="R27" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="U27" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="V27" t="n">
         <v>1.16</v>
@@ -5661,10 +5661,10 @@
         <v>2.46</v>
       </c>
       <c r="X27" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -5673,104 +5673,104 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG27" t="n">
         <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ27" t="n">
         <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU27" t="n">
         <v>7.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>8.199999999999999</v>
+        <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AX27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BE27" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AZ27" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>11</v>
-      </c>
       <c r="BF27" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG27" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -5840,13 +5840,13 @@
         <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
         <v>1.84</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -6004,10 +6004,10 @@
         <v>2.12</v>
       </c>
       <c r="I29" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
         <v>3.4</v>
@@ -6043,7 +6043,7 @@
         <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W29" t="n">
         <v>1.29</v>
@@ -6052,31 +6052,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z29" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AB29" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF29" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AH29" t="n">
         <v>27</v>
@@ -6100,7 +6100,7 @@
         <v>120</v>
       </c>
       <c r="AO29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AP29" t="n">
         <v>8.4</v>
@@ -6112,7 +6112,7 @@
         <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AT29" t="n">
         <v>9.6</v>
@@ -6124,10 +6124,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW29" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="AY29" t="n">
         <v>15</v>
@@ -6136,29 +6136,29 @@
         <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG29" t="n">
         <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>1.7</v>
       </c>
       <c r="G30" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H30" t="n">
         <v>5.8</v>
@@ -6222,7 +6222,7 @@
         <v>1.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="R30" t="n">
         <v>1.23</v>
@@ -6237,7 +6237,7 @@
         <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W30" t="n">
         <v>2.24</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="M31" t="n">
         <v>1.11</v>
@@ -6422,7 +6422,7 @@
         <v>1.23</v>
       </c>
       <c r="S31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T31" t="n">
         <v>2.12</v>
@@ -6443,7 +6443,7 @@
         <v>14</v>
       </c>
       <c r="Z31" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
         <v>130</v>
@@ -6452,7 +6452,7 @@
         <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
         <v>21</v>
@@ -6479,7 +6479,7 @@
         <v>36</v>
       </c>
       <c r="AL31" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
         <v>200</v>
@@ -6518,7 +6518,7 @@
         <v>9.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
         <v>17</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
         <v>1.82</v>
       </c>
       <c r="G32" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H32" t="n">
         <v>4.9</v>
@@ -6592,7 +6592,7 @@
         <v>3.55</v>
       </c>
       <c r="K32" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L32" t="n">
         <v>1.38</v>
@@ -6610,7 +6610,7 @@
         <v>1.81</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="R32" t="n">
         <v>1.31</v>
@@ -6622,7 +6622,7 @@
         <v>1.92</v>
       </c>
       <c r="U32" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V32" t="n">
         <v>1.22</v>
@@ -6634,13 +6634,13 @@
         <v>15</v>
       </c>
       <c r="Y32" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="Z32" t="n">
         <v>46</v>
       </c>
       <c r="AA32" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB32" t="n">
         <v>9.199999999999999</v>
@@ -6664,7 +6664,7 @@
         <v>24</v>
       </c>
       <c r="AI32" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ32" t="n">
         <v>24</v>
@@ -6694,7 +6694,7 @@
         <v>4.7</v>
       </c>
       <c r="AS32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT32" t="n">
         <v>7</v>
@@ -6730,17 +6730,17 @@
         <v>4.7</v>
       </c>
       <c r="BE32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF32" t="n">
         <v>10.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="G33" t="n">
         <v>1.3</v>
@@ -6786,10 +6786,10 @@
         <v>6.2</v>
       </c>
       <c r="K33" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="M33" t="n">
         <v>1.02</v>
@@ -6801,7 +6801,7 @@
         <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q33" t="n">
         <v>1.51</v>
@@ -6810,7 +6810,7 @@
         <v>1.66</v>
       </c>
       <c r="S33" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="T33" t="n">
         <v>2.08</v>
@@ -6870,13 +6870,13 @@
         <v>40</v>
       </c>
       <c r="AM33" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN33" t="n">
         <v>4.3</v>
       </c>
       <c r="AO33" t="n">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="AP33" t="n">
         <v>6.8</v>
@@ -6885,7 +6885,7 @@
         <v>7.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS33" t="n">
         <v>8.800000000000001</v>
@@ -6909,7 +6909,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA33" t="n">
         <v>8.4</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-31 12:43:31</t>
+          <t>2026-03-31 14:53:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
         <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="I2" t="n">
         <v>2.08</v>
@@ -772,10 +772,10 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
@@ -784,25 +784,25 @@
         <v>2.34</v>
       </c>
       <c r="O2" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.64</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.6</v>
       </c>
       <c r="V2" t="n">
         <v>1.92</v>
@@ -811,10 +811,10 @@
         <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
@@ -823,104 +823,104 @@
         <v>26</v>
       </c>
       <c r="AB2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AG2" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ2" t="n">
         <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AM2" t="n">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AO2" t="n">
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AS2" t="n">
         <v>17.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV2" t="n">
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>25</v>
+        <v>7.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>10.5</v>
+        <v>28</v>
       </c>
       <c r="AY2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>12</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD2" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="BE2" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="BG2" t="n">
         <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -984,7 +984,7 @@
         <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.74</v>
+        <v>2.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.13</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1145,46 +1145,46 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H4" t="n">
-        <v>1.11</v>
+        <v>5.5</v>
       </c>
       <c r="I4" t="n">
-        <v>980</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>1.02</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R4" t="n">
         <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1.05</v>
+        <v>2.74</v>
       </c>
       <c r="T4" t="n">
         <v>2.32</v>
@@ -1193,122 +1193,122 @@
         <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="X4" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
         <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="AB4" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AE4" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AF4" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK4" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM4" t="n">
-        <v>1000</v>
+        <v>820</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.04</v>
+        <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.04</v>
+        <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.04</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.05</v>
+        <v>3.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.04</v>
+        <v>12</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.04</v>
+        <v>17.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.04</v>
+        <v>3.35</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.04</v>
+        <v>3.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
         <v>3.4</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
         <v>3.95</v>
@@ -1387,7 +1387,7 @@
         <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
         <v>1.62</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="n">
         <v>3.35</v>
@@ -1584,7 +1584,7 @@
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
@@ -1593,7 +1593,7 @@
         <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1620,7 +1620,7 @@
         <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
         <v>32</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1647,10 +1647,10 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
         <v>8.4</v>
@@ -1662,7 +1662,7 @@
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="AX6" t="n">
         <v>12.5</v>
@@ -1674,29 +1674,29 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB6" t="n">
         <v>17.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG6" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1739,10 +1739,10 @@
         <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.35</v>
@@ -1751,28 +1751,28 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
         <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
         <v>1.44</v>
@@ -1781,7 +1781,7 @@
         <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
         <v>12.5</v>
@@ -1799,7 +1799,7 @@
         <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE7" t="n">
         <v>38</v>
@@ -1811,7 +1811,7 @@
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI7" t="n">
         <v>50</v>
@@ -1823,10 +1823,10 @@
         <v>27</v>
       </c>
       <c r="AL7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
         <v>28</v>
@@ -1841,16 +1841,16 @@
         <v>11</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV7" t="n">
         <v>12.5</v>
@@ -1865,32 +1865,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF7" t="n">
         <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>29</v>
+        <v>12.5</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G8" t="n">
         <v>2.2</v>
       </c>
       <c r="H8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I8" t="n">
         <v>4.2</v>
       </c>
-      <c r="I8" t="n">
-        <v>4.5</v>
-      </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
         <v>1.45</v>
@@ -1948,28 +1948,28 @@
         <v>2.98</v>
       </c>
       <c r="O8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
         <v>1.84</v>
@@ -1981,7 +1981,7 @@
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA8" t="n">
         <v>110</v>
@@ -1999,16 +1999,16 @@
         <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
         <v>28</v>
@@ -2017,19 +2017,19 @@
         <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AN8" t="n">
         <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
@@ -2038,7 +2038,7 @@
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT8" t="n">
         <v>6.6</v>
@@ -2050,7 +2050,7 @@
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AX8" t="n">
         <v>10</v>
@@ -2059,32 +2059,32 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BB8" t="n">
         <v>24</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2118,16 +2118,16 @@
         <v>1.88</v>
       </c>
       <c r="G9" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K9" t="n">
         <v>3.4</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2309,112 +2309,112 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="H10" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K10" t="n">
         <v>5.4</v>
       </c>
-      <c r="I10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5.3</v>
-      </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="R10" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S10" t="n">
         <v>1.05</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.71</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="X10" t="n">
         <v>18</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="Z10" t="n">
-        <v>75</v>
+        <v>130</v>
       </c>
       <c r="AA10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>290</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>240</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM10" t="n">
         <v>320</v>
       </c>
-      <c r="AB10" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>160</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>150</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>270</v>
-      </c>
       <c r="AN10" t="n">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>260</v>
+        <v>550</v>
       </c>
       <c r="AP10" t="n">
         <v>1.03</v>
@@ -2465,14 +2465,14 @@
         <v>1.03</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BG10" t="n">
         <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2503,19 +2503,19 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G11" t="n">
         <v>2.08</v>
       </c>
       <c r="H11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I11" t="n">
         <v>4.1</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
         <v>3.85</v>
@@ -2536,7 +2536,7 @@
         <v>2.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R11" t="n">
         <v>1.43</v>
@@ -2554,7 +2554,7 @@
         <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="X11" t="n">
         <v>16.5</v>
@@ -2587,7 +2587,7 @@
         <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI11" t="n">
         <v>55</v>
@@ -2602,7 +2602,7 @@
         <v>34</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN11" t="n">
         <v>13.5</v>
@@ -2638,7 +2638,7 @@
         <v>12</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
         <v>15.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.63</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>3.25</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.22</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.26</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.27</v>
       </c>
       <c r="BF12" t="n">
-        <v>32</v>
+        <v>1.24</v>
       </c>
       <c r="BG12" t="n">
-        <v>50</v>
+        <v>1.26</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G13" t="n">
         <v>2.14</v>
@@ -2915,7 +2915,7 @@
         <v>1.09</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
         <v>1.42</v>
@@ -2939,10 +2939,10 @@
         <v>1.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W13" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X13" t="n">
         <v>13</v>
@@ -3020,7 +3020,7 @@
         <v>5.9</v>
       </c>
       <c r="AW13" t="n">
-        <v>7.6</v>
+        <v>50</v>
       </c>
       <c r="AX13" t="n">
         <v>10.5</v>
@@ -3047,14 +3047,14 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF13" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="BG13" t="n">
         <v>7.8</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3091,10 +3091,10 @@
         <v>1.6</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J14" t="n">
         <v>3.85</v>
@@ -3118,10 +3118,10 @@
         <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S14" t="n">
         <v>3.45</v>
@@ -3136,7 +3136,7 @@
         <v>1.11</v>
       </c>
       <c r="W14" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X14" t="n">
         <v>14</v>
@@ -3145,7 +3145,7 @@
         <v>26</v>
       </c>
       <c r="Z14" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
@@ -3193,62 +3193,62 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.03</v>
+        <v>3.8</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AT14" t="n">
         <v>5.1</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.03</v>
+        <v>3.05</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.03</v>
+        <v>3.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.6</v>
+        <v>3.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>90</v>
+        <v>4.4</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="G15" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H15" t="n">
         <v>2.86</v>
@@ -3291,7 +3291,7 @@
         <v>2.96</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
         <v>3.15</v>
@@ -3330,7 +3330,7 @@
         <v>1.51</v>
       </c>
       <c r="W15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="X15" t="n">
         <v>8</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I17" t="n">
         <v>5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G18" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="H18" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="I18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>3.05</v>
       </c>
       <c r="K18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.44</v>
@@ -3891,7 +3891,7 @@
         <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="Q18" t="n">
         <v>2.32</v>
@@ -3909,10 +3909,10 @@
         <v>1.92</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="X18" t="n">
         <v>12</v>
@@ -3930,13 +3930,13 @@
         <v>10</v>
       </c>
       <c r="AC18" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD18" t="n">
         <v>17</v>
       </c>
       <c r="AE18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF18" t="n">
         <v>16.5</v>
@@ -3948,7 +3948,7 @@
         <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ18" t="n">
         <v>42</v>
@@ -3978,7 +3978,7 @@
         <v>18.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -4002,36 +4002,36 @@
         <v>17.5</v>
       </c>
       <c r="BA18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF18" t="n">
         <v>5.2</v>
       </c>
-      <c r="BB18" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BG18" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,186 +4046,186 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EC Bahia (W)</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>America MG (W)</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.04</v>
+        <v>1.89</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="H19" t="n">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I19" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="K19" t="n">
-        <v>950</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M19" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>1.26</v>
+        <v>2.88</v>
       </c>
       <c r="O19" t="n">
-        <v>1.16</v>
+        <v>1.46</v>
       </c>
       <c r="P19" t="n">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.16</v>
+        <v>2.36</v>
       </c>
       <c r="R19" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>1.16</v>
+        <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V19" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z19" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AA19" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB19" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF19" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI19" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AO19" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AT19" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD19" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>EC Bahia (W)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>America MG (W)</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.96</v>
+        <v>1.04</v>
       </c>
       <c r="G20" t="n">
-        <v>1.99</v>
+        <v>1000</v>
       </c>
       <c r="H20" t="n">
-        <v>4.7</v>
+        <v>1.04</v>
       </c>
       <c r="I20" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>950</v>
       </c>
       <c r="L20" t="n">
-        <v>1.42</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N20" t="n">
         <v>1.1</v>
       </c>
-      <c r="N20" t="n">
-        <v>2.88</v>
-      </c>
       <c r="O20" t="n">
-        <v>1.46</v>
+        <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.36</v>
+        <v>1.16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="S20" t="n">
-        <v>4.7</v>
+        <v>1.16</v>
       </c>
       <c r="T20" t="n">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.23</v>
+        <v>1.01</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AQ20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR20" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT20" t="n">
-        <v>6.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU20" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AV20" t="n">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AW20" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AX20" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BA20" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="BB20" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BC20" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="BD20" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="BE20" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BF20" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>3.5</v>
       </c>
       <c r="J21" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>3.5</v>
@@ -4530,7 +4530,7 @@
         <v>24</v>
       </c>
       <c r="AI21" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ21" t="n">
         <v>34</v>
@@ -4539,7 +4539,7 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM21" t="n">
         <v>130</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         <v>3.4</v>
       </c>
       <c r="L22" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4673,7 +4673,7 @@
         <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
         <v>4.1</v>
@@ -4688,7 +4688,7 @@
         <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X22" t="n">
         <v>11.5</v>
@@ -4775,7 +4775,7 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
         <v>8.4</v>
@@ -4793,14 +4793,14 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF22" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BG22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -4840,10 +4840,10 @@
         <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
@@ -4891,7 +4891,7 @@
         <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AA23" t="n">
         <v>190</v>
@@ -4933,7 +4933,7 @@
         <v>340</v>
       </c>
       <c r="AN23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO23" t="n">
         <v>240</v>
@@ -4957,13 +4957,13 @@
         <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW23" t="n">
         <v>38</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
@@ -4978,10 +4978,10 @@
         <v>16.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE23" t="n">
         <v>95</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>1.84</v>
       </c>
       <c r="G24" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H24" t="n">
         <v>4.9</v>
@@ -5043,7 +5043,7 @@
         <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
@@ -5052,7 +5052,7 @@
         <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P24" t="n">
         <v>1.83</v>
@@ -5064,7 +5064,7 @@
         <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T24" t="n">
         <v>1.98</v>
@@ -5082,10 +5082,10 @@
         <v>13</v>
       </c>
       <c r="Y24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
         <v>150</v>
@@ -5115,7 +5115,7 @@
         <v>100</v>
       </c>
       <c r="AJ24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK24" t="n">
         <v>22</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -5219,31 +5219,31 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="G25" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
       </c>
       <c r="I25" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L25" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
         <v>1.39</v>
@@ -5261,16 +5261,16 @@
         <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X25" t="n">
         <v>12.5</v>
@@ -5282,7 +5282,7 @@
         <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB25" t="n">
         <v>7</v>
@@ -5291,10 +5291,10 @@
         <v>9</v>
       </c>
       <c r="AD25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE25" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF25" t="n">
         <v>8.6</v>
@@ -5306,7 +5306,7 @@
         <v>27</v>
       </c>
       <c r="AI25" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ25" t="n">
         <v>15</v>
@@ -5315,31 +5315,31 @@
         <v>19.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>210</v>
       </c>
       <c r="AM25" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="n">
         <v>11.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AS25" t="n">
         <v>48</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU25" t="n">
         <v>8.199999999999999</v>
@@ -5369,7 +5369,7 @@
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BE25" t="n">
         <v>46</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>20:15:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Atletico Choloma</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.66</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>3.25</v>
+        <v>1.03</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>950</v>
       </c>
       <c r="L26" t="n">
-        <v>1.41</v>
+        <v>1.01</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>1.24</v>
       </c>
       <c r="O26" t="n">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="P26" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.28</v>
+        <v>1.24</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.57</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR26" t="n">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV26" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW26" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AX26" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AY26" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BA26" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="BE26" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="BF26" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.65</v>
+        <v>2.66</v>
       </c>
       <c r="G27" t="n">
-        <v>1.68</v>
+        <v>2.78</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>3.15</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
         <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="P27" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.96</v>
+        <v>2.28</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U27" t="n">
-        <v>1.86</v>
+        <v>1.97</v>
       </c>
       <c r="V27" t="n">
-        <v>1.16</v>
+        <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>2.46</v>
+        <v>1.56</v>
       </c>
       <c r="X27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR27" t="n">
         <v>16.5</v>
       </c>
-      <c r="Y27" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>120</v>
-      </c>
-      <c r="AJ27" t="n">
+      <c r="AS27" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>17</v>
       </c>
-      <c r="AK27" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BA27" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>7.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="BD27" t="n">
         <v>7.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
-        <v>1.9</v>
+        <v>3.45</v>
       </c>
       <c r="O28" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P28" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S28" t="n">
-        <v>1.89</v>
+        <v>3.55</v>
       </c>
       <c r="T28" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.11</v>
+        <v>1.86</v>
       </c>
       <c r="V28" t="n">
-        <v>1.84</v>
+        <v>1.16</v>
       </c>
       <c r="W28" t="n">
-        <v>1.26</v>
+        <v>2.46</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AK28" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,184 +5981,184 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="T29" t="n">
         <v>1.11</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U29" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="W29" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="X29" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>210</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -6175,184 +6175,184 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.7</v>
+        <v>3.9</v>
       </c>
       <c r="G30" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.79</v>
       </c>
-      <c r="H30" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I30" t="n">
+      <c r="V30" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="X30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BB30" t="n">
         <v>7</v>
       </c>
-      <c r="J30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S30" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W30" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="X30" t="n">
-        <v>11</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>250</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>230</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU30" t="n">
+      <c r="BC30" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE30" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="BF30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG30" t="n">
         <v>21</v>
       </c>
-      <c r="AW30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>12</v>
-      </c>
-      <c r="BG30" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -6404,7 +6404,7 @@
         <v>1.53</v>
       </c>
       <c r="M31" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
         <v>3</v>
@@ -6452,7 +6452,7 @@
         <v>7</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD31" t="n">
         <v>21</v>
@@ -6473,10 +6473,10 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
@@ -6740,14 +6740,14 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-31 14:53:12</t>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,184 +6757,378 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>22:30:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="G33" t="n">
-        <v>1.3</v>
+        <v>1.79</v>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>5.8</v>
       </c>
       <c r="I33" t="n">
-        <v>16.5</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="X33" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>240</v>
+      </c>
+      <c r="AB33" t="n">
         <v>7.6</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N33" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="S33" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W33" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="X33" t="n">
-        <v>30</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>170</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AC33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AF33" t="n">
         <v>11</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>9</v>
       </c>
       <c r="AG33" t="n">
         <v>12</v>
       </c>
       <c r="AH33" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>140</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>230</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>12</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:00:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Atletico Nacional Medellin</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>13</v>
+      </c>
+      <c r="I34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="K34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N34" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W34" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="X34" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH34" t="n">
         <v>36</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AI34" t="n">
         <v>200</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AJ34" t="n">
         <v>10.5</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AK34" t="n">
         <v>15</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AL34" t="n">
         <v>40</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AM34" t="n">
         <v>200</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AN34" t="n">
         <v>4.3</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AO34" t="n">
         <v>340</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AP34" t="n">
         <v>6.8</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AQ34" t="n">
         <v>7.4</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AR34" t="n">
         <v>8.4</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AS34" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AT34" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AU34" t="n">
         <v>13</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AV34" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AW34" t="n">
         <v>8.4</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AX34" t="n">
         <v>7.2</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="AY34" t="n">
         <v>9.6</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="AZ34" t="n">
         <v>7.2</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BA34" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BB34" t="n">
         <v>8.6</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BC34" t="n">
         <v>12</v>
       </c>
-      <c r="BD33" t="n">
+      <c r="BD34" t="n">
         <v>7.2</v>
       </c>
-      <c r="BE33" t="n">
+      <c r="BE34" t="n">
         <v>8.4</v>
       </c>
-      <c r="BF33" t="n">
+      <c r="BF34" t="n">
         <v>3.6</v>
       </c>
-      <c r="BG33" t="n">
+      <c r="BG34" t="n">
         <v>8.6</v>
       </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-03-31 14:53:12</t>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-31 17:00:46</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -781,7 +781,7 @@
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O2" t="n">
         <v>1.61</v>
@@ -790,7 +790,7 @@
         <v>1.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="R2" t="n">
         <v>1.16</v>
@@ -814,7 +814,7 @@
         <v>7.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
@@ -829,7 +829,7 @@
         <v>7.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>32</v>
@@ -865,7 +865,7 @@
         <v>32</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
         <v>5.4</v>
@@ -886,7 +886,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.4</v>
+        <v>16</v>
       </c>
       <c r="AX2" t="n">
         <v>28</v>
@@ -898,29 +898,29 @@
         <v>24</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BD2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K3" t="n">
         <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M3" t="n">
         <v>1.13</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
         <v>1.69</v>
@@ -999,10 +999,10 @@
         <v>1.53</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1062,13 +1062,13 @@
         <v>5.3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.67</v>
+        <v>2.38</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.52</v>
+        <v>2.48</v>
       </c>
       <c r="AT3" t="n">
         <v>4.1</v>
@@ -1077,44 +1077,44 @@
         <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.96</v>
+        <v>2.34</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.65</v>
+        <v>2.34</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.52</v>
+        <v>2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.63</v>
+        <v>2.3</v>
       </c>
       <c r="BC3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BD3" t="n">
         <v>1.99</v>
       </c>
-      <c r="BD3" t="n">
-        <v>1.51</v>
-      </c>
       <c r="BE3" t="n">
-        <v>1.71</v>
+        <v>2.84</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.64</v>
+        <v>2.34</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.71</v>
+        <v>2.48</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1148,19 +1148,19 @@
         <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="H4" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L4" t="n">
         <v>1.47</v>
@@ -1169,13 +1169,13 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="O4" t="n">
         <v>1.45</v>
       </c>
       <c r="P4" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q4" t="n">
         <v>2.42</v>
@@ -1193,16 +1193,16 @@
         <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
         <v>95</v>
@@ -1250,10 +1250,10 @@
         <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>12</v>
@@ -1262,19 +1262,19 @@
         <v>3.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AT4" t="n">
-        <v>2.34</v>
+        <v>3.25</v>
       </c>
       <c r="AU4" t="n">
         <v>7.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.25</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AX4" t="n">
         <v>6</v>
@@ -1286,7 +1286,7 @@
         <v>3.25</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BB4" t="n">
         <v>12</v>
@@ -1304,11 +1304,11 @@
         <v>10.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
         <v>2.6</v>
       </c>
       <c r="H5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="I5" t="n">
         <v>3.4</v>
@@ -1354,34 +1354,34 @@
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="O5" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q5" t="n">
         <v>1.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="S5" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U5" t="n">
         <v>2.26</v>
@@ -1393,7 +1393,7 @@
         <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1408,7 +1408,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1453,25 +1453,25 @@
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>6.6</v>
+        <v>4.1</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV5" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AY5" t="n">
         <v>8.6</v>
@@ -1480,29 +1480,29 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="H6" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.36</v>
@@ -1575,16 +1575,16 @@
         <v>3.5</v>
       </c>
       <c r="T6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
@@ -1593,10 +1593,10 @@
         <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
         <v>11</v>
@@ -1620,10 +1620,10 @@
         <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AJ6" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1635,7 +1635,7 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1647,25 +1647,25 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.2</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AU6" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV6" t="n">
         <v>12.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
         <v>7.8</v>
@@ -1674,7 +1674,7 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
         <v>17.5</v>
@@ -1683,20 +1683,20 @@
         <v>21</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.7</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BF6" t="n">
         <v>16.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
         <v>2.48</v>
@@ -1736,16 +1736,16 @@
         <v>3.2</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
         <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1757,7 +1757,7 @@
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -1766,13 +1766,13 @@
         <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V7" t="n">
         <v>1.44</v>
@@ -1781,10 +1781,10 @@
         <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -1796,7 +1796,7 @@
         <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
@@ -1811,10 +1811,10 @@
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AJ7" t="n">
         <v>34</v>
@@ -1826,7 +1826,7 @@
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
         <v>28</v>
@@ -1838,22 +1838,22 @@
         <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW7" t="n">
         <v>32</v>
@@ -1874,23 +1874,23 @@
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD7" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BF7" t="n">
         <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.18</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J8" t="n">
         <v>3.3</v>
@@ -1951,25 +1951,25 @@
         <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T8" t="n">
         <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
         <v>1.84</v>
@@ -1984,19 +1984,19 @@
         <v>28</v>
       </c>
       <c r="AA8" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
@@ -2008,7 +2008,7 @@
         <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>28</v>
@@ -2017,13 +2017,13 @@
         <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
         <v>95</v>
@@ -2032,28 +2032,28 @@
         <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="AX8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
@@ -2062,29 +2062,29 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.5</v>
+        <v>70</v>
       </c>
       <c r="BB8" t="n">
         <v>24</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BE8" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
         <v>14</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.88</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
         <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1.46</v>
       </c>
       <c r="H10" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="I10" t="n">
         <v>12.5</v>
@@ -2327,7 +2327,7 @@
         <v>5.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
@@ -2354,7 +2354,7 @@
         <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2378,7 +2378,7 @@
         <v>8</v>
       </c>
       <c r="AC10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AD10" t="n">
         <v>50</v>
@@ -2399,10 +2399,10 @@
         <v>240</v>
       </c>
       <c r="AJ10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AK10" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AL10" t="n">
         <v>65</v>
@@ -2411,68 +2411,68 @@
         <v>320</v>
       </c>
       <c r="AN10" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO10" t="n">
         <v>550</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.03</v>
+        <v>5.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF10" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
         <v>2.04</v>
       </c>
-      <c r="G11" t="n">
-        <v>2.08</v>
-      </c>
       <c r="H11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="J11" t="n">
         <v>3.7</v>
@@ -2527,13 +2527,13 @@
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P11" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
         <v>1.87</v>
@@ -2542,22 +2542,22 @@
         <v>1.43</v>
       </c>
       <c r="S11" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T11" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="U11" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V11" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="X11" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y11" t="n">
         <v>16.5</v>
@@ -2566,7 +2566,7 @@
         <v>30</v>
       </c>
       <c r="AA11" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB11" t="n">
         <v>10.5</v>
@@ -2578,7 +2578,7 @@
         <v>16.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF11" t="n">
         <v>13.5</v>
@@ -2593,13 +2593,13 @@
         <v>55</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK11" t="n">
         <v>21</v>
       </c>
       <c r="AL11" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM11" t="n">
         <v>90</v>
@@ -2608,31 +2608,31 @@
         <v>13.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP11" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
         <v>14.5</v>
       </c>
       <c r="AR11" t="n">
-        <v>27</v>
+        <v>14.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU11" t="n">
         <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="AX11" t="n">
         <v>12</v>
@@ -2644,10 +2644,10 @@
         <v>15.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BB11" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BC11" t="n">
         <v>18.5</v>
@@ -2656,7 +2656,7 @@
         <v>29</v>
       </c>
       <c r="BE11" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BF11" t="n">
         <v>11.5</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2700,16 +2700,16 @@
         <v>2.54</v>
       </c>
       <c r="G12" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="H12" t="n">
         <v>3.05</v>
       </c>
       <c r="I12" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="K12" t="n">
         <v>3.2</v>
@@ -2721,7 +2721,7 @@
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="O12" t="n">
         <v>1.52</v>
@@ -2730,7 +2730,7 @@
         <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
@@ -2745,13 +2745,13 @@
         <v>1.78</v>
       </c>
       <c r="V12" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y12" t="n">
         <v>1000</v>
@@ -2766,7 +2766,7 @@
         <v>1000</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT12" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ12" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AU12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.27</v>
+        <v>3.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.27</v>
+        <v>3.4</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.27</v>
+        <v>5.1</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.22</v>
+        <v>3.6</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.26</v>
+        <v>2.38</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.24</v>
+        <v>2.38</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.24</v>
+        <v>2.32</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.25</v>
+        <v>2.38</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.27</v>
+        <v>2.44</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.24</v>
+        <v>2.3</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.26</v>
+        <v>2.32</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>2.14</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I13" t="n">
         <v>4.6</v>
@@ -2906,10 +2906,10 @@
         <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L13" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="M13" t="n">
         <v>1.09</v>
@@ -2924,25 +2924,25 @@
         <v>1.71</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S13" t="n">
         <v>4.1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="U13" t="n">
         <v>1.92</v>
       </c>
       <c r="V13" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="X13" t="n">
         <v>13</v>
@@ -2951,7 +2951,7 @@
         <v>15</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA13" t="n">
         <v>1000</v>
@@ -2963,7 +2963,7 @@
         <v>8</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE13" t="n">
         <v>1000</v>
@@ -2981,7 +2981,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK13" t="n">
         <v>29</v>
@@ -2990,10 +2990,10 @@
         <v>55</v>
       </c>
       <c r="AM13" t="n">
-        <v>160</v>
+        <v>580</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO13" t="n">
         <v>1000</v>
@@ -3008,7 +3008,7 @@
         <v>6.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
         <v>7</v>
@@ -3017,7 +3017,7 @@
         <v>6.8</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.9</v>
+        <v>9</v>
       </c>
       <c r="AW13" t="n">
         <v>50</v>
@@ -3029,32 +3029,32 @@
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BA13" t="n">
         <v>7.8</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.4</v>
+        <v>11.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD13" t="n">
         <v>7.4</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
         <v>17</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G14" t="n">
         <v>1.6</v>
@@ -3097,10 +3097,10 @@
         <v>11</v>
       </c>
       <c r="J14" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.36</v>
@@ -3109,16 +3109,16 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.28</v>
@@ -3127,10 +3127,10 @@
         <v>3.45</v>
       </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="U14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="V14" t="n">
         <v>1.11</v>
@@ -3139,7 +3139,7 @@
         <v>2.66</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y14" t="n">
         <v>26</v>
@@ -3151,104 +3151,104 @@
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AD14" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AG14" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="AH14" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AK14" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="AL14" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AM14" t="n">
         <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>12.5</v>
+        <v>29</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AR14" t="n">
         <v>4.2</v>
       </c>
       <c r="AS14" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT14" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY14" t="n">
         <v>5.1</v>
       </c>
-      <c r="AU14" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AZ14" t="n">
-        <v>3.95</v>
+        <v>2.68</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.5</v>
+        <v>5.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="BD14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BG14" t="n">
         <v>4.2</v>
       </c>
-      <c r="BE14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G15" t="n">
         <v>3.1</v>
@@ -3288,7 +3288,7 @@
         <v>2.86</v>
       </c>
       <c r="I15" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="J15" t="n">
         <v>2.94</v>
@@ -3297,22 +3297,22 @@
         <v>3.15</v>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M15" t="n">
         <v>1.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="O15" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="P15" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="R15" t="n">
         <v>1.17</v>
@@ -3327,7 +3327,7 @@
         <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
         <v>1.47</v>
@@ -3342,7 +3342,7 @@
         <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="AB15" t="n">
         <v>9.199999999999999</v>
@@ -3351,31 +3351,31 @@
         <v>8</v>
       </c>
       <c r="AD15" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="AF15" t="n">
         <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="AJ15" t="n">
-        <v>60</v>
+        <v>340</v>
       </c>
       <c r="AK15" t="n">
-        <v>50</v>
+        <v>190</v>
       </c>
       <c r="AL15" t="n">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -3396,7 +3396,7 @@
         <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT15" t="n">
         <v>7</v>
@@ -3408,7 +3408,7 @@
         <v>13</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX15" t="n">
         <v>15.5</v>
@@ -3417,32 +3417,32 @@
         <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BA15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC15" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE15" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BG15" t="n">
         <v>9</v>
       </c>
-      <c r="BF15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S16" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="T16" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U16" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="W16" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
         <v>2.08</v>
       </c>
       <c r="H17" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K17" t="n">
         <v>3.45</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>2.52</v>
       </c>
       <c r="G18" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H18" t="n">
         <v>3.45</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>3.2</v>
@@ -3885,55 +3885,55 @@
         <v>1.1</v>
       </c>
       <c r="N18" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="O18" t="n">
         <v>1.44</v>
       </c>
       <c r="P18" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="Q18" t="n">
         <v>2.32</v>
       </c>
       <c r="R18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S18" t="n">
         <v>4.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W18" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X18" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA18" t="n">
         <v>70</v>
       </c>
       <c r="AB18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE18" t="n">
         <v>50</v>
@@ -3945,7 +3945,7 @@
         <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="AI18" t="n">
         <v>70</v>
@@ -3954,13 +3954,13 @@
         <v>42</v>
       </c>
       <c r="AK18" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL18" t="n">
         <v>65</v>
       </c>
       <c r="AM18" t="n">
-        <v>160</v>
+        <v>450</v>
       </c>
       <c r="AN18" t="n">
         <v>34</v>
@@ -3978,7 +3978,7 @@
         <v>18.5</v>
       </c>
       <c r="AS18" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="AT18" t="n">
         <v>7.4</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX18" t="n">
         <v>12</v>
@@ -3999,32 +3999,32 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BB18" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC18" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>5.6</v>
+        <v>8</v>
       </c>
       <c r="BE18" t="n">
-        <v>5.9</v>
+        <v>8.4</v>
       </c>
       <c r="BF18" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BG18" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>1.89</v>
       </c>
       <c r="G19" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H19" t="n">
         <v>4.8</v>
@@ -4067,10 +4067,10 @@
         <v>5.4</v>
       </c>
       <c r="J19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L19" t="n">
         <v>1.52</v>
@@ -4079,7 +4079,7 @@
         <v>1.1</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O19" t="n">
         <v>1.46</v>
@@ -4097,7 +4097,7 @@
         <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
@@ -4112,13 +4112,13 @@
         <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>970</v>
+        <v>28</v>
       </c>
       <c r="Z19" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="AA19" t="n">
-        <v>180</v>
+        <v>900</v>
       </c>
       <c r="AB19" t="n">
         <v>7</v>
@@ -4127,10 +4127,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD19" t="n">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>470</v>
       </c>
       <c r="AF19" t="n">
         <v>10.5</v>
@@ -4139,25 +4139,25 @@
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>120</v>
+        <v>450</v>
       </c>
       <c r="AJ19" t="n">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="AL19" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN19" t="n">
         <v>55</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>970</v>
       </c>
       <c r="AO19" t="n">
         <v>170</v>
@@ -4169,10 +4169,10 @@
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4181,10 +4181,10 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX19" t="n">
         <v>9.199999999999999</v>
@@ -4193,22 +4193,22 @@
         <v>9.6</v>
       </c>
       <c r="AZ19" t="n">
-        <v>8.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>8</v>
+        <v>10.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
       </c>
       <c r="BE19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF19" t="n">
         <v>14</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -4249,19 +4249,19 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="G20" t="n">
-        <v>1000</v>
+        <v>1.67</v>
       </c>
       <c r="H20" t="n">
-        <v>1.04</v>
+        <v>4.6</v>
       </c>
       <c r="I20" t="n">
         <v>1000</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="K20" t="n">
         <v>950</v>
@@ -4273,19 +4273,19 @@
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="O20" t="n">
         <v>1.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Q20" t="n">
         <v>1.16</v>
       </c>
       <c r="R20" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S20" t="n">
         <v>1.16</v>
@@ -4297,10 +4297,10 @@
         <v>1.11</v>
       </c>
       <c r="V20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4351,68 +4351,68 @@
         <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO20" t="n">
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.03</v>
+        <v>1.44</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.03</v>
+        <v>1.49</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.03</v>
+        <v>1.56</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4488,7 @@
         <v>1.93</v>
       </c>
       <c r="U21" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.4</v>
@@ -4503,10 +4503,10 @@
         <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AB21" t="n">
         <v>8.800000000000001</v>
@@ -4527,7 +4527,7 @@
         <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
         <v>60</v>
@@ -4560,7 +4560,7 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AT21" t="n">
         <v>8</v>
@@ -4569,10 +4569,10 @@
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4584,7 +4584,7 @@
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>13.5</v>
+        <v>44</v>
       </c>
       <c r="BB21" t="n">
         <v>28</v>
@@ -4593,20 +4593,20 @@
         <v>25</v>
       </c>
       <c r="BD21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE21" t="n">
-        <v>13.5</v>
+        <v>70</v>
       </c>
       <c r="BF21" t="n">
         <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>11.5</v>
+        <v>26</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.28</v>
       </c>
       <c r="G22" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
         <v>3.75</v>
@@ -4649,7 +4649,7 @@
         <v>3.85</v>
       </c>
       <c r="J22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
         <v>3.4</v>
@@ -4682,7 +4682,7 @@
         <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V22" t="n">
         <v>1.35</v>
@@ -4691,82 +4691,82 @@
         <v>1.75</v>
       </c>
       <c r="X22" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y22" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA22" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
         <v>7.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG22" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH22" t="n">
         <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ22" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP22" t="n">
         <v>10</v>
       </c>
       <c r="AQ22" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
@@ -4775,10 +4775,10 @@
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BB22" t="n">
         <v>23</v>
@@ -4787,20 +4787,20 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="BE22" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BF22" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG22" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>2.02</v>
       </c>
       <c r="G23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H23" t="n">
         <v>4.7</v>
@@ -4843,7 +4843,7 @@
         <v>5.3</v>
       </c>
       <c r="J23" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K23" t="n">
         <v>3.25</v>
@@ -4945,7 +4945,7 @@
         <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS23" t="n">
         <v>42</v>
@@ -4957,7 +4957,7 @@
         <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW23" t="n">
         <v>38</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -5052,13 +5052,13 @@
         <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P24" t="n">
         <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
         <v>1.31</v>
@@ -5067,7 +5067,7 @@
         <v>3.95</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
         <v>1.95</v>
@@ -5082,7 +5082,7 @@
         <v>13</v>
       </c>
       <c r="Y24" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -5094,7 +5094,7 @@
         <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>21</v>
@@ -5118,7 +5118,7 @@
         <v>21</v>
       </c>
       <c r="AK24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL24" t="n">
         <v>42</v>
@@ -5130,7 +5130,7 @@
         <v>14.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
@@ -5139,7 +5139,7 @@
         <v>14</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS24" t="n">
         <v>40</v>
@@ -5175,7 +5175,7 @@
         <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BE24" t="n">
         <v>44</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G25" t="n">
         <v>1.64</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1.65</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
@@ -5231,7 +5231,7 @@
         <v>7.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -5252,43 +5252,43 @@
         <v>1.79</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X25" t="n">
         <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z25" t="n">
         <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AB25" t="n">
         <v>7</v>
       </c>
       <c r="AC25" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
         <v>28</v>
@@ -5297,7 +5297,7 @@
         <v>130</v>
       </c>
       <c r="AF25" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG25" t="n">
         <v>10.5</v>
@@ -5306,16 +5306,16 @@
         <v>27</v>
       </c>
       <c r="AI25" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AJ25" t="n">
         <v>15</v>
       </c>
       <c r="AK25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>210</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
         <v>190</v>
@@ -5330,22 +5330,22 @@
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
         <v>48</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW25" t="n">
         <v>40</v>
@@ -5369,7 +5369,7 @@
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
         <v>46</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -5413,19 +5413,19 @@
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J26" t="n">
         <v>1.04</v>
-      </c>
-      <c r="G26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J26" t="n">
-        <v>1.03</v>
       </c>
       <c r="K26" t="n">
         <v>950</v>
@@ -5437,7 +5437,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O26" t="n">
         <v>1.24</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -5625,7 +5625,7 @@
         <v>3.35</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="M27" t="n">
         <v>1.1</v>
@@ -5658,7 +5658,7 @@
         <v>1.47</v>
       </c>
       <c r="W27" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X27" t="n">
         <v>13.5</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
         <v>3.15</v>
       </c>
       <c r="K30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L30" t="n">
         <v>1.48</v>
@@ -6234,10 +6234,10 @@
         <v>2.08</v>
       </c>
       <c r="U30" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="V30" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="W30" t="n">
         <v>1.29</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G31" t="n">
         <v>2.02</v>
@@ -6398,7 +6398,7 @@
         <v>3.3</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.53</v>
@@ -6413,10 +6413,10 @@
         <v>1.47</v>
       </c>
       <c r="P31" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R31" t="n">
         <v>1.23</v>
@@ -6428,7 +6428,7 @@
         <v>2.12</v>
       </c>
       <c r="U31" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V31" t="n">
         <v>1.24</v>
@@ -6473,10 +6473,10 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>1000</v>
@@ -6518,10 +6518,10 @@
         <v>9.6</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>65</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
         <v>3.75</v>
       </c>
       <c r="T32" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U32" t="n">
         <v>1.94</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
         <v>2.16</v>
       </c>
       <c r="U33" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="V33" t="n">
         <v>1.17</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>
@@ -6965,10 +6965,10 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="G34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="H34" t="n">
         <v>13</v>
@@ -7004,7 +7004,7 @@
         <v>1.66</v>
       </c>
       <c r="S34" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="T34" t="n">
         <v>2.08</v>
@@ -7016,7 +7016,7 @@
         <v>1.06</v>
       </c>
       <c r="W34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="X34" t="n">
         <v>30</v>
@@ -7073,7 +7073,7 @@
         <v>340</v>
       </c>
       <c r="AP34" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ34" t="n">
         <v>7.4</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-31 17:00:46</t>
+          <t>2026-03-31 19:07:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G2" t="n">
         <v>5.7</v>
@@ -796,7 +796,7 @@
         <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T2" t="n">
         <v>2.34</v>
@@ -838,7 +838,7 @@
         <v>44</v>
       </c>
       <c r="AG2" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="AH2" t="n">
         <v>36</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -954,46 +954,46 @@
         <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="H3" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I3" t="n">
         <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M3" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="N3" t="n">
         <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="P3" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.96</v>
+        <v>2.76</v>
       </c>
       <c r="R3" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
         <v>6.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="U3" t="n">
         <v>1.53</v>
@@ -1002,7 +1002,7 @@
         <v>1.17</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1059,16 +1059,16 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="AT3" t="n">
         <v>4.1</v>
@@ -1077,44 +1077,44 @@
         <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.34</v>
+        <v>3.15</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="BA3" t="n">
-        <v>2</v>
+        <v>2.62</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.3</v>
+        <v>2.56</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.34</v>
+        <v>3.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.99</v>
+        <v>2.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.84</v>
+        <v>4.2</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1148,13 +1148,13 @@
         <v>1.57</v>
       </c>
       <c r="G4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
         <v>6.2</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J4" t="n">
         <v>3.1</v>
@@ -1163,7 +1163,7 @@
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.02</v>
@@ -1193,10 +1193,10 @@
         <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
@@ -1250,7 +1250,7 @@
         <v>28</v>
       </c>
       <c r="AO4" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP4" t="n">
         <v>4.2</v>
@@ -1262,7 +1262,7 @@
         <v>3.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AT4" t="n">
         <v>3.25</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
         <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H5" t="n">
         <v>2.9</v>
@@ -1390,7 +1390,7 @@
         <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X5" t="n">
         <v>30</v>
@@ -1402,7 +1402,7 @@
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
@@ -1429,7 +1429,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1480,7 +1480,7 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="BB5" t="n">
         <v>6.6</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
         <v>46</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>36</v>
@@ -1692,11 +1692,11 @@
         <v>16.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1727,25 +1727,25 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.46</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.48</v>
-      </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.5</v>
       </c>
-      <c r="K7" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1757,13 +1757,13 @@
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
         <v>3.6</v>
@@ -1775,28 +1775,28 @@
         <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y7" t="n">
         <v>13.5</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
         <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
@@ -1844,7 +1844,7 @@
         <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
@@ -1865,32 +1865,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.3</v>
@@ -1945,13 +1945,13 @@
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q8" t="n">
         <v>2.4</v>
@@ -1960,22 +1960,22 @@
         <v>1.23</v>
       </c>
       <c r="S8" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -1990,7 +1990,7 @@
         <v>7.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD8" t="n">
         <v>17.5</v>
@@ -2005,19 +2005,19 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
@@ -2041,25 +2041,25 @@
         <v>15</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AX8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY8" t="n">
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA8" t="n">
         <v>70</v>
@@ -2071,20 +2071,20 @@
         <v>24</v>
       </c>
       <c r="BD8" t="n">
-        <v>13.5</v>
+        <v>44</v>
       </c>
       <c r="BE8" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BF8" t="n">
         <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G9" t="n">
         <v>1.86</v>
       </c>
-      <c r="G9" t="n">
-        <v>1.88</v>
-      </c>
       <c r="H9" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I9" t="n">
         <v>5.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
         <v>1.46</v>
       </c>
       <c r="H10" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I10" t="n">
         <v>12.5</v>
@@ -2327,13 +2327,13 @@
         <v>5.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
@@ -2354,7 +2354,7 @@
         <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2363,10 +2363,10 @@
         <v>3.15</v>
       </c>
       <c r="X10" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="Z10" t="n">
         <v>130</v>
@@ -2381,7 +2381,7 @@
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="AE10" t="n">
         <v>290</v>
@@ -2417,69 +2417,69 @@
         <v>550</v>
       </c>
       <c r="AP10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY10" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AR10" t="n">
+      <c r="AZ10" t="n">
         <v>5.3</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="BA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD10" t="n">
         <v>5.5</v>
       </c>
-      <c r="AT10" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BE10" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Brazilian Campeonato Women</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,191 +2489,191 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>EC Bahia (W)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sporting Gijon</t>
+          <t>America MG (W)</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="G11" t="n">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>4.2</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="X11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>85</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>90</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>50</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AR11" t="n">
-        <v>14.5</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>15</v>
+        <v>1.41</v>
       </c>
       <c r="AT11" t="n">
-        <v>9.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>7.6</v>
+        <v>1.41</v>
       </c>
       <c r="AV11" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
-        <v>12</v>
+        <v>4.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.6</v>
+        <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>15.5</v>
+        <v>1.41</v>
       </c>
       <c r="BA11" t="n">
-        <v>23</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
-        <v>11.5</v>
+        <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>18.5</v>
+        <v>1.41</v>
       </c>
       <c r="BD11" t="n">
-        <v>29</v>
+        <v>1.41</v>
       </c>
       <c r="BE11" t="n">
-        <v>28</v>
+        <v>1.41</v>
       </c>
       <c r="BF11" t="n">
-        <v>11.5</v>
+        <v>1.51</v>
       </c>
       <c r="BG11" t="n">
-        <v>36</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,191 +2683,191 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bogota</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Real Soacha Cundinamarca FC</t>
+          <t>Sporting Gijon</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.54</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>2.84</v>
+        <v>2.04</v>
       </c>
       <c r="H12" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>2.46</v>
+        <v>4.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>2.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>3.15</v>
       </c>
       <c r="T12" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.78</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="X12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>17</v>
+      </c>
+      <c r="Z12" t="n">
         <v>90</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>40</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP12" t="n">
         <v>14</v>
       </c>
-      <c r="AD12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AQ12" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.55</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>2.32</v>
+        <v>15</v>
       </c>
       <c r="AT12" t="n">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>3.9</v>
+        <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>3.3</v>
+        <v>15</v>
       </c>
       <c r="AW12" t="n">
-        <v>2.38</v>
+        <v>14</v>
       </c>
       <c r="AX12" t="n">
-        <v>3.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.1</v>
+        <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>3.6</v>
+        <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>2.38</v>
+        <v>23</v>
       </c>
       <c r="BB12" t="n">
-        <v>2.38</v>
+        <v>11.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>2.32</v>
+        <v>10.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>2.38</v>
+        <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.44</v>
+        <v>28</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.3</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.32</v>
+        <v>14.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Bogota</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Real Soacha Cundinamarca FC</t>
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T13" t="n">
         <v>2.02</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="I13" t="n">
+      <c r="U13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X13" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ13" t="n">
         <v>4.6</v>
       </c>
-      <c r="J13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K13" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L13" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O13" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="X13" t="n">
-        <v>13</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>15</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>95</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>46</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>10</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>11.5</v>
-      </c>
       <c r="AR13" t="n">
-        <v>6.8</v>
+        <v>2.62</v>
       </c>
       <c r="AS13" t="n">
-        <v>7.8</v>
+        <v>2.42</v>
       </c>
       <c r="AT13" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.8</v>
+        <v>3.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>50</v>
+        <v>2.48</v>
       </c>
       <c r="AX13" t="n">
-        <v>10.5</v>
+        <v>2.96</v>
       </c>
       <c r="AY13" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>11.5</v>
+        <v>3.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>7.8</v>
+        <v>2.48</v>
       </c>
       <c r="BB13" t="n">
-        <v>11.5</v>
+        <v>2.38</v>
       </c>
       <c r="BC13" t="n">
-        <v>11.5</v>
+        <v>2.76</v>
       </c>
       <c r="BD13" t="n">
-        <v>7.4</v>
+        <v>2.42</v>
       </c>
       <c r="BE13" t="n">
-        <v>8</v>
+        <v>2.48</v>
       </c>
       <c r="BF13" t="n">
-        <v>17</v>
+        <v>2.38</v>
       </c>
       <c r="BG13" t="n">
-        <v>7.6</v>
+        <v>2.36</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Boyaca Patriotas</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Leones FC</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.51</v>
+        <v>2.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.6</v>
+        <v>2.16</v>
       </c>
       <c r="H14" t="n">
+        <v>4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="X14" t="n">
+        <v>13</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>46</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU14" t="n">
         <v>6.8</v>
       </c>
-      <c r="I14" t="n">
-        <v>11</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N14" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="X14" t="n">
-        <v>970</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>95</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>970</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV14" t="n">
-        <v>4.2</v>
+        <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>5.1</v>
+        <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>2.68</v>
+        <v>11.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB14" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BC14" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.78</v>
+        <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>2.02</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.8</v>
+        <v>17</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.2</v>
+        <v>8.6</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,191 +3265,191 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>18:10:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Alianza FC Valledupar</t>
+          <t>Boyaca Patriotas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Deportivo Pasto</t>
+          <t>Leones FC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.88</v>
+        <v>1.39</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>1.48</v>
       </c>
       <c r="H15" t="n">
-        <v>2.86</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>3.1</v>
+        <v>13.5</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>6.4</v>
       </c>
       <c r="L15" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="M15" t="n">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>2.48</v>
+        <v>3.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.59</v>
+        <v>1.29</v>
       </c>
       <c r="P15" t="n">
-        <v>1.49</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.78</v>
+        <v>1.98</v>
       </c>
       <c r="R15" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>32</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>120</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC15" t="n">
         <v>6</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="X15" t="n">
-        <v>8</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>370</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>340</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>190</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>370</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU15" t="n">
+      <c r="BD15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BF15" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG15" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,117 +3459,117 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:10:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rubio Nu</t>
+          <t>Alianza FC Valledupar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Guarani (Par)</t>
+          <t>Deportivo Pasto</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.55</v>
+        <v>2.86</v>
       </c>
       <c r="G16" t="n">
-        <v>4.6</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.02</v>
+        <v>2.86</v>
       </c>
       <c r="I16" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="N16" t="n">
         <v>2.48</v>
       </c>
-      <c r="K16" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="M16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.42</v>
-      </c>
       <c r="O16" t="n">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="S16" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>1.98</v>
+        <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V16" t="n">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA16" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF16" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG16" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AK16" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AL16" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3581,69 +3581,69 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,184 +3653,184 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Atletico GO</t>
+          <t>Rubio Nu</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Nautico PE</t>
+          <t>Guarani (Par)</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.04</v>
+        <v>3.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.08</v>
+        <v>4.6</v>
       </c>
       <c r="H17" t="n">
-        <v>4.3</v>
+        <v>2.22</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>2.48</v>
       </c>
       <c r="J17" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="K17" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
         <v>1.57</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -3852,179 +3852,179 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Atletico GO</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Goias</t>
+          <t>Nautico PE</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.52</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.64</v>
+        <v>2.08</v>
       </c>
       <c r="H18" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.6</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="L18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -4058,10 +4058,10 @@
         <v>1.89</v>
       </c>
       <c r="G19" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
         <v>5.4</v>
@@ -4106,7 +4106,7 @@
         <v>1.23</v>
       </c>
       <c r="W19" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X19" t="n">
         <v>10.5</v>
@@ -4124,7 +4124,7 @@
         <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>55</v>
@@ -4160,7 +4160,7 @@
         <v>55</v>
       </c>
       <c r="AO19" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AP19" t="n">
         <v>9.199999999999999</v>
@@ -4169,10 +4169,10 @@
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4184,7 +4184,7 @@
         <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AX19" t="n">
         <v>9.199999999999999</v>
@@ -4196,7 +4196,7 @@
         <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BB19" t="n">
         <v>10.5</v>
@@ -4205,27 +4205,27 @@
         <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF19" t="n">
         <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brazilian Campeonato Women</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,179 +4240,179 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EC Bahia (W)</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>America MG (W)</t>
+          <t>Goias</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.17</v>
+        <v>2.54</v>
       </c>
       <c r="G20" t="n">
-        <v>1.67</v>
+        <v>2.66</v>
       </c>
       <c r="H20" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>1000</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
-        <v>3.9</v>
+        <v>2.94</v>
       </c>
       <c r="K20" t="n">
-        <v>950</v>
+        <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>1.29</v>
+        <v>3.05</v>
       </c>
       <c r="O20" t="n">
-        <v>1.16</v>
+        <v>1.4</v>
       </c>
       <c r="P20" t="n">
-        <v>1.29</v>
+        <v>1.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.16</v>
+        <v>2.26</v>
       </c>
       <c r="R20" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>1.16</v>
+        <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.03</v>
+        <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.6</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ20" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>4.2</v>
+        <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.56</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.56</v>
+        <v>6.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>4.2</v>
+        <v>38</v>
       </c>
       <c r="AX20" t="n">
-        <v>4.4</v>
+        <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.44</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.56</v>
+        <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.49</v>
+        <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.56</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.51</v>
+        <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.56</v>
+        <v>8.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -4449,16 +4449,16 @@
         <v>2.4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J21" t="n">
         <v>3.45</v>
       </c>
       <c r="K21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
         <v>1.47</v>
@@ -4467,31 +4467,31 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S21" t="n">
         <v>4.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W21" t="n">
         <v>1.71</v>
@@ -4506,7 +4506,7 @@
         <v>22</v>
       </c>
       <c r="AA21" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AB21" t="n">
         <v>8.800000000000001</v>
@@ -4521,13 +4521,13 @@
         <v>46</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
         <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI21" t="n">
         <v>60</v>
@@ -4551,7 +4551,7 @@
         <v>50</v>
       </c>
       <c r="AP21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ21" t="n">
         <v>10.5</v>
@@ -4563,13 +4563,13 @@
         <v>42</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW21" t="n">
         <v>29</v>
@@ -4581,10 +4581,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BB21" t="n">
         <v>28</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I22" t="n">
         <v>3.85</v>
@@ -4652,10 +4652,10 @@
         <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4676,19 +4676,19 @@
         <v>1.28</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4712,7 +4712,7 @@
         <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF22" t="n">
         <v>14</v>
@@ -4724,7 +4724,7 @@
         <v>20</v>
       </c>
       <c r="AI22" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AJ22" t="n">
         <v>32</v>
@@ -4733,7 +4733,7 @@
         <v>28</v>
       </c>
       <c r="AL22" t="n">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>130</v>
@@ -4766,7 +4766,7 @@
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
@@ -4787,7 +4787,7 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="BE22" t="n">
         <v>29</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -4840,13 +4840,13 @@
         <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L23" t="n">
         <v>1.53</v>
@@ -4891,10 +4891,10 @@
         <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB23" t="n">
         <v>6.2</v>
@@ -4903,7 +4903,7 @@
         <v>7.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4936,7 +4936,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4945,7 +4945,7 @@
         <v>10</v>
       </c>
       <c r="AR23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS23" t="n">
         <v>42</v>
@@ -4957,7 +4957,7 @@
         <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AW23" t="n">
         <v>38</v>
@@ -4975,13 +4975,13 @@
         <v>44</v>
       </c>
       <c r="BB23" t="n">
-        <v>16.5</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
         <v>26</v>
       </c>
       <c r="BD23" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE23" t="n">
         <v>95</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G24" t="n">
         <v>1.9</v>
       </c>
       <c r="H24" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I24" t="n">
         <v>5.2</v>
@@ -5040,10 +5040,10 @@
         <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L24" t="n">
-        <v>1.37</v>
+        <v>1.46</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
@@ -5058,7 +5058,7 @@
         <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
         <v>1.31</v>
@@ -5067,10 +5067,10 @@
         <v>3.95</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U24" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
         <v>1.24</v>
@@ -5082,13 +5082,13 @@
         <v>13</v>
       </c>
       <c r="Y24" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
         <v>8</v>
@@ -5112,7 +5112,7 @@
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AJ24" t="n">
         <v>21</v>
@@ -5136,7 +5136,7 @@
         <v>11.5</v>
       </c>
       <c r="AQ24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR24" t="n">
         <v>22</v>
@@ -5145,13 +5145,13 @@
         <v>40</v>
       </c>
       <c r="AT24" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU24" t="n">
         <v>7.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW24" t="n">
         <v>32</v>
@@ -5163,10 +5163,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="BB24" t="n">
         <v>18</v>
@@ -5178,7 +5178,7 @@
         <v>25</v>
       </c>
       <c r="BE24" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BF24" t="n">
         <v>13</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -5231,7 +5231,7 @@
         <v>7.4</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K25" t="n">
         <v>4.1</v>
@@ -5249,16 +5249,16 @@
         <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
         <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
         <v>2.16</v>
@@ -5315,7 +5315,7 @@
         <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>200</v>
       </c>
       <c r="AM25" t="n">
         <v>190</v>
@@ -5339,13 +5339,13 @@
         <v>48</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU25" t="n">
         <v>8.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>40</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Honduras Liga Nacional</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>20:15:00</t>
+          <t>20:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Atletico Choloma</t>
+          <t>Coritiba</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Platense FC</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.3</v>
+        <v>2.66</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.76</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3</v>
+        <v>2.96</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
-        <v>1.04</v>
+        <v>3.25</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>3.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M26" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.24</v>
+        <v>2.26</v>
       </c>
       <c r="R26" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>1.24</v>
+        <v>4.5</v>
       </c>
       <c r="T26" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="V26" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="W26" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="X26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AF26" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL26" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN26" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO26" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AT26" t="n">
-        <v>1.03</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,186 +5598,186 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Coritiba</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.66</v>
+        <v>1.65</v>
       </c>
       <c r="G27" t="n">
-        <v>2.78</v>
+        <v>1.68</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="J27" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="O27" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.28</v>
+        <v>1.98</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="S27" t="n">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="U27" t="n">
-        <v>1.97</v>
+        <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>1.47</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>1.57</v>
+        <v>2.46</v>
       </c>
       <c r="X27" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="Y27" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG27" t="n">
         <v>10.5</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AH27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>17</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV27" t="n">
         <v>21</v>
       </c>
-      <c r="AA27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB27" t="n">
+      <c r="AW27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>14</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>16</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>8</v>
+      </c>
+      <c r="BE27" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AC27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>42</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>36</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ27" t="n">
+      <c r="BF27" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AR27" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>25</v>
-      </c>
       <c r="BG27" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5792,186 +5792,186 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Olimpia</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.65</v>
+        <v>3.95</v>
       </c>
       <c r="G28" t="n">
-        <v>1.68</v>
+        <v>6.2</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>1.66</v>
       </c>
       <c r="I28" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="K28" t="n">
         <v>7</v>
       </c>
-      <c r="J28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K28" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L28" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="O28" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="P28" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R28" t="n">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>1.72</v>
       </c>
       <c r="V28" t="n">
-        <v>1.16</v>
+        <v>1.8</v>
       </c>
       <c r="W28" t="n">
-        <v>2.46</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
         <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,191 +5981,191 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olimpia</t>
+          <t>Ceara SC Fortaleza</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="L29" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>1.9</v>
+        <v>2.74</v>
       </c>
       <c r="O29" t="n">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="P29" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.9</v>
+        <v>2.46</v>
       </c>
       <c r="R29" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>1.05</v>
+        <v>5.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V29" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="W29" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Brazilian Serie A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Fluminense</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ceara SC Fortaleza</t>
+          <t>Corinthians</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>3.9</v>
+        <v>1.95</v>
       </c>
       <c r="G30" t="n">
-        <v>4.4</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S30" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T30" t="n">
         <v>2.12</v>
       </c>
-      <c r="I30" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U30" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="V30" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA30" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="AB30" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ30" t="n">
         <v>12</v>
       </c>
-      <c r="AE30" t="n">
-        <v>34</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>80</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>120</v>
-      </c>
-      <c r="AO30" t="n">
+      <c r="AR30" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>48</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>17</v>
+      </c>
+      <c r="BD30" t="n">
         <v>29</v>
       </c>
-      <c r="AP30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC30" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>7</v>
-      </c>
       <c r="BE30" t="n">
-        <v>7.2</v>
+        <v>46</v>
       </c>
       <c r="BF30" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Brazilian Serie A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Fluminense</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Corinthians</t>
+          <t>Avai</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="G31" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="H31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>46</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR31" t="n">
         <v>4.7</v>
       </c>
-      <c r="I31" t="n">
+      <c r="AS31" t="n">
         <v>5.1</v>
       </c>
-      <c r="J31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="X31" t="n">
+      <c r="AT31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BF31" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y31" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>27</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>34</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>16</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF31" t="n">
-        <v>14.5</v>
-      </c>
       <c r="BG31" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
@@ -6568,186 +6568,186 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Criciuma</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Avai</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="G32" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="H32" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="I32" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M32" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
-        <v>1.81</v>
+        <v>1.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="S32" t="n">
-        <v>3.75</v>
+        <v>4.4</v>
       </c>
       <c r="T32" t="n">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>1.94</v>
+        <v>1.71</v>
       </c>
       <c r="V32" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="W32" t="n">
-        <v>2.08</v>
+        <v>2.24</v>
       </c>
       <c r="X32" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
         <v>18.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="AA32" t="n">
-        <v>150</v>
+        <v>240</v>
       </c>
       <c r="AB32" t="n">
-        <v>9.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC32" t="n">
         <v>9.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AE32" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AF32" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG32" t="n">
         <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AI32" t="n">
-        <v>90</v>
+        <v>140</v>
       </c>
       <c r="AJ32" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK32" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AL32" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM32" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="AN32" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AR32" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>4.7</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="BA32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD32" t="n">
         <v>5.1</v>
       </c>
-      <c r="AT32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BE32" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BG32" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,191 +6757,191 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>21:30:00</t>
+          <t>22:30:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>Atletico Nacional Medellin</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.7</v>
+        <v>1.24</v>
       </c>
       <c r="G33" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13</v>
+      </c>
+      <c r="I33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="K33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U33" t="n">
         <v>1.79</v>
       </c>
-      <c r="H33" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="I33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W33" t="n">
         <v>4.4</v>
       </c>
-      <c r="T33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.24</v>
-      </c>
       <c r="X33" t="n">
+        <v>30</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>50</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>170</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
         <v>11</v>
       </c>
-      <c r="Y33" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>240</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AC33" t="n">
-        <v>9.6</v>
+        <v>16.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="AE33" t="n">
-        <v>140</v>
+        <v>280</v>
       </c>
       <c r="AF33" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG33" t="n">
         <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI33" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="AJ33" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="AK33" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="AL33" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AM33" t="n">
-        <v>230</v>
+        <v>200</v>
       </c>
       <c r="AN33" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>340</v>
       </c>
       <c r="AP33" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT33" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU33" t="n">
+        <v>13</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AX33" t="n">
         <v>7.2</v>
       </c>
-      <c r="AV33" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>7.8</v>
-      </c>
       <c r="AY33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="BB33" t="n">
-        <v>15.5</v>
+        <v>8.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>18.5</v>
+        <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="BF33" t="n">
-        <v>12</v>
+        <v>3.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Honduras Liga Nacional</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6956,179 +6956,179 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Atletico Nacional Medellin</t>
+          <t>Atletico Choloma</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Platense FC</t>
         </is>
       </c>
       <c r="F34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K34" t="n">
+        <v>950</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O34" t="n">
         <v>1.24</v>
       </c>
-      <c r="G34" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="H34" t="n">
-        <v>13</v>
-      </c>
-      <c r="I34" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="J34" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="K34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N34" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O34" t="n">
-        <v>1.17</v>
-      </c>
       <c r="P34" t="n">
-        <v>2.64</v>
+        <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.51</v>
+        <v>1.23</v>
       </c>
       <c r="R34" t="n">
-        <v>1.66</v>
+        <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>2.26</v>
+        <v>1.24</v>
       </c>
       <c r="T34" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U34" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V34" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W34" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="X34" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="Y34" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="Z34" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AA34" t="n">
         <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AC34" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD34" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE34" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG34" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH34" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI34" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AK34" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AL34" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ34" t="n">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR34" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AS34" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AT34" t="n">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AU34" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AV34" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AX34" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AY34" t="n">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AZ34" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BB34" t="n">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="BC34" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="BE34" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="BF34" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-31 19:07:55</t>
+          <t>2026-03-31 21:14:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,46 +757,46 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
         <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="I2" t="n">
         <v>2.08</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="M2" t="n">
         <v>1.13</v>
       </c>
       <c r="N2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="P2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="R2" t="n">
         <v>1.16</v>
       </c>
       <c r="S2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.34</v>
@@ -814,13 +814,13 @@
         <v>7.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB2" t="n">
         <v>12.5</v>
@@ -832,19 +832,19 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
         <v>44</v>
       </c>
       <c r="AG2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH2" t="n">
         <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AJ2" t="n">
         <v>190</v>
@@ -868,7 +868,7 @@
         <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AR2" t="n">
         <v>9</v>
@@ -886,7 +886,7 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
         <v>28</v>
@@ -895,32 +895,32 @@
         <v>20</v>
       </c>
       <c r="AZ2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>9.4</v>
+        <v>12.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>9.6</v>
+        <v>13</v>
       </c>
       <c r="BE2" t="n">
+        <v>14</v>
+      </c>
+      <c r="BF2" t="n">
         <v>10</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="BG2" t="n">
         <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -969,7 +969,7 @@
         <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.56</v>
+        <v>1.01</v>
       </c>
       <c r="M3" t="n">
         <v>1.15</v>
@@ -996,7 +996,7 @@
         <v>2.58</v>
       </c>
       <c r="U3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="V3" t="n">
         <v>1.17</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H4" t="n">
         <v>6.2</v>
@@ -1169,7 +1169,7 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
         <v>1.45</v>
@@ -1196,7 +1196,7 @@
         <v>1.1</v>
       </c>
       <c r="W4" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
         <v>10.5</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="G5" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
         <v>1.31</v>
@@ -1363,7 +1363,7 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O5" t="n">
         <v>1.27</v>
@@ -1375,7 +1375,7 @@
         <v>1.74</v>
       </c>
       <c r="R5" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S5" t="n">
         <v>3.05</v>
@@ -1387,13 +1387,13 @@
         <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="W5" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="X5" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1429,7 +1429,7 @@
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
         <v>1000</v>
@@ -1450,28 +1450,28 @@
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY5" t="n">
         <v>8.6</v>
@@ -1480,10 +1480,10 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
         <v>6.4</v>
@@ -1492,7 +1492,7 @@
         <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
         <v>2.28</v>
@@ -1551,7 +1551,7 @@
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1727,25 +1727,25 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
         <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
@@ -1778,7 +1778,7 @@
         <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X7" t="n">
         <v>14</v>
@@ -1790,7 +1790,7 @@
         <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
         <v>10.5</v>
@@ -1802,10 +1802,10 @@
         <v>13.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF7" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
@@ -1835,7 +1835,7 @@
         <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11.5</v>
@@ -1844,7 +1844,7 @@
         <v>19</v>
       </c>
       <c r="AS7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AT7" t="n">
         <v>9.6</v>
@@ -1868,7 +1868,7 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
@@ -1877,20 +1877,20 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BF7" t="n">
         <v>19.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.18</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
         <v>4</v>
@@ -1951,28 +1951,28 @@
         <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
         <v>2.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
         <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="V8" t="n">
         <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="X8" t="n">
         <v>10.5</v>
@@ -2005,7 +2005,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
@@ -2017,7 +2017,7 @@
         <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AM8" t="n">
         <v>580</v>
@@ -2050,7 +2050,7 @@
         <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2062,16 +2062,16 @@
         <v>19.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>70</v>
+        <v>14.5</v>
       </c>
       <c r="BB8" t="n">
         <v>24</v>
       </c>
       <c r="BC8" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="BD8" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="BE8" t="n">
         <v>18</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="H9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K9" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2148,7 +2148,7 @@
         <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         <v>12</v>
       </c>
       <c r="AD10" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AE10" t="n">
         <v>290</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>1.63</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I11" t="n">
         <v>1000</v>
@@ -2527,19 +2527,19 @@
         <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
         <v>1.16</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
         <v>1.94</v>
@@ -2620,7 +2620,7 @@
         <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.41</v>
+        <v>4.2</v>
       </c>
       <c r="AT11" t="n">
         <v>5.6</v>
@@ -2662,11 +2662,11 @@
         <v>1.51</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>4.2</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2706,13 +2706,13 @@
         <v>4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.32</v>
@@ -2733,7 +2733,7 @@
         <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S12" t="n">
         <v>3.15</v>
@@ -2742,10 +2742,10 @@
         <v>1.75</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
         <v>1.96</v>
@@ -2757,10 +2757,10 @@
         <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>85</v>
+        <v>500</v>
       </c>
       <c r="AB12" t="n">
         <v>10.5</v>
@@ -2799,7 +2799,7 @@
         <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO12" t="n">
         <v>46</v>
@@ -2817,13 +2817,13 @@
         <v>15</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
         <v>7.6</v>
       </c>
       <c r="AV12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AW12" t="n">
         <v>14</v>
@@ -2856,11 +2856,11 @@
         <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G13" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="H13" t="n">
         <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="J13" t="n">
         <v>2.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>1.11</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>2.18</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="P13" t="n">
         <v>1.41</v>
@@ -2927,22 +2927,22 @@
         <v>2.32</v>
       </c>
       <c r="R13" t="n">
-        <v>1.16</v>
+        <v>1.13</v>
       </c>
       <c r="S13" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="T13" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X13" t="n">
         <v>90</v>
@@ -3005,10 +3005,10 @@
         <v>4.6</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="AS13" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="AT13" t="n">
         <v>4.2</v>
@@ -3017,44 +3017,44 @@
         <v>3.9</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AW13" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="AY13" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="BA13" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="BB13" t="n">
         <v>2.38</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3097,40 +3097,40 @@
         <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>1.47</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R14" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
         <v>1.29</v>
@@ -3139,10 +3139,10 @@
         <v>1.86</v>
       </c>
       <c r="X14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y14" t="n">
         <v>13</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>15.5</v>
       </c>
       <c r="Z14" t="n">
         <v>500</v>
@@ -3154,7 +3154,7 @@
         <v>7.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>30</v>
@@ -3193,16 +3193,16 @@
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AQ14" t="n">
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -3214,7 +3214,7 @@
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3223,10 +3223,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BB14" t="n">
         <v>22</v>
@@ -3235,20 +3235,20 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>17</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG14" t="n">
-        <v>8.6</v>
+        <v>11.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
         <v>13.5</v>
@@ -3294,7 +3294,7 @@
         <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>6.4</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.33</v>
@@ -3321,7 +3321,7 @@
         <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
@@ -3330,13 +3330,13 @@
         <v>1.09</v>
       </c>
       <c r="W15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>32</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
         <v>110</v>
@@ -3351,7 +3351,7 @@
         <v>970</v>
       </c>
       <c r="AD15" t="n">
-        <v>120</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
         <v>1000</v>
@@ -3363,7 +3363,7 @@
         <v>36</v>
       </c>
       <c r="AH15" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="I16" t="n">
         <v>3.1</v>
@@ -3545,7 +3545,7 @@
         <v>8</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE16" t="n">
         <v>190</v>
@@ -3590,7 +3590,7 @@
         <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -3602,7 +3602,7 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX16" t="n">
         <v>15.5</v>
@@ -3614,29 +3614,29 @@
         <v>22</v>
       </c>
       <c r="BA16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB16" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB16" t="n">
+      <c r="BC16" t="n">
         <v>9</v>
       </c>
-      <c r="BC16" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BD16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE16" t="n">
         <v>10</v>
       </c>
       <c r="BF16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG16" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
         <v>1.19</v>
       </c>
       <c r="S17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T17" t="n">
         <v>1.94</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>2.08</v>
       </c>
       <c r="H18" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
         <v>4.9</v>
@@ -3876,7 +3876,7 @@
         <v>3.15</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>1.96</v>
       </c>
       <c r="H19" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
         <v>5.4</v>
@@ -4076,28 +4076,28 @@
         <v>1.52</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P19" t="n">
         <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
         <v>4.7</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
@@ -4109,7 +4109,7 @@
         <v>2.04</v>
       </c>
       <c r="X19" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19" t="n">
         <v>28</v>
@@ -4163,16 +4163,16 @@
         <v>700</v>
       </c>
       <c r="AP19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
         <v>11.5</v>
       </c>
       <c r="AR19" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4181,10 +4181,10 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX19" t="n">
         <v>9.199999999999999</v>
@@ -4196,7 +4196,7 @@
         <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB19" t="n">
         <v>10.5</v>
@@ -4205,20 +4205,20 @@
         <v>11.5</v>
       </c>
       <c r="BD19" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF19" t="n">
         <v>14</v>
       </c>
       <c r="BG19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>2.54</v>
       </c>
       <c r="G20" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H20" t="n">
         <v>3.45</v>
@@ -4273,13 +4273,13 @@
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q20" t="n">
         <v>2.26</v>
@@ -4291,7 +4291,7 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
@@ -4300,10 +4300,10 @@
         <v>1.38</v>
       </c>
       <c r="W20" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y20" t="n">
         <v>11.5</v>
@@ -4357,16 +4357,16 @@
         <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR20" t="n">
         <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AT20" t="n">
         <v>8.199999999999999</v>
@@ -4378,7 +4378,7 @@
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>38</v>
+        <v>7.6</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
@@ -4390,10 +4390,10 @@
         <v>13.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BC20" t="n">
         <v>14.5</v>
@@ -4402,17 +4402,17 @@
         <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BG20" t="n">
         <v>8.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -4446,16 +4446,16 @@
         <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
         <v>3.45</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
         <v>3.55</v>
@@ -4494,7 +4494,7 @@
         <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X21" t="n">
         <v>12</v>
@@ -4512,7 +4512,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
         <v>14.5</v>
@@ -4533,7 +4533,7 @@
         <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -4569,7 +4569,7 @@
         <v>7</v>
       </c>
       <c r="AV21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
         <v>29</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.36</v>
       </c>
       <c r="H22" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
         <v>3.85</v>
@@ -4661,34 +4661,34 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
         <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
         <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
         <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V22" t="n">
         <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4706,7 +4706,7 @@
         <v>9</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
         <v>15.5</v>
@@ -4715,7 +4715,7 @@
         <v>50</v>
       </c>
       <c r="AF22" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG22" t="n">
         <v>11.5</v>
@@ -4739,7 +4739,7 @@
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
         <v>60</v>
@@ -4754,10 +4754,10 @@
         <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU22" t="n">
         <v>6.8</v>
@@ -4772,13 +4772,13 @@
         <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="BB22" t="n">
         <v>23</v>
@@ -4787,20 +4787,20 @@
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BE22" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="BF22" t="n">
         <v>20</v>
       </c>
       <c r="BG22" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -4891,7 +4891,7 @@
         <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="AA23" t="n">
         <v>180</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G24" t="n">
         <v>1.9</v>
@@ -5034,7 +5034,7 @@
         <v>4.8</v>
       </c>
       <c r="I24" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J24" t="n">
         <v>3.65</v>
@@ -5076,7 +5076,7 @@
         <v>1.24</v>
       </c>
       <c r="W24" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="X24" t="n">
         <v>13</v>
@@ -5139,7 +5139,7 @@
         <v>13.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AS24" t="n">
         <v>40</v>
@@ -5154,7 +5154,7 @@
         <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AX24" t="n">
         <v>9.6</v>
@@ -5166,7 +5166,7 @@
         <v>17.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="BB24" t="n">
         <v>18</v>
@@ -5175,7 +5175,7 @@
         <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BE24" t="n">
         <v>42</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
@@ -5231,10 +5231,10 @@
         <v>7.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L25" t="n">
         <v>1.45</v>
@@ -5249,16 +5249,16 @@
         <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q25" t="n">
         <v>2.14</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
         <v>2.16</v>
@@ -5270,7 +5270,7 @@
         <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X25" t="n">
         <v>12.5</v>
@@ -5303,7 +5303,7 @@
         <v>10.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
         <v>140</v>
@@ -5315,10 +5315,10 @@
         <v>19</v>
       </c>
       <c r="AL25" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM25" t="n">
         <v>200</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>190</v>
       </c>
       <c r="AN25" t="n">
         <v>11.5</v>
@@ -5330,7 +5330,7 @@
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>28</v>
@@ -5339,7 +5339,7 @@
         <v>48</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU25" t="n">
         <v>8.4</v>
@@ -5369,7 +5369,7 @@
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE25" t="n">
         <v>46</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>2.76</v>
       </c>
       <c r="H26" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>3.1</v>
@@ -5434,7 +5434,7 @@
         <v>1.49</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
         <v>3</v>
@@ -5452,19 +5452,19 @@
         <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T26" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="U26" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V26" t="n">
         <v>1.47</v>
       </c>
       <c r="W26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X26" t="n">
         <v>13.5</v>
@@ -5560,7 +5560,7 @@
         <v>7.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>7.2</v>
+        <v>28</v>
       </c>
       <c r="BD26" t="n">
         <v>7.6</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>1.65</v>
       </c>
       <c r="G27" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="H27" t="n">
         <v>6</v>
@@ -5622,7 +5622,7 @@
         <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
         <v>1.41</v>
@@ -5637,16 +5637,16 @@
         <v>1.34</v>
       </c>
       <c r="P27" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R27" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
         <v>1.97</v>
@@ -5655,10 +5655,10 @@
         <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="X27" t="n">
         <v>16</v>
@@ -5691,7 +5691,7 @@
         <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
         <v>110</v>
@@ -5700,7 +5700,7 @@
         <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>42</v>
@@ -5721,10 +5721,10 @@
         <v>16.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AS27" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
@@ -5736,7 +5736,7 @@
         <v>21</v>
       </c>
       <c r="AW27" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AX27" t="n">
         <v>8.199999999999999</v>
@@ -5745,10 +5745,10 @@
         <v>8.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5757,20 +5757,20 @@
         <v>16</v>
       </c>
       <c r="BD27" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF27" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BG27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -5804,19 +5804,19 @@
         <v>3.95</v>
       </c>
       <c r="G28" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="H28" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="I28" t="n">
         <v>2.24</v>
       </c>
       <c r="J28" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>950</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5825,7 +5825,7 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
         <v>1.37</v>
@@ -5834,25 +5834,25 @@
         <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="V28" t="n">
         <v>1.8</v>
       </c>
       <c r="W28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5909,62 +5909,62 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AV28" t="n">
         <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -6001,16 +6001,16 @@
         <v>4.3</v>
       </c>
       <c r="H29" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I29" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L29" t="n">
         <v>1.53</v>
@@ -6019,7 +6019,7 @@
         <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
         <v>1.51</v>
@@ -6043,7 +6043,7 @@
         <v>1.76</v>
       </c>
       <c r="V29" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="W29" t="n">
         <v>1.3</v>
@@ -6052,16 +6052,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="Z29" t="n">
         <v>13</v>
       </c>
       <c r="AA29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
@@ -6070,7 +6070,7 @@
         <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF29" t="n">
         <v>30</v>
@@ -6079,10 +6079,10 @@
         <v>18.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AI29" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ29" t="n">
         <v>120</v>
@@ -6103,7 +6103,7 @@
         <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29" t="n">
         <v>6.2</v>
@@ -6112,7 +6112,7 @@
         <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT29" t="n">
         <v>9.800000000000001</v>
@@ -6124,10 +6124,10 @@
         <v>9.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY29" t="n">
         <v>15</v>
@@ -6136,29 +6136,29 @@
         <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB29" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BD29" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF29" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="BG29" t="n">
         <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -6204,7 +6204,7 @@
         <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L30" t="n">
         <v>1.53</v>
@@ -6216,7 +6216,7 @@
         <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P30" t="n">
         <v>1.65</v>
@@ -6225,7 +6225,7 @@
         <v>2.44</v>
       </c>
       <c r="R30" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S30" t="n">
         <v>4.8</v>
@@ -6237,7 +6237,7 @@
         <v>1.82</v>
       </c>
       <c r="V30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W30" t="n">
         <v>2</v>
@@ -6246,7 +6246,7 @@
         <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
@@ -6267,7 +6267,7 @@
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
@@ -6297,13 +6297,13 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS30" t="n">
         <v>40</v>
@@ -6330,7 +6330,7 @@
         <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="BB30" t="n">
         <v>16</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G31" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="H31" t="n">
         <v>4.9</v>
@@ -6395,10 +6395,10 @@
         <v>5.5</v>
       </c>
       <c r="J31" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L31" t="n">
         <v>1.38</v>
@@ -6407,13 +6407,13 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q31" t="n">
         <v>2.06</v>
@@ -6425,10 +6425,10 @@
         <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U31" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V31" t="n">
         <v>1.22</v>
@@ -6437,7 +6437,7 @@
         <v>2.08</v>
       </c>
       <c r="X31" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y31" t="n">
         <v>18.5</v>
@@ -6458,7 +6458,7 @@
         <v>24</v>
       </c>
       <c r="AE31" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AF31" t="n">
         <v>12.5</v>
@@ -6491,16 +6491,16 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ31" t="n">
         <v>12.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT31" t="n">
         <v>7</v>
@@ -6512,7 +6512,7 @@
         <v>15.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX31" t="n">
         <v>9.4</v>
@@ -6524,29 +6524,29 @@
         <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB31" t="n">
         <v>17.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF31" t="n">
         <v>10.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -6586,22 +6586,22 @@
         <v>5.8</v>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K32" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O32" t="n">
         <v>1.45</v>
@@ -6613,10 +6613,10 @@
         <v>2.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T32" t="n">
         <v>2.16</v>
@@ -6628,10 +6628,10 @@
         <v>1.17</v>
       </c>
       <c r="W32" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X32" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y32" t="n">
         <v>18.5</v>
@@ -6691,10 +6691,10 @@
         <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AT32" t="n">
         <v>5.7</v>
@@ -6706,7 +6706,7 @@
         <v>21</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX32" t="n">
         <v>7.8</v>
@@ -6715,10 +6715,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BB32" t="n">
         <v>15.5</v>
@@ -6727,20 +6727,20 @@
         <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF32" t="n">
         <v>12</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -6774,13 +6774,13 @@
         <v>1.24</v>
       </c>
       <c r="G33" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="H33" t="n">
         <v>13</v>
       </c>
       <c r="I33" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="J33" t="n">
         <v>6.6</v>
@@ -6822,13 +6822,13 @@
         <v>1.06</v>
       </c>
       <c r="W33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X33" t="n">
-        <v>30</v>
+        <v>950</v>
       </c>
       <c r="Y33" t="n">
-        <v>50</v>
+        <v>950</v>
       </c>
       <c r="Z33" t="n">
         <v>170</v>
@@ -6843,7 +6843,7 @@
         <v>16.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>55</v>
+        <v>950</v>
       </c>
       <c r="AE33" t="n">
         <v>280</v>
@@ -6855,7 +6855,7 @@
         <v>12</v>
       </c>
       <c r="AH33" t="n">
-        <v>36</v>
+        <v>950</v>
       </c>
       <c r="AI33" t="n">
         <v>200</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>
@@ -7073,52 +7073,52 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF34" t="n">
         <v>1.01</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-31 21:14:52</t>
+          <t>2026-03-31 23:21:19</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,40 +757,40 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="I2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
         <v>3.3</v>
       </c>
       <c r="L2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O2" t="n">
         <v>1.63</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.6</v>
       </c>
       <c r="P2" t="n">
         <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="R2" t="n">
         <v>1.16</v>
@@ -802,16 +802,16 @@
         <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V2" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Y2" t="n">
         <v>6.2</v>
@@ -820,7 +820,7 @@
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AB2" t="n">
         <v>12.5</v>
@@ -832,10 +832,10 @@
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AF2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
         <v>24</v>
@@ -850,7 +850,7 @@
         <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
         <v>450</v>
@@ -862,7 +862,7 @@
         <v>240</v>
       </c>
       <c r="AO2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AP2" t="n">
         <v>6.8</v>
@@ -874,7 +874,7 @@
         <v>9</v>
       </c>
       <c r="AS2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AT2" t="n">
         <v>11</v>
@@ -886,10 +886,10 @@
         <v>10.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AY2" t="n">
         <v>20</v>
@@ -898,29 +898,29 @@
         <v>25</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.800000000000001</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BE2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BF2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG2" t="n">
         <v>20</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -954,43 +954,43 @@
         <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H3" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I3" t="n">
         <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
         <v>3.35</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="M3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
         <v>1.68</v>
       </c>
       <c r="P3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.76</v>
+        <v>3.05</v>
       </c>
       <c r="R3" t="n">
         <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
         <v>2.58</v>
@@ -999,10 +999,10 @@
         <v>1.54</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AC3" t="n">
         <v>42</v>
@@ -1041,10 +1041,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>3.25</v>
+        <v>4.8</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AU3" t="n">
         <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>3.15</v>
+        <v>4.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.2</v>
+        <v>10</v>
       </c>
       <c r="BA3" t="n">
-        <v>2.62</v>
+        <v>5.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.56</v>
+        <v>4.6</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="BD3" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="I4" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K4" t="n">
         <v>3.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="M4" t="n">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="P4" t="n">
-        <v>1.42</v>
+        <v>1.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.42</v>
+        <v>2.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>2.74</v>
+        <v>6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>2.5</v>
       </c>
       <c r="U4" t="n">
         <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z4" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>660</v>
+        <v>360</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="AC4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG4" t="n">
         <v>11.5</v>
       </c>
-      <c r="AD4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>410</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15.5</v>
-      </c>
       <c r="AH4" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AK4" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AL4" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
-        <v>820</v>
+        <v>430</v>
       </c>
       <c r="AN4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>3.3</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>3.4</v>
+        <v>13.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="AW4" t="n">
-        <v>3.35</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>3.25</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.35</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.35</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>3.4</v>
+        <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>10.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>13.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
         <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
         <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="R5" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="T5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U5" t="n">
         <v>2.26</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="W5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1408,7 +1408,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1450,19 +1450,19 @@
         <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR5" t="n">
         <v>6.2</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV5" t="n">
         <v>10.5</v>
@@ -1480,19 +1480,19 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="BB5" t="n">
         <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD5" t="n">
         <v>6.6</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G6" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K6" t="n">
         <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="Q6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="U6" t="n">
         <v>2</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.04</v>
-      </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X6" t="n">
         <v>16</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
         <v>70</v>
@@ -1599,7 +1599,7 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC6" t="n">
         <v>9.4</v>
@@ -1608,7 +1608,7 @@
         <v>20</v>
       </c>
       <c r="AE6" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="AF6" t="n">
         <v>15</v>
@@ -1635,7 +1635,7 @@
         <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1650,10 +1650,10 @@
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
         <v>6.8</v>
@@ -1665,7 +1665,7 @@
         <v>5.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
         <v>7.8</v>
@@ -1674,7 +1674,7 @@
         <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB6" t="n">
         <v>17.5</v>
@@ -1689,14 +1689,14 @@
         <v>5.6</v>
       </c>
       <c r="BF6" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG6" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1733,10 @@
         <v>2.48</v>
       </c>
       <c r="H7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="I7" t="n">
         <v>3.25</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.35</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
@@ -1745,46 +1745,46 @@
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R7" t="n">
         <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T7" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U7" t="n">
         <v>2.18</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W7" t="n">
         <v>1.67</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>22</v>
@@ -1793,7 +1793,7 @@
         <v>55</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -1811,7 +1811,7 @@
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI7" t="n">
         <v>46</v>
@@ -1832,31 +1832,31 @@
         <v>28</v>
       </c>
       <c r="AO7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1865,10 +1865,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
@@ -1877,20 +1877,20 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BE7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BF7" t="n">
         <v>19.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -1921,61 +1921,61 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.18</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.22</v>
-      </c>
       <c r="H8" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
         <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O8" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U8" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W8" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -1987,7 +1987,7 @@
         <v>95</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC8" t="n">
         <v>7.6</v>
@@ -1996,16 +1996,16 @@
         <v>17.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
@@ -2014,7 +2014,7 @@
         <v>27</v>
       </c>
       <c r="AK8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
         <v>55</v>
@@ -2023,13 +2023,13 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
         <v>95</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2038,19 +2038,19 @@
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AT8" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2059,32 +2059,32 @@
         <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>14.5</v>
+        <v>20</v>
       </c>
       <c r="BB8" t="n">
         <v>24</v>
       </c>
       <c r="BC8" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="BE8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BF8" t="n">
         <v>21</v>
       </c>
       <c r="BG8" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G9" t="n">
         <v>1.87</v>
       </c>
       <c r="H9" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I9" t="n">
         <v>6</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
         <v>3.5</v>
@@ -2148,7 +2148,7 @@
         <v>1.61</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -2327,13 +2327,13 @@
         <v>5.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
         <v>1.33</v>
@@ -2348,13 +2348,13 @@
         <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>1.05</v>
+        <v>3.15</v>
       </c>
       <c r="T10" t="n">
         <v>2.3</v>
       </c>
       <c r="U10" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2387,7 +2387,7 @@
         <v>290</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AG10" t="n">
         <v>13</v>
@@ -2417,62 +2417,62 @@
         <v>550</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AR10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV10" t="n">
         <v>5.8</v>
       </c>
-      <c r="AS10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AW10" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AX10" t="n">
         <v>3.6</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AZ10" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BA10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BD10" t="n">
         <v>6</v>
       </c>
-      <c r="BB10" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BE10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF10" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -2506,7 +2506,7 @@
         <v>1.27</v>
       </c>
       <c r="G11" t="n">
-        <v>1.63</v>
+        <v>1.37</v>
       </c>
       <c r="H11" t="n">
         <v>5.5</v>
@@ -2515,19 +2515,19 @@
         <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
         <v>950</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.16</v>
@@ -2536,7 +2536,7 @@
         <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="R11" t="n">
         <v>1.47</v>
@@ -2554,7 +2554,7 @@
         <v>1.03</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -2697,46 +2697,46 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G12" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
         <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S12" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
         <v>1.75</v>
@@ -2745,37 +2745,37 @@
         <v>2.24</v>
       </c>
       <c r="V12" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
         <v>15.5</v>
       </c>
       <c r="Y12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD12" t="n">
         <v>17</v>
       </c>
-      <c r="Z12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>500</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AE12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
@@ -2787,7 +2787,7 @@
         <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AK12" t="n">
         <v>21</v>
@@ -2799,7 +2799,7 @@
         <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AO12" t="n">
         <v>46</v>
@@ -2814,53 +2814,53 @@
         <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV12" t="n">
         <v>15.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="BB12" t="n">
-        <v>11.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
         <v>29</v>
       </c>
       <c r="BE12" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BF12" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -2894,43 +2894,43 @@
         <v>2.54</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H13" t="n">
         <v>3.1</v>
       </c>
       <c r="I13" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>2.64</v>
       </c>
       <c r="O13" t="n">
-        <v>1.27</v>
+        <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.32</v>
+        <v>2.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="S13" t="n">
-        <v>2.78</v>
+        <v>5.3</v>
       </c>
       <c r="T13" t="n">
         <v>1.11</v>
@@ -2939,10 +2939,10 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X13" t="n">
         <v>90</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AT13" t="n">
         <v>4.3</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AU13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="AW13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BB13" t="n">
         <v>2.4</v>
       </c>
-      <c r="AX13" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="BA13" t="n">
+      <c r="BC13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BE13" t="n">
         <v>2.42</v>
       </c>
-      <c r="BB13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>2.4</v>
-      </c>
       <c r="BF13" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G14" t="n">
         <v>2.16</v>
@@ -3094,37 +3094,37 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L14" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="M14" t="n">
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O14" t="n">
         <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.26</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.98</v>
@@ -3133,13 +3133,13 @@
         <v>1.89</v>
       </c>
       <c r="V14" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W14" t="n">
         <v>1.86</v>
       </c>
       <c r="X14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3169,13 +3169,13 @@
         <v>12.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK14" t="n">
         <v>29</v>
@@ -3187,7 +3187,7 @@
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
@@ -3199,10 +3199,10 @@
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -3214,7 +3214,7 @@
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
@@ -3226,7 +3226,7 @@
         <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BB14" t="n">
         <v>22</v>
@@ -3235,20 +3235,20 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF14" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BG14" t="n">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H15" t="n">
         <v>9</v>
@@ -3291,37 +3291,37 @@
         <v>13.5</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N15" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
         <v>1.84</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="T15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U15" t="n">
         <v>1.64</v>
@@ -3330,7 +3330,7 @@
         <v>1.09</v>
       </c>
       <c r="W15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -3387,7 +3387,7 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.2</v>
@@ -3399,7 +3399,7 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
@@ -3414,10 +3414,10 @@
         <v>5.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
@@ -3426,23 +3426,23 @@
         <v>8.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BF15" t="n">
         <v>6.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -3476,40 +3476,40 @@
         <v>2.86</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H16" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
         <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="O16" t="n">
         <v>1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="S16" t="n">
         <v>6</v>
@@ -3518,28 +3518,28 @@
         <v>2.2</v>
       </c>
       <c r="U16" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="Y16" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="AB16" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="n">
         <v>8</v>
@@ -3551,7 +3551,7 @@
         <v>190</v>
       </c>
       <c r="AF16" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG16" t="n">
         <v>14.5</v>
@@ -3581,7 +3581,7 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
@@ -3608,13 +3608,13 @@
         <v>15.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
         <v>22</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BB16" t="n">
         <v>9.199999999999999</v>
@@ -3623,10 +3623,10 @@
         <v>9</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BE16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BF16" t="n">
         <v>9.199999999999999</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -3667,46 +3667,46 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G17" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.22</v>
+        <v>2.36</v>
       </c>
       <c r="I17" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J17" t="n">
         <v>2.96</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="M17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P17" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.94</v>
@@ -3715,10 +3715,10 @@
         <v>1.92</v>
       </c>
       <c r="V17" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="W17" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
         <v>11.5</v>
@@ -3736,7 +3736,7 @@
         <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD17" t="n">
         <v>13.5</v>
@@ -3778,59 +3778,59 @@
         <v>7.8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AR17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AV17" t="n">
         <v>4.1</v>
       </c>
-      <c r="AS17" t="n">
+      <c r="AW17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG17" t="n">
         <v>4.9</v>
       </c>
-      <c r="AT17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="n">
         <v>2.08</v>
@@ -3870,13 +3870,13 @@
         <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.28</v>
+        <v>2.56</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="G19" t="n">
         <v>1.96</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J19" t="n">
         <v>3.4</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L19" t="n">
         <v>1.52</v>
@@ -4079,25 +4079,25 @@
         <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>1.47</v>
       </c>
       <c r="P19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="R19" t="n">
         <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -4252,67 +4252,67 @@
         <v>2.54</v>
       </c>
       <c r="G20" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="H20" t="n">
         <v>3.45</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K20" t="n">
         <v>3.15</v>
       </c>
       <c r="L20" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M20" t="n">
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P20" t="n">
         <v>1.71</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="R20" t="n">
         <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U20" t="n">
         <v>2</v>
       </c>
       <c r="V20" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X20" t="n">
         <v>11</v>
       </c>
       <c r="Y20" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Z20" t="n">
         <v>24</v>
       </c>
       <c r="AA20" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AB20" t="n">
         <v>10</v>
@@ -4330,7 +4330,7 @@
         <v>16.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
         <v>18.5</v>
@@ -4348,7 +4348,7 @@
         <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>34</v>
@@ -4378,7 +4378,7 @@
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>7.6</v>
+        <v>38</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
@@ -4393,7 +4393,7 @@
         <v>7.8</v>
       </c>
       <c r="BB20" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="BC20" t="n">
         <v>14.5</v>
@@ -4402,17 +4402,17 @@
         <v>7.8</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF20" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BG20" t="n">
         <v>8.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>3.45</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K21" t="n">
         <v>3.55</v>
@@ -4467,16 +4467,16 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O21" t="n">
         <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R21" t="n">
         <v>1.29</v>
@@ -4503,22 +4503,22 @@
         <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA21" t="n">
         <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
         <v>14.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
@@ -4527,13 +4527,13 @@
         <v>11.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -4542,13 +4542,13 @@
         <v>46</v>
       </c>
       <c r="AM21" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN21" t="n">
         <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
@@ -4560,10 +4560,10 @@
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU21" t="n">
         <v>7</v>
@@ -4572,7 +4572,7 @@
         <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AX21" t="n">
         <v>12.5</v>
@@ -4584,7 +4584,7 @@
         <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BB21" t="n">
         <v>28</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H22" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
         <v>3.85</v>
@@ -4670,16 +4670,16 @@
         <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
         <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
         <v>2.02</v>
@@ -4688,7 +4688,7 @@
         <v>1.35</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4739,7 +4739,7 @@
         <v>130</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>60</v>
@@ -4757,7 +4757,7 @@
         <v>34</v>
       </c>
       <c r="AT22" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
         <v>6.8</v>
@@ -4781,13 +4781,13 @@
         <v>32</v>
       </c>
       <c r="BB22" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE22" t="n">
         <v>65</v>
@@ -4796,11 +4796,11 @@
         <v>20</v>
       </c>
       <c r="BG22" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G23" t="n">
         <v>2.1</v>
@@ -4840,37 +4840,37 @@
         <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K23" t="n">
         <v>3.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="M23" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="P23" t="n">
         <v>1.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="R23" t="n">
         <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="T23" t="n">
         <v>2.42</v>
@@ -4879,7 +4879,7 @@
         <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
         <v>1.9</v>
@@ -4891,10 +4891,10 @@
         <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AB23" t="n">
         <v>6.2</v>
@@ -4936,7 +4936,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>230</v>
+        <v>260</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4960,7 +4960,7 @@
         <v>19.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AX23" t="n">
         <v>9.4</v>
@@ -4969,7 +4969,7 @@
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="BA23" t="n">
         <v>44</v>
@@ -4981,20 +4981,20 @@
         <v>26</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BE23" t="n">
         <v>95</v>
       </c>
       <c r="BF23" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BG23" t="n">
         <v>46</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -5028,28 +5028,28 @@
         <v>1.86</v>
       </c>
       <c r="G24" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H24" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I24" t="n">
         <v>5.1</v>
       </c>
       <c r="J24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L24" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O24" t="n">
         <v>1.38</v>
@@ -5058,19 +5058,19 @@
         <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
         <v>1.31</v>
       </c>
       <c r="S24" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V24" t="n">
         <v>1.24</v>
@@ -5091,7 +5091,7 @@
         <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC24" t="n">
         <v>8.199999999999999</v>
@@ -5103,13 +5103,13 @@
         <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG24" t="n">
         <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
         <v>95</v>
@@ -5118,7 +5118,7 @@
         <v>21</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
         <v>42</v>
@@ -5127,7 +5127,7 @@
         <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO24" t="n">
         <v>110</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -5225,49 +5225,49 @@
         <v>1.63</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I25" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K25" t="n">
         <v>4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="O25" t="n">
         <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R25" t="n">
         <v>1.3</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V25" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W25" t="n">
         <v>2.58</v>
@@ -5291,7 +5291,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE25" t="n">
         <v>130</v>
@@ -5306,7 +5306,7 @@
         <v>26</v>
       </c>
       <c r="AI25" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ25" t="n">
         <v>15</v>
@@ -5315,10 +5315,10 @@
         <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>48</v>
+        <v>170</v>
       </c>
       <c r="AM25" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="n">
         <v>11.5</v>
@@ -5330,7 +5330,7 @@
         <v>11</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AR25" t="n">
         <v>28</v>
@@ -5339,7 +5339,7 @@
         <v>48</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU25" t="n">
         <v>8.4</v>
@@ -5360,7 +5360,7 @@
         <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BB25" t="n">
         <v>13.5</v>
@@ -5372,17 +5372,17 @@
         <v>32</v>
       </c>
       <c r="BE25" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF25" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG25" t="n">
         <v>46</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5419,7 @@
         <v>2.76</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I26" t="n">
         <v>3.1</v>
@@ -5431,28 +5431,28 @@
         <v>3.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M26" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O26" t="n">
         <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="R26" t="n">
         <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T26" t="n">
         <v>1.94</v>
@@ -5464,7 +5464,7 @@
         <v>1.47</v>
       </c>
       <c r="W26" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="X26" t="n">
         <v>13.5</v>
@@ -5473,7 +5473,7 @@
         <v>10.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA26" t="n">
         <v>55</v>
@@ -5530,7 +5530,7 @@
         <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT26" t="n">
         <v>8.199999999999999</v>
@@ -5557,16 +5557,16 @@
         <v>7.8</v>
       </c>
       <c r="BB26" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC26" t="n">
         <v>28</v>
       </c>
       <c r="BD26" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF26" t="n">
         <v>25</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -5616,34 +5616,34 @@
         <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
         <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R27" t="n">
         <v>1.34</v>
-      </c>
-      <c r="P27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.33</v>
       </c>
       <c r="S27" t="n">
         <v>3.85</v>
@@ -5655,7 +5655,7 @@
         <v>1.89</v>
       </c>
       <c r="V27" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
         <v>2.42</v>
@@ -5664,7 +5664,7 @@
         <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -5673,7 +5673,7 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC27" t="n">
         <v>9.4</v>
@@ -5688,7 +5688,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG27" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH27" t="n">
         <v>23</v>
@@ -5700,7 +5700,7 @@
         <v>17</v>
       </c>
       <c r="AK27" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AL27" t="n">
         <v>42</v>
@@ -5721,16 +5721,16 @@
         <v>16.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AS27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT27" t="n">
         <v>6.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV27" t="n">
         <v>21</v>
@@ -5742,13 +5742,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
         <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5757,20 +5757,20 @@
         <v>16</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G28" t="n">
-        <v>5.9</v>
+        <v>5.6</v>
       </c>
       <c r="H28" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="I28" t="n">
-        <v>2.24</v>
+        <v>2.06</v>
       </c>
       <c r="J28" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L28" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S28" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP28" t="n">
         <v>1.01</v>
       </c>
-      <c r="M28" t="n">
+      <c r="AQ28" t="n">
         <v>1.01</v>
       </c>
-      <c r="N28" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O28" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="P28" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AR28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
         <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -6007,31 +6007,31 @@
         <v>2.26</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K29" t="n">
         <v>3.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M29" t="n">
         <v>1.11</v>
       </c>
       <c r="N29" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="O29" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="R29" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S29" t="n">
         <v>5.1</v>
@@ -6040,7 +6040,7 @@
         <v>2.08</v>
       </c>
       <c r="U29" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V29" t="n">
         <v>1.79</v>
@@ -6070,7 +6070,7 @@
         <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AF29" t="n">
         <v>30</v>
@@ -6079,7 +6079,7 @@
         <v>18.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AI29" t="n">
         <v>60</v>
@@ -6088,22 +6088,22 @@
         <v>120</v>
       </c>
       <c r="AK29" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AL29" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM29" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN29" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ29" t="n">
         <v>6.2</v>
@@ -6112,7 +6112,7 @@
         <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AT29" t="n">
         <v>9.800000000000001</v>
@@ -6124,10 +6124,10 @@
         <v>9.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AY29" t="n">
         <v>15</v>
@@ -6136,29 +6136,29 @@
         <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB29" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC29" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BG29" t="n">
         <v>21</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -6198,52 +6198,52 @@
         <v>4.7</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L30" t="n">
         <v>1.53</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N30" t="n">
         <v>3</v>
       </c>
       <c r="O30" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P30" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R30" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U30" t="n">
         <v>1.82</v>
       </c>
       <c r="V30" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
         <v>2</v>
       </c>
       <c r="X30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y30" t="n">
         <v>13.5</v>
@@ -6267,7 +6267,7 @@
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
@@ -6279,10 +6279,10 @@
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK30" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL30" t="n">
         <v>1000</v>
@@ -6291,7 +6291,7 @@
         <v>200</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
@@ -6303,13 +6303,13 @@
         <v>12</v>
       </c>
       <c r="AR30" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="AS30" t="n">
         <v>40</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU30" t="n">
         <v>7</v>
@@ -6318,25 +6318,25 @@
         <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="AX30" t="n">
         <v>9.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="BB30" t="n">
         <v>16</v>
       </c>
       <c r="BC30" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BD30" t="n">
         <v>29</v>
@@ -6345,14 +6345,14 @@
         <v>46</v>
       </c>
       <c r="BF30" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG30" t="n">
-        <v>40</v>
+        <v>95</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -6383,70 +6383,70 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="G31" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H31" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="I31" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J31" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
         <v>3.8</v>
       </c>
       <c r="L31" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
       </c>
       <c r="S31" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U31" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V31" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W31" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X31" t="n">
         <v>14</v>
       </c>
       <c r="Y31" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z31" t="n">
         <v>46</v>
       </c>
       <c r="AA31" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB31" t="n">
         <v>9.199999999999999</v>
@@ -6515,7 +6515,7 @@
         <v>5.1</v>
       </c>
       <c r="AX31" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
@@ -6524,16 +6524,16 @@
         <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB31" t="n">
         <v>17.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE31" t="n">
         <v>5.3</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -6577,58 +6577,58 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="G32" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H32" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
         <v>3.8</v>
       </c>
       <c r="L32" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
         <v>1.45</v>
       </c>
       <c r="P32" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="R32" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T32" t="n">
         <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="V32" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="X32" t="n">
         <v>10.5</v>
@@ -6652,7 +6652,7 @@
         <v>29</v>
       </c>
       <c r="AE32" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AF32" t="n">
         <v>11</v>
@@ -6667,7 +6667,7 @@
         <v>140</v>
       </c>
       <c r="AJ32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="n">
         <v>26</v>
@@ -6679,7 +6679,7 @@
         <v>230</v>
       </c>
       <c r="AN32" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -6691,10 +6691,10 @@
         <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AT32" t="n">
         <v>5.7</v>
@@ -6706,7 +6706,7 @@
         <v>21</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AX32" t="n">
         <v>7.8</v>
@@ -6715,10 +6715,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB32" t="n">
         <v>15.5</v>
@@ -6727,20 +6727,20 @@
         <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BF32" t="n">
         <v>12</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="G33" t="n">
         <v>1.27</v>
@@ -6789,28 +6789,28 @@
         <v>7.6</v>
       </c>
       <c r="L33" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O33" t="n">
         <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R33" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S33" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="T33" t="n">
         <v>2.08</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-31 23:21:19</t>
+          <t>2026-04-01 01:28:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,82 +757,82 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I2" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L2" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N2" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.44</v>
       </c>
-      <c r="O2" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U2" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="W2" t="n">
         <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Z2" t="n">
         <v>10.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AB2" t="n">
         <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF2" t="n">
         <v>40</v>
@@ -844,31 +844,31 @@
         <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="AJ2" t="n">
         <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL2" t="n">
-        <v>450</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AO2" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR2" t="n">
         <v>9</v>
@@ -877,13 +877,13 @@
         <v>18</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
         <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
         <v>18</v>
@@ -895,32 +895,32 @@
         <v>20</v>
       </c>
       <c r="AZ2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>28</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>25</v>
       </c>
-      <c r="BA2" t="n">
-        <v>32</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>20</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="H3" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>1.69</v>
       </c>
       <c r="M3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="O3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="P3" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="Q3" t="n">
         <v>3.05</v>
@@ -990,25 +990,25 @@
         <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
         <v>1.54</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W3" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>22</v>
+        <v>5.7</v>
       </c>
       <c r="AC3" t="n">
         <v>42</v>
@@ -1029,7 +1029,7 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG3" t="n">
         <v>1000</v>
@@ -1044,7 +1044,7 @@
         <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,16 +1059,16 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
         <v>4.7</v>
@@ -1077,44 +1077,44 @@
         <v>6.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.4</v>
+        <v>7.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.6</v>
+        <v>7.4</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.05</v>
+        <v>6.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="BF3" t="n">
-        <v>2.82</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1145,133 +1145,133 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="U4" t="n">
         <v>1.66</v>
       </c>
-      <c r="G4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S4" t="n">
-        <v>6</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.57</v>
-      </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="Z4" t="n">
         <v>65</v>
       </c>
       <c r="AA4" t="n">
-        <v>360</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD4" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE4" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AF4" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AG4" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI4" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AM4" t="n">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
         <v>700</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="AS4" t="n">
         <v>13.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="AU4" t="n">
         <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW4" t="n">
         <v>13</v>
@@ -1283,32 +1283,32 @@
         <v>10</v>
       </c>
       <c r="AZ4" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BA4" t="n">
         <v>13</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="BE4" t="n">
         <v>13.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG4" t="n">
         <v>13.5</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
         <v>3.1</v>
       </c>
       <c r="I5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L5" t="n">
         <v>1.38</v>
@@ -1363,31 +1363,31 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O5" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P5" t="n">
         <v>2.08</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="T5" t="n">
         <v>1.65</v>
       </c>
       <c r="U5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V5" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W5" t="n">
         <v>1.67</v>
@@ -1441,7 +1441,7 @@
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
@@ -1453,25 +1453,25 @@
         <v>11.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>8.6</v>
@@ -1480,29 +1480,29 @@
         <v>11.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE5" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="BF5" t="n">
         <v>13</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1533,64 +1533,64 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="P6" t="n">
         <v>1.75</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z6" t="n">
         <v>70</v>
@@ -1599,46 +1599,46 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AE6" t="n">
         <v>150</v>
       </c>
       <c r="AF6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI6" t="n">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
         <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>10</v>
@@ -1647,56 +1647,56 @@
         <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.6</v>
+        <v>9.6</v>
       </c>
       <c r="AX6" t="n">
         <v>11.5</v>
       </c>
       <c r="AY6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF6" t="n">
         <v>7.8</v>
       </c>
-      <c r="AZ6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>16</v>
-      </c>
       <c r="BG6" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1727,10 +1727,10 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G7" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H7" t="n">
         <v>3.2</v>
@@ -1739,10 +1739,10 @@
         <v>3.25</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.44</v>
@@ -1751,7 +1751,7 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
@@ -1772,7 +1772,7 @@
         <v>1.75</v>
       </c>
       <c r="U7" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
         <v>1.44</v>
@@ -1787,7 +1787,7 @@
         <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA7" t="n">
         <v>55</v>
@@ -1796,7 +1796,7 @@
         <v>11.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD7" t="n">
         <v>13.5</v>
@@ -1835,13 +1835,13 @@
         <v>34</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS7" t="n">
         <v>24</v>
@@ -1856,7 +1856,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1868,7 +1868,7 @@
         <v>14.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
@@ -1877,10 +1877,10 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>24</v>
+        <v>14.5</v>
       </c>
       <c r="BE7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BF7" t="n">
         <v>19.5</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -1921,16 +1921,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
         <v>4.2</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.4</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
@@ -1945,16 +1945,16 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O8" t="n">
         <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R8" t="n">
         <v>1.22</v>
@@ -1963,55 +1963,55 @@
         <v>5.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
         <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
         <v>12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>11.5</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
@@ -2023,34 +2023,34 @@
         <v>580</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO8" t="n">
         <v>95</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU8" t="n">
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
@@ -2062,29 +2062,29 @@
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE8" t="n">
-        <v>21</v>
+        <v>18.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG8" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H9" t="n">
         <v>5.6</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -2309,13 +2309,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="G10" t="n">
         <v>1.46</v>
       </c>
       <c r="H10" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="n">
         <v>12.5</v>
@@ -2327,34 +2327,34 @@
         <v>5.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
         <v>1.32</v>
       </c>
       <c r="S10" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U10" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
         <v>1.08</v>
@@ -2375,7 +2375,7 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
         <v>12</v>
@@ -2390,10 +2390,10 @@
         <v>7.6</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>42</v>
+        <v>95</v>
       </c>
       <c r="AI10" t="n">
         <v>240</v>
@@ -2405,7 +2405,7 @@
         <v>18.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AM10" t="n">
         <v>320</v>
@@ -2417,62 +2417,62 @@
         <v>550</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="AQ10" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.6</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AV10" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AY10" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF10" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>3.8</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -2506,61 +2506,61 @@
         <v>1.27</v>
       </c>
       <c r="G11" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="H11" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="K11" t="n">
-        <v>950</v>
+        <v>7.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>1.1</v>
+        <v>4.8</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>2.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V11" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>2.58</v>
+        <v>3.75</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,70 +2569,70 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>10.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>4.6</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.41</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="AT11" t="n">
         <v>5.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.41</v>
+        <v>5.7</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX11" t="n">
         <v>4.4</v>
@@ -2641,32 +2641,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.41</v>
+        <v>6.8</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
         <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.41</v>
+        <v>5.6</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.41</v>
+        <v>7</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.41</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.51</v>
+        <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="G12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
         <v>1.39</v>
@@ -2724,13 +2724,13 @@
         <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
         <v>2.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R12" t="n">
         <v>1.43</v>
@@ -2739,7 +2739,7 @@
         <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="U12" t="n">
         <v>2.24</v>
@@ -2748,16 +2748,16 @@
         <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X12" t="n">
         <v>15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
         <v>90</v>
@@ -2772,16 +2772,16 @@
         <v>17</v>
       </c>
       <c r="AE12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
@@ -2790,7 +2790,7 @@
         <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL12" t="n">
         <v>32</v>
@@ -2799,34 +2799,34 @@
         <v>90</v>
       </c>
       <c r="AN12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AP12" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>30</v>
       </c>
       <c r="AS12" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU12" t="n">
         <v>7.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX12" t="n">
         <v>11.5</v>
@@ -2841,10 +2841,10 @@
         <v>48</v>
       </c>
       <c r="BB12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
         <v>29</v>
@@ -2856,11 +2856,11 @@
         <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -2891,28 +2891,28 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="G13" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="H13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
         <v>2.9</v>
       </c>
       <c r="K13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="L13" t="n">
         <v>1.58</v>
       </c>
       <c r="M13" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N13" t="n">
         <v>2.64</v>
@@ -2921,28 +2921,28 @@
         <v>1.53</v>
       </c>
       <c r="P13" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q13" t="n">
         <v>2.66</v>
       </c>
       <c r="R13" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.8</v>
       </c>
       <c r="V13" t="n">
         <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X13" t="n">
         <v>90</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AS13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AW13" t="n">
         <v>2.32</v>
       </c>
-      <c r="AT13" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.42</v>
-      </c>
       <c r="AX13" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="BA13" t="n">
         <v>2.32</v>
       </c>
       <c r="BB13" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="BD13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BE13" t="n">
         <v>2.32</v>
       </c>
-      <c r="BE13" t="n">
-        <v>2.42</v>
-      </c>
       <c r="BF13" t="n">
-        <v>2.24</v>
+        <v>2.14</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -3109,28 +3109,28 @@
         <v>1.1</v>
       </c>
       <c r="N14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
         <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R14" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S14" t="n">
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
         <v>1.3</v>
@@ -3139,7 +3139,7 @@
         <v>1.86</v>
       </c>
       <c r="X14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3163,7 +3163,7 @@
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG14" t="n">
         <v>12.5</v>
@@ -3199,34 +3199,34 @@
         <v>11</v>
       </c>
       <c r="AR14" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AT14" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU14" t="n">
         <v>7</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>6.8</v>
       </c>
       <c r="AV14" t="n">
         <v>9</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AX14" t="n">
         <v>10.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
         <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB14" t="n">
         <v>22</v>
@@ -3235,20 +3235,20 @@
         <v>11.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.6</v>
+        <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="BG14" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -3279,76 +3279,76 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="G15" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="H15" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="I15" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="J15" t="n">
         <v>4.2</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.32</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="V15" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W15" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="X15" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
         <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -3357,7 +3357,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG15" t="n">
         <v>36</v>
@@ -3369,7 +3369,7 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
         <v>970</v>
@@ -3387,7 +3387,7 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.2</v>
@@ -3399,10 +3399,10 @@
         <v>4.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV15" t="n">
         <v>4.2</v>
@@ -3411,38 +3411,38 @@
         <v>4.2</v>
       </c>
       <c r="AX15" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.22</v>
+        <v>3.8</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.4</v>
+        <v>5.6</v>
       </c>
       <c r="BC15" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -3473,31 +3473,31 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
         <v>2.88</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L16" t="n">
         <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O16" t="n">
         <v>1.59</v>
@@ -3524,10 +3524,10 @@
         <v>1.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y16" t="n">
         <v>8.199999999999999</v>
@@ -3536,7 +3536,7 @@
         <v>17.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>280</v>
+        <v>60</v>
       </c>
       <c r="AB16" t="n">
         <v>9</v>
@@ -3548,7 +3548,7 @@
         <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>190</v>
+        <v>110</v>
       </c>
       <c r="AF16" t="n">
         <v>17.5</v>
@@ -3581,7 +3581,7 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AQ16" t="n">
         <v>7</v>
@@ -3590,7 +3590,7 @@
         <v>15</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AT16" t="n">
         <v>7</v>
@@ -3602,7 +3602,7 @@
         <v>13</v>
       </c>
       <c r="AW16" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX16" t="n">
         <v>15.5</v>
@@ -3614,29 +3614,29 @@
         <v>22</v>
       </c>
       <c r="BA16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC16" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE16" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="G17" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="H17" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="I17" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="J17" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.52</v>
@@ -3694,7 +3694,7 @@
         <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P17" t="n">
         <v>1.64</v>
@@ -3706,28 +3706,28 @@
         <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="U17" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V17" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="W17" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X17" t="n">
         <v>11.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA17" t="n">
         <v>1000</v>
@@ -3736,10 +3736,10 @@
         <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD17" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
         <v>1000</v>
@@ -3748,7 +3748,7 @@
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AR17" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>8.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX17" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="AY17" t="n">
-        <v>4.4</v>
+        <v>13</v>
       </c>
       <c r="AZ17" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF17" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.9</v>
+        <v>20</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -4094,7 +4094,7 @@
         <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T19" t="n">
         <v>2.08</v>
@@ -4130,7 +4130,7 @@
         <v>55</v>
       </c>
       <c r="AE19" t="n">
-        <v>470</v>
+        <v>110</v>
       </c>
       <c r="AF19" t="n">
         <v>10.5</v>
@@ -4163,7 +4163,7 @@
         <v>700</v>
       </c>
       <c r="AP19" t="n">
-        <v>8.800000000000001</v>
+        <v>5.8</v>
       </c>
       <c r="AQ19" t="n">
         <v>11.5</v>
@@ -4172,7 +4172,7 @@
         <v>10.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT19" t="n">
         <v>6.2</v>
@@ -4190,19 +4190,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ19" t="n">
         <v>13</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB19" t="n">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BD19" t="n">
         <v>11.5</v>
@@ -4211,14 +4211,14 @@
         <v>13.5</v>
       </c>
       <c r="BF19" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="BG19" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -4261,7 +4261,7 @@
         <v>3.55</v>
       </c>
       <c r="J20" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K20" t="n">
         <v>3.15</v>
@@ -4279,10 +4279,10 @@
         <v>1.43</v>
       </c>
       <c r="P20" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
         <v>1.26</v>
@@ -4294,13 +4294,13 @@
         <v>1.86</v>
       </c>
       <c r="U20" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X20" t="n">
         <v>11</v>
@@ -4324,7 +4324,7 @@
         <v>15.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AF20" t="n">
         <v>16.5</v>
@@ -4351,13 +4351,13 @@
         <v>580</v>
       </c>
       <c r="AN20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO20" t="n">
         <v>90</v>
       </c>
       <c r="AP20" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
@@ -4366,7 +4366,7 @@
         <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AT20" t="n">
         <v>8.199999999999999</v>
@@ -4378,7 +4378,7 @@
         <v>11</v>
       </c>
       <c r="AW20" t="n">
-        <v>38</v>
+        <v>7.8</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
@@ -4387,22 +4387,22 @@
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB20" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC20" t="n">
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF20" t="n">
         <v>7.2</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -4452,10 +4452,10 @@
         <v>3.35</v>
       </c>
       <c r="I21" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
         <v>3.55</v>
@@ -4467,25 +4467,25 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
         <v>1.4</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T21" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="U21" t="n">
         <v>2.02</v>
@@ -4503,7 +4503,7 @@
         <v>11.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA21" t="n">
         <v>65</v>
@@ -4533,7 +4533,7 @@
         <v>60</v>
       </c>
       <c r="AJ21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -4554,13 +4554,13 @@
         <v>11</v>
       </c>
       <c r="AQ21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AT21" t="n">
         <v>8.4</v>
@@ -4581,10 +4581,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BB21" t="n">
         <v>28</v>
@@ -4593,7 +4593,7 @@
         <v>25</v>
       </c>
       <c r="BD21" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE21" t="n">
         <v>70</v>
@@ -4602,11 +4602,11 @@
         <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -4643,16 +4643,16 @@
         <v>2.34</v>
       </c>
       <c r="H22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L22" t="n">
         <v>1.48</v>
@@ -4661,19 +4661,19 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
         <v>2.26</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S22" t="n">
         <v>4.2</v>
@@ -4697,13 +4697,13 @@
         <v>12.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA22" t="n">
         <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC22" t="n">
         <v>7.4</v>
@@ -4727,7 +4727,7 @@
         <v>150</v>
       </c>
       <c r="AJ22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK22" t="n">
         <v>28</v>
@@ -4781,13 +4781,13 @@
         <v>32</v>
       </c>
       <c r="BB22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="BE22" t="n">
         <v>65</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -4837,10 +4837,10 @@
         <v>2.1</v>
       </c>
       <c r="H23" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J23" t="n">
         <v>3.15</v>
@@ -4855,7 +4855,7 @@
         <v>1.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="O23" t="n">
         <v>1.65</v>
@@ -4870,7 +4870,7 @@
         <v>1.16</v>
       </c>
       <c r="S23" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T23" t="n">
         <v>2.42</v>
@@ -4879,7 +4879,7 @@
         <v>1.62</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W23" t="n">
         <v>1.9</v>
@@ -4918,7 +4918,7 @@
         <v>32</v>
       </c>
       <c r="AI23" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ23" t="n">
         <v>26</v>
@@ -4936,7 +4936,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4978,7 +4978,7 @@
         <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD23" t="n">
         <v>60</v>
@@ -4987,14 +4987,14 @@
         <v>95</v>
       </c>
       <c r="BF23" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="BG23" t="n">
         <v>46</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="G24" t="n">
-        <v>1.89</v>
+        <v>1.99</v>
       </c>
       <c r="H24" t="n">
-        <v>4.9</v>
+        <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="J24" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K24" t="n">
         <v>3.7</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3.85</v>
       </c>
       <c r="L24" t="n">
         <v>1.47</v>
@@ -5049,73 +5049,73 @@
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O24" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R24" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W24" t="n">
         <v>2</v>
       </c>
-      <c r="U24" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.1</v>
-      </c>
       <c r="X24" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG24" t="n">
         <v>10.5</v>
       </c>
       <c r="AH24" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>22</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>21</v>
       </c>
       <c r="AK24" t="n">
         <v>22</v>
@@ -5124,13 +5124,13 @@
         <v>42</v>
       </c>
       <c r="AM24" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN24" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AP24" t="n">
         <v>11.5</v>
@@ -5139,56 +5139,56 @@
         <v>13.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AS24" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AW24" t="n">
         <v>44</v>
       </c>
       <c r="AX24" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY24" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY24" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AZ24" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BB24" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE24" t="n">
         <v>42</v>
       </c>
       <c r="BF24" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -5222,10 +5222,10 @@
         <v>1.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="H25" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
         <v>7.2</v>
@@ -5243,10 +5243,10 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O25" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P25" t="n">
         <v>1.82</v>
@@ -5264,25 +5264,25 @@
         <v>2.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V25" t="n">
         <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="X25" t="n">
         <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z25" t="n">
         <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="AB25" t="n">
         <v>7</v>
@@ -5300,7 +5300,7 @@
         <v>8.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>26</v>
@@ -5315,7 +5315,7 @@
         <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AM25" t="n">
         <v>190</v>
@@ -5327,13 +5327,13 @@
         <v>200</v>
       </c>
       <c r="AP25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ25" t="n">
         <v>17.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS25" t="n">
         <v>48</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -5413,25 +5413,25 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.66</v>
+        <v>2.76</v>
       </c>
       <c r="G26" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H26" t="n">
         <v>2.98</v>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J26" t="n">
         <v>3.25</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
@@ -5443,7 +5443,7 @@
         <v>1.44</v>
       </c>
       <c r="P26" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q26" t="n">
         <v>2.36</v>
@@ -5458,43 +5458,43 @@
         <v>1.94</v>
       </c>
       <c r="U26" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V26" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="W26" t="n">
         <v>1.56</v>
       </c>
       <c r="X26" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y26" t="n">
         <v>10.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
@@ -5503,7 +5503,7 @@
         <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK26" t="n">
         <v>36</v>
@@ -5512,71 +5512,71 @@
         <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN26" t="n">
         <v>36</v>
       </c>
       <c r="AO26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP26" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>7.8</v>
+        <v>12.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU26" t="n">
         <v>6.8</v>
       </c>
       <c r="AV26" t="n">
+        <v>12</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>15</v>
+      </c>
+      <c r="AY26" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX26" t="n">
+      <c r="AZ26" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD26" t="n">
         <v>14</v>
       </c>
-      <c r="AY26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>28</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BE26" t="n">
-        <v>8.6</v>
+        <v>15</v>
       </c>
       <c r="BF26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="BG26" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -5607,7 +5607,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G27" t="n">
         <v>1.69</v>
@@ -5622,7 +5622,7 @@
         <v>3.85</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L27" t="n">
         <v>1.42</v>
@@ -5664,7 +5664,7 @@
         <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z27" t="n">
         <v>55</v>
@@ -5673,7 +5673,7 @@
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC27" t="n">
         <v>9.4</v>
@@ -5727,7 +5727,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU27" t="n">
         <v>8.199999999999999</v>
@@ -5748,7 +5748,7 @@
         <v>19</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB27" t="n">
         <v>14</v>
@@ -5757,10 +5757,10 @@
         <v>16</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF27" t="n">
         <v>9.6</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -5801,37 +5801,37 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="G28" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="H28" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="I28" t="n">
         <v>2.06</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L28" t="n">
         <v>1.48</v>
       </c>
       <c r="M28" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N28" t="n">
         <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q28" t="n">
         <v>2.2</v>
@@ -5843,10 +5843,10 @@
         <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="V28" t="n">
         <v>1.94</v>
@@ -5855,116 +5855,116 @@
         <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK28" t="n">
         <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G29" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H29" t="n">
         <v>2.14</v>
       </c>
       <c r="I29" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J29" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
         <v>3.3</v>
@@ -6043,7 +6043,7 @@
         <v>1.79</v>
       </c>
       <c r="V29" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W29" t="n">
         <v>1.3</v>
@@ -6103,7 +6103,7 @@
         <v>28</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29" t="n">
         <v>6.2</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="H30" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="I30" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K30" t="n">
         <v>3.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M30" t="n">
         <v>1.11</v>
@@ -6222,7 +6222,7 @@
         <v>1.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R30" t="n">
         <v>1.23</v>
@@ -6231,22 +6231,22 @@
         <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U30" t="n">
         <v>1.82</v>
       </c>
       <c r="V30" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
@@ -6255,7 +6255,7 @@
         <v>130</v>
       </c>
       <c r="AB30" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC30" t="n">
         <v>7.6</v>
@@ -6279,7 +6279,7 @@
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK30" t="n">
         <v>1000</v>
@@ -6297,7 +6297,7 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
         <v>12</v>
@@ -6309,19 +6309,19 @@
         <v>40</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU30" t="n">
         <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW30" t="n">
         <v>34</v>
       </c>
       <c r="AX30" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY30" t="n">
         <v>9.6</v>
@@ -6330,29 +6330,29 @@
         <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC30" t="n">
         <v>22</v>
       </c>
       <c r="BD30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE30" t="n">
         <v>46</v>
       </c>
       <c r="BF30" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BG30" t="n">
         <v>95</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -6398,25 +6398,25 @@
         <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L31" t="n">
         <v>1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O31" t="n">
         <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
@@ -6425,7 +6425,7 @@
         <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U31" t="n">
         <v>1.94</v>
@@ -6443,7 +6443,7 @@
         <v>18</v>
       </c>
       <c r="Z31" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AA31" t="n">
         <v>140</v>
@@ -6452,10 +6452,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD31" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AE31" t="n">
         <v>75</v>
@@ -6464,13 +6464,13 @@
         <v>12.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH31" t="n">
         <v>24</v>
       </c>
       <c r="AI31" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ31" t="n">
         <v>24</v>
@@ -6482,7 +6482,7 @@
         <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN31" t="n">
         <v>16.5</v>
@@ -6497,25 +6497,25 @@
         <v>12.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU31" t="n">
         <v>7.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.1</v>
+        <v>55</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY31" t="n">
         <v>9</v>
@@ -6524,29 +6524,29 @@
         <v>18</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.2</v>
+        <v>55</v>
       </c>
       <c r="BB31" t="n">
         <v>17.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BD31" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF31" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
         <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K32" t="n">
         <v>3.8</v>
@@ -6634,52 +6634,52 @@
         <v>10.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA32" t="n">
         <v>240</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AD32" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE32" t="n">
         <v>130</v>
       </c>
       <c r="AF32" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG32" t="n">
         <v>11</v>
       </c>
-      <c r="AG32" t="n">
-        <v>12</v>
-      </c>
       <c r="AH32" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AI32" t="n">
         <v>140</v>
       </c>
       <c r="AJ32" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK32" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM32" t="n">
         <v>230</v>
       </c>
       <c r="AN32" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
@@ -6691,10 +6691,10 @@
         <v>13.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT32" t="n">
         <v>5.7</v>
@@ -6706,7 +6706,7 @@
         <v>21</v>
       </c>
       <c r="AW32" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="AX32" t="n">
         <v>7.8</v>
@@ -6715,10 +6715,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BA32" t="n">
-        <v>5.6</v>
+        <v>8.6</v>
       </c>
       <c r="BB32" t="n">
         <v>15.5</v>
@@ -6727,20 +6727,20 @@
         <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF32" t="n">
         <v>12</v>
       </c>
       <c r="BG32" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="G33" t="n">
         <v>1.27</v>
@@ -6786,7 +6786,7 @@
         <v>6.6</v>
       </c>
       <c r="K33" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L33" t="n">
         <v>1.27</v>
@@ -6795,22 +6795,22 @@
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O33" t="n">
         <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R33" t="n">
         <v>1.68</v>
       </c>
       <c r="S33" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="T33" t="n">
         <v>2.08</v>
@@ -6879,10 +6879,10 @@
         <v>340</v>
       </c>
       <c r="AP33" t="n">
-        <v>7.6</v>
+        <v>24</v>
       </c>
       <c r="AQ33" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AR33" t="n">
         <v>8.4</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G34" t="n">
         <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
@@ -6992,19 +6992,19 @@
         <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P34" t="n">
         <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R34" t="n">
         <v>1.18</v>
       </c>
       <c r="S34" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 01:28:12</t>
+          <t>2026-04-01 03:35:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -760,76 +760,76 @@
         <v>5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="H2" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="I2" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N2" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="P2" t="n">
         <v>1.43</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S2" t="n">
         <v>6.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="V2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>7.2</v>
+        <v>10</v>
       </c>
       <c r="Y2" t="n">
         <v>6</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="AE2" t="n">
         <v>34</v>
@@ -838,89 +838,89 @@
         <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="AH2" t="n">
         <v>36</v>
       </c>
       <c r="AI2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AJ2" t="n">
         <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AN2" t="n">
-        <v>260</v>
+        <v>300</v>
       </c>
       <c r="AO2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.3</v>
+        <v>4.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AX2" t="n">
-        <v>30</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="BC2" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BE2" t="n">
         <v>28</v>
       </c>
-      <c r="BD2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BF2" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="H3" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="I3" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
         <v>1.69</v>
@@ -975,40 +975,40 @@
         <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="O3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P3" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="Q3" t="n">
         <v>3.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W3" t="n">
         <v>2.14</v>
       </c>
       <c r="X3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
         <v>1000</v>
@@ -1017,7 +1017,7 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
         <v>42</v>
@@ -1029,7 +1029,7 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
         <v>1000</v>
@@ -1041,10 +1041,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AQ3" t="n">
         <v>6.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>7.4</v>
+        <v>1.82</v>
       </c>
       <c r="AS3" t="n">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.7</v>
+        <v>2.62</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.2</v>
+        <v>3.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>7.6</v>
+        <v>1.78</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>1.86</v>
       </c>
       <c r="AX3" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="AY3" t="n">
         <v>5.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>14</v>
+        <v>1.79</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.2</v>
+        <v>1.86</v>
       </c>
       <c r="BB3" t="n">
-        <v>7.4</v>
+        <v>2.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>6.6</v>
+        <v>1.83</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>1.85</v>
       </c>
       <c r="BE3" t="n">
-        <v>13</v>
+        <v>1.88</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.5</v>
+        <v>1.86</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.4</v>
+        <v>1.86</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1145,85 +1145,85 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.67</v>
       </c>
-      <c r="H4" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="I4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.62</v>
-      </c>
       <c r="Q4" t="n">
-        <v>2.46</v>
+        <v>2.32</v>
       </c>
       <c r="R4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="T4" t="n">
-        <v>2.32</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.66</v>
+        <v>1.57</v>
       </c>
       <c r="V4" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W4" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="Y4" t="n">
         <v>18.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>370</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AE4" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF4" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
@@ -1232,83 +1232,83 @@
         <v>32</v>
       </c>
       <c r="AI4" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM4" t="n">
         <v>250</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>390</v>
       </c>
       <c r="AN4" t="n">
         <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>700</v>
+        <v>290</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="AS4" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU4" t="n">
         <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>27</v>
+        <v>6.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AY4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>27</v>
+        <v>6.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB4" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="BE4" t="n">
-        <v>13.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF4" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>13.5</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="G5" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K5" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.82</v>
+        <v>1.7</v>
       </c>
       <c r="R5" t="n">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="S5" t="n">
-        <v>3.05</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>1.65</v>
+        <v>1.11</v>
       </c>
       <c r="U5" t="n">
-        <v>2.28</v>
+        <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="X5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
         <v>1000</v>
@@ -1402,13 +1402,13 @@
         <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>12</v>
+        <v>1.41</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.5</v>
+        <v>1.43</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.8</v>
+        <v>1.43</v>
       </c>
       <c r="AS5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AU5" t="n">
         <v>3.85</v>
       </c>
-      <c r="AT5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AV5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AW5" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>6</v>
-      </c>
       <c r="AY5" t="n">
-        <v>8.6</v>
+        <v>4.8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11.5</v>
+        <v>1.35</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC5" t="n">
-        <v>6.8</v>
+        <v>1.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.4</v>
+        <v>1.41</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.65</v>
+        <v>1.42</v>
       </c>
       <c r="BF5" t="n">
-        <v>13</v>
+        <v>1.55</v>
       </c>
       <c r="BG5" t="n">
-        <v>7.2</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1533,31 +1533,31 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="I6" t="n">
         <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="L6" t="n">
         <v>1.47</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
         <v>1.39</v>
@@ -1575,128 +1575,128 @@
         <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V6" t="n">
         <v>1.35</v>
       </c>
       <c r="W6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>900</v>
       </c>
-      <c r="AB6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>150</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>14</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>48</v>
-      </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>10</v>
+        <v>6.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR6" t="n">
-        <v>22</v>
+        <v>3.05</v>
       </c>
       <c r="AS6" t="n">
-        <v>9.6</v>
+        <v>1.95</v>
       </c>
       <c r="AT6" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV6" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU6" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AW6" t="n">
-        <v>9.6</v>
+        <v>1.91</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="BA6" t="n">
-        <v>9.6</v>
+        <v>1.95</v>
       </c>
       <c r="BB6" t="n">
-        <v>11.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC6" t="n">
-        <v>11.5</v>
+        <v>2.84</v>
       </c>
       <c r="BD6" t="n">
-        <v>9.4</v>
+        <v>1.94</v>
       </c>
       <c r="BE6" t="n">
-        <v>10</v>
+        <v>1.97</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.8</v>
+        <v>4.3</v>
       </c>
       <c r="BG6" t="n">
-        <v>9.800000000000001</v>
+        <v>2.04</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1727,82 +1727,82 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.46</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="H7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.55</v>
       </c>
       <c r="L7" t="n">
         <v>1.44</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S7" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T7" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="U7" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="X7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y7" t="n">
         <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC7" t="n">
         <v>7.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AE7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF7" t="n">
         <v>15.5</v>
@@ -1811,7 +1811,7 @@
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI7" t="n">
         <v>46</v>
@@ -1826,28 +1826,28 @@
         <v>40</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>200</v>
       </c>
       <c r="AN7" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="AO7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AP7" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>11.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
@@ -1856,7 +1856,7 @@
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="AX7" t="n">
         <v>14</v>
@@ -1865,10 +1865,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BB7" t="n">
         <v>30</v>
@@ -1877,20 +1877,20 @@
         <v>23</v>
       </c>
       <c r="BD7" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="BE7" t="n">
-        <v>18</v>
+        <v>60</v>
       </c>
       <c r="BF7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -1921,73 +1921,73 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G8" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="I8" t="n">
         <v>4</v>
-      </c>
-      <c r="I8" t="n">
-        <v>4.2</v>
       </c>
       <c r="J8" t="n">
         <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="R8" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W8" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
         <v>27</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
@@ -1999,7 +1999,7 @@
         <v>65</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
@@ -2011,7 +2011,7 @@
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
         <v>29</v>
@@ -2020,71 +2020,71 @@
         <v>55</v>
       </c>
       <c r="AM8" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
         <v>28</v>
       </c>
       <c r="AO8" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP8" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>19.5</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV8" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AX8" t="n">
         <v>11</v>
       </c>
       <c r="AY8" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>20</v>
       </c>
       <c r="BA8" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>25</v>
+      </c>
+      <c r="BD8" t="n">
         <v>26</v>
       </c>
-      <c r="BC8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>40</v>
-      </c>
       <c r="BE8" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="BF8" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>17.5</v>
+        <v>12</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J9" t="n">
         <v>3.4</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" t="n">
         <v>2.58</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="G10" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>12.5</v>
+        <v>42</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M10" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="O10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R10" t="n">
         <v>1.31</v>
       </c>
-      <c r="P10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.32</v>
-      </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>3.7</v>
       </c>
       <c r="T10" t="n">
-        <v>2.28</v>
+        <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="V10" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="W10" t="n">
-        <v>3.15</v>
+        <v>2.42</v>
       </c>
       <c r="X10" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="Y10" t="n">
-        <v>29</v>
+        <v>950</v>
       </c>
       <c r="Z10" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>7</v>
+        <v>970</v>
       </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AD10" t="n">
         <v>950</v>
       </c>
       <c r="AE10" t="n">
-        <v>290</v>
+        <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="AG10" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AH10" t="n">
-        <v>95</v>
+        <v>950</v>
       </c>
       <c r="AI10" t="n">
-        <v>240</v>
+        <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>12</v>
+        <v>900</v>
       </c>
       <c r="AK10" t="n">
-        <v>18.5</v>
+        <v>970</v>
       </c>
       <c r="AL10" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM10" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.6</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>5.7</v>
+        <v>3.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6.8</v>
+        <v>4.2</v>
       </c>
       <c r="AR10" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="AT10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX10" t="n">
         <v>3.95</v>
       </c>
-      <c r="AU10" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AY10" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>7.2</v>
+        <v>1.67</v>
       </c>
       <c r="BA10" t="n">
-        <v>8.6</v>
+        <v>4.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>7.8</v>
+        <v>1.67</v>
       </c>
       <c r="BE10" t="n">
-        <v>8.800000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="BF10" t="n">
-        <v>4.4</v>
+        <v>1.46</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -2503,64 +2503,64 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="H11" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="I11" t="n">
-        <v>14.5</v>
+        <v>60</v>
       </c>
       <c r="J11" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="L11" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="M11" t="n">
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>4.8</v>
+        <v>2.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="P11" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="R11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="T11" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="U11" t="n">
-        <v>1.78</v>
+        <v>1.11</v>
       </c>
       <c r="V11" t="n">
         <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="X11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,70 +2569,70 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10.5</v>
+        <v>900</v>
       </c>
       <c r="AK11" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>4.6</v>
+        <v>29</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.4</v>
+        <v>1.57</v>
       </c>
       <c r="AQ11" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.4</v>
+        <v>4.2</v>
       </c>
       <c r="AT11" t="n">
         <v>5.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.7</v>
+        <v>1.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="AW11" t="n">
-        <v>8.199999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="AX11" t="n">
         <v>4.4</v>
@@ -2641,32 +2641,32 @@
         <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.8</v>
+        <v>1.94</v>
       </c>
       <c r="BA11" t="n">
-        <v>8</v>
+        <v>4.2</v>
       </c>
       <c r="BB11" t="n">
         <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.6</v>
+        <v>1.77</v>
       </c>
       <c r="BD11" t="n">
-        <v>7</v>
+        <v>1.88</v>
       </c>
       <c r="BE11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>3</v>
+        <v>1.51</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="G12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
@@ -2718,55 +2718,55 @@
         <v>1.39</v>
       </c>
       <c r="M12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R12" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="U12" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>15.5</v>
+        <v>28</v>
       </c>
       <c r="Y12" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="AB12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD12" t="n">
         <v>17</v>
@@ -2775,19 +2775,19 @@
         <v>50</v>
       </c>
       <c r="AF12" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK12" t="n">
         <v>19.5</v>
@@ -2796,49 +2796,49 @@
         <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AN12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>46</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX12" t="n">
         <v>12</v>
       </c>
-      <c r="AO12" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>30</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="AY12" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>24</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>48</v>
+        <v>12.5</v>
       </c>
       <c r="BB12" t="n">
         <v>20</v>
@@ -2847,20 +2847,20 @@
         <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="BF12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="H13" t="n">
         <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J13" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
         <v>3.1</v>
       </c>
       <c r="L13" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="P13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R13" t="n">
         <v>1.19</v>
       </c>
       <c r="S13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.06</v>
+        <v>1.11</v>
       </c>
       <c r="U13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BA13" t="n">
         <v>1.8</v>
       </c>
-      <c r="V13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="X13" t="n">
-        <v>90</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>2.32</v>
-      </c>
       <c r="BB13" t="n">
-        <v>2.34</v>
+        <v>1.78</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.62</v>
+        <v>2.08</v>
       </c>
       <c r="BD13" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="BE13" t="n">
-        <v>2.32</v>
+        <v>1.8</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G14" t="n">
         <v>2.16</v>
@@ -3094,10 +3094,10 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K14" t="n">
         <v>3.55</v>
@@ -3127,10 +3127,10 @@
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V14" t="n">
         <v>1.3</v>
@@ -3139,37 +3139,37 @@
         <v>1.86</v>
       </c>
       <c r="X14" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3178,77 +3178,77 @@
         <v>900</v>
       </c>
       <c r="AK14" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.6</v>
+        <v>1.81</v>
       </c>
       <c r="AS14" t="n">
-        <v>10</v>
+        <v>1.84</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>7</v>
+        <v>4.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>9</v>
+        <v>1.75</v>
       </c>
       <c r="AW14" t="n">
-        <v>9.6</v>
+        <v>1.83</v>
       </c>
       <c r="AX14" t="n">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>6.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>1.77</v>
       </c>
       <c r="BA14" t="n">
-        <v>9.800000000000001</v>
+        <v>1.83</v>
       </c>
       <c r="BB14" t="n">
-        <v>22</v>
+        <v>6.4</v>
       </c>
       <c r="BC14" t="n">
-        <v>11.5</v>
+        <v>1.8</v>
       </c>
       <c r="BD14" t="n">
-        <v>38</v>
+        <v>1.83</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>1.85</v>
       </c>
       <c r="BF14" t="n">
-        <v>7.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>10.5</v>
+        <v>1.84</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -3279,37 +3279,37 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G15" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H15" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
       <c r="I15" t="n">
-        <v>11.5</v>
+        <v>65</v>
       </c>
       <c r="J15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="L15" t="n">
         <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O15" t="n">
         <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q15" t="n">
         <v>1.94</v>
@@ -3321,34 +3321,34 @@
         <v>3.45</v>
       </c>
       <c r="T15" t="n">
-        <v>2.12</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X15" t="n">
-        <v>90</v>
+        <v>970</v>
       </c>
       <c r="Y15" t="n">
         <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>95</v>
+        <v>480</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>970</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -3357,10 +3357,10 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>36</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
@@ -3387,7 +3387,7 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>2.22</v>
       </c>
       <c r="AQ15" t="n">
         <v>4.2</v>
@@ -3396,53 +3396,53 @@
         <v>4.2</v>
       </c>
       <c r="AS15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AT15" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT15" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AU15" t="n">
-        <v>7.8</v>
+        <v>2.08</v>
       </c>
       <c r="AV15" t="n">
         <v>4.2</v>
       </c>
       <c r="AW15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AX15" t="n">
         <v>4.2</v>
       </c>
-      <c r="AX15" t="n">
-        <v>6</v>
-      </c>
       <c r="AY15" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="AZ15" t="n">
-        <v>3.8</v>
+        <v>1.78</v>
       </c>
       <c r="BA15" t="n">
         <v>4.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>5.6</v>
+        <v>2.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>1.83</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.8</v>
+        <v>1.84</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.4</v>
+        <v>2.74</v>
       </c>
       <c r="BG15" t="n">
-        <v>15</v>
+        <v>4.2</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -3473,103 +3473,103 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.9</v>
       </c>
-      <c r="G16" t="n">
-        <v>3.1</v>
-      </c>
       <c r="H16" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="I16" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="J16" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="N16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="P16" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="U16" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="X16" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="Z16" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>60</v>
+        <v>500</v>
       </c>
       <c r="AB16" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AC16" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="AD16" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE16" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AF16" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AG16" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AI16" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AJ16" t="n">
-        <v>340</v>
+        <v>500</v>
       </c>
       <c r="AK16" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AL16" t="n">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="AM16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>1.77</v>
       </c>
       <c r="AR16" t="n">
-        <v>15</v>
+        <v>8.4</v>
       </c>
       <c r="AS16" t="n">
-        <v>9.6</v>
+        <v>1.87</v>
       </c>
       <c r="AT16" t="n">
-        <v>7</v>
+        <v>1.77</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="AV16" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.4</v>
+        <v>1.86</v>
       </c>
       <c r="AX16" t="n">
-        <v>15.5</v>
+        <v>8.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BA16" t="n">
-        <v>10</v>
+        <v>1.81</v>
       </c>
       <c r="BB16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>9.4</v>
+        <v>1.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>10</v>
+        <v>1.81</v>
       </c>
       <c r="BE16" t="n">
-        <v>11</v>
+        <v>1.92</v>
       </c>
       <c r="BF16" t="n">
-        <v>9.4</v>
+        <v>3.75</v>
       </c>
       <c r="BG16" t="n">
-        <v>9.4</v>
+        <v>3.55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -3670,19 +3670,19 @@
         <v>3.7</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I17" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="K17" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L17" t="n">
         <v>1.52</v>
@@ -3691,52 +3691,52 @@
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O17" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S17" t="n">
         <v>4.7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.98</v>
+        <v>1.11</v>
       </c>
       <c r="U17" t="n">
-        <v>1.9</v>
+        <v>1.11</v>
       </c>
       <c r="V17" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W17" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB17" t="n">
         <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>8.199999999999999</v>
+        <v>42</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
@@ -3745,10 +3745,10 @@
         <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG17" t="n">
-        <v>950</v>
+        <v>25</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="AQ17" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.2</v>
+        <v>2.52</v>
       </c>
       <c r="AT17" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AV17" t="n">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="AW17" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>5.7</v>
+        <v>2.3</v>
       </c>
       <c r="AY17" t="n">
-        <v>13</v>
+        <v>2.26</v>
       </c>
       <c r="AZ17" t="n">
-        <v>5.5</v>
+        <v>2.48</v>
       </c>
       <c r="BA17" t="n">
-        <v>6.4</v>
+        <v>2.54</v>
       </c>
       <c r="BB17" t="n">
-        <v>6.8</v>
+        <v>2.58</v>
       </c>
       <c r="BC17" t="n">
-        <v>6.6</v>
+        <v>2.56</v>
       </c>
       <c r="BD17" t="n">
-        <v>6.8</v>
+        <v>2.56</v>
       </c>
       <c r="BE17" t="n">
-        <v>7.2</v>
+        <v>2.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>6.8</v>
+        <v>2.54</v>
       </c>
       <c r="BG17" t="n">
-        <v>20</v>
+        <v>5.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -3861,22 +3861,22 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H18" t="n">
         <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="n">
         <v>1.96</v>
@@ -4067,7 +4067,7 @@
         <v>5.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
         <v>3.55</v>
@@ -4076,19 +4076,19 @@
         <v>1.52</v>
       </c>
       <c r="M19" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N19" t="n">
         <v>3</v>
       </c>
       <c r="O19" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P19" t="n">
         <v>1.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R19" t="n">
         <v>1.23</v>
@@ -4097,7 +4097,7 @@
         <v>4.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
@@ -4109,31 +4109,31 @@
         <v>2.04</v>
       </c>
       <c r="X19" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="AA19" t="n">
-        <v>900</v>
+        <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AC19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AD19" t="n">
         <v>55</v>
       </c>
       <c r="AE19" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF19" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
@@ -4142,83 +4142,83 @@
         <v>60</v>
       </c>
       <c r="AI19" t="n">
-        <v>450</v>
+        <v>110</v>
       </c>
       <c r="AJ19" t="n">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="AK19" t="n">
         <v>65</v>
       </c>
       <c r="AL19" t="n">
-        <v>290</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>580</v>
+        <v>210</v>
       </c>
       <c r="AN19" t="n">
         <v>55</v>
       </c>
       <c r="AO19" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AP19" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AQ19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR19" t="n">
         <v>11.5</v>
       </c>
-      <c r="AR19" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AS19" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="AT19" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AX19" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY19" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
         <v>13</v>
       </c>
       <c r="BA19" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD19" t="n">
         <v>13</v>
       </c>
-      <c r="BB19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>21</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BE19" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG19" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -4249,16 +4249,16 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G20" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="I20" t="n">
         <v>3.45</v>
-      </c>
-      <c r="I20" t="n">
-        <v>3.55</v>
       </c>
       <c r="J20" t="n">
         <v>3.1</v>
@@ -4273,73 +4273,73 @@
         <v>1.1</v>
       </c>
       <c r="N20" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R20" t="n">
         <v>1.26</v>
       </c>
       <c r="S20" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.86</v>
+        <v>1.11</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>1.11</v>
       </c>
       <c r="V20" t="n">
         <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X20" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y20" t="n">
         <v>11</v>
       </c>
-      <c r="Y20" t="n">
-        <v>12.5</v>
-      </c>
       <c r="Z20" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
         <v>160</v>
       </c>
       <c r="AB20" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>7.2</v>
+        <v>12</v>
       </c>
       <c r="AD20" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH20" t="n">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>160</v>
+        <v>65</v>
       </c>
       <c r="AJ20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK20" t="n">
         <v>34</v>
@@ -4348,71 +4348,71 @@
         <v>55</v>
       </c>
       <c r="AM20" t="n">
-        <v>580</v>
+        <v>140</v>
       </c>
       <c r="AN20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO20" t="n">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AQ20" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="AR20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
-        <v>8</v>
+        <v>6.4</v>
       </c>
       <c r="AT20" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AU20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>20</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BA20" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>8</v>
-      </c>
       <c r="BB20" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BC20" t="n">
         <v>14.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>8</v>
+        <v>6.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.2</v>
+        <v>6.2</v>
       </c>
       <c r="BG20" t="n">
         <v>8.4</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G21" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H21" t="n">
         <v>3.35</v>
@@ -4455,10 +4455,10 @@
         <v>3.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.47</v>
@@ -4467,40 +4467,40 @@
         <v>1.09</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V21" t="n">
         <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X21" t="n">
         <v>12</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
         <v>22</v>
@@ -4509,22 +4509,22 @@
         <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD21" t="n">
         <v>14.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF21" t="n">
         <v>14</v>
       </c>
       <c r="AG21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH21" t="n">
         <v>19</v>
@@ -4539,19 +4539,19 @@
         <v>28</v>
       </c>
       <c r="AL21" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
         <v>48</v>
       </c>
       <c r="AP21" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>11</v>
@@ -4566,16 +4566,16 @@
         <v>8.4</v>
       </c>
       <c r="AU21" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AW21" t="n">
         <v>34</v>
       </c>
       <c r="AX21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY21" t="n">
         <v>10.5</v>
@@ -4584,29 +4584,29 @@
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="BB21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC21" t="n">
-        <v>25</v>
+        <v>19.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
         <v>70</v>
       </c>
       <c r="BF21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG21" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -4637,16 +4637,16 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I22" t="n">
         <v>3.7</v>
-      </c>
-      <c r="I22" t="n">
-        <v>3.8</v>
       </c>
       <c r="J22" t="n">
         <v>3.25</v>
@@ -4661,37 +4661,37 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O22" t="n">
         <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
         <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W22" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
         <v>12.5</v>
@@ -4703,7 +4703,7 @@
         <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
         <v>7.4</v>
@@ -4712,7 +4712,7 @@
         <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="AF22" t="n">
         <v>13.5</v>
@@ -4721,10 +4721,10 @@
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="AI22" t="n">
-        <v>150</v>
+        <v>370</v>
       </c>
       <c r="AJ22" t="n">
         <v>30</v>
@@ -4736,13 +4736,13 @@
         <v>48</v>
       </c>
       <c r="AM22" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO22" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP22" t="n">
         <v>10</v>
@@ -4754,10 +4754,10 @@
         <v>22</v>
       </c>
       <c r="AS22" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU22" t="n">
         <v>6.8</v>
@@ -4766,41 +4766,41 @@
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AX22" t="n">
         <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA22" t="n">
         <v>32</v>
       </c>
       <c r="BB22" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="BC22" t="n">
         <v>20</v>
       </c>
       <c r="BD22" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="BE22" t="n">
         <v>65</v>
       </c>
       <c r="BF22" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -4831,40 +4831,40 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="H23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I23" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J23" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
         <v>1.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="O23" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="P23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R23" t="n">
         <v>1.16</v>
@@ -4876,73 +4876,73 @@
         <v>2.42</v>
       </c>
       <c r="U23" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="V23" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X23" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z23" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AA23" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AI23" t="n">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
       </c>
       <c r="AQ23" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR23" t="n">
         <v>20</v>
@@ -4960,31 +4960,31 @@
         <v>19.5</v>
       </c>
       <c r="AW23" t="n">
-        <v>85</v>
+        <v>40</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="BA23" t="n">
         <v>44</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="BD23" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="BF23" t="n">
         <v>18.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
         <v>3.6</v>
@@ -5043,49 +5043,49 @@
         <v>3.7</v>
       </c>
       <c r="L24" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M24" t="n">
         <v>1.08</v>
       </c>
       <c r="N24" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="O24" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T24" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X24" t="n">
         <v>12.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AA24" t="n">
         <v>120</v>
@@ -5094,13 +5094,13 @@
         <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AE24" t="n">
-        <v>65</v>
+        <v>990</v>
       </c>
       <c r="AF24" t="n">
         <v>11</v>
@@ -5109,43 +5109,43 @@
         <v>10.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI24" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK24" t="n">
         <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM24" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO24" t="n">
         <v>85</v>
       </c>
       <c r="AP24" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ24" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ24" t="n">
-        <v>13.5</v>
-      </c>
       <c r="AR24" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU24" t="n">
         <v>7.4</v>
@@ -5157,25 +5157,25 @@
         <v>44</v>
       </c>
       <c r="AX24" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY24" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>46</v>
+      </c>
+      <c r="BB24" t="n">
         <v>19</v>
       </c>
-      <c r="BA24" t="n">
-        <v>34</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>20</v>
-      </c>
       <c r="BC24" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BD24" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE24" t="n">
         <v>42</v>
@@ -5184,11 +5184,11 @@
         <v>14.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.61</v>
       </c>
       <c r="G25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="H25" t="n">
         <v>7</v>
@@ -5243,55 +5243,55 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O25" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="P25" t="n">
-        <v>1.82</v>
+        <v>1.86</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
         <v>2.14</v>
       </c>
       <c r="U25" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="V25" t="n">
         <v>1.16</v>
       </c>
       <c r="W25" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="X25" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="n">
         <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AD25" t="n">
-        <v>27</v>
+        <v>950</v>
       </c>
       <c r="AE25" t="n">
         <v>130</v>
@@ -5303,10 +5303,10 @@
         <v>10</v>
       </c>
       <c r="AH25" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AI25" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ25" t="n">
         <v>15</v>
@@ -5315,25 +5315,25 @@
         <v>19</v>
       </c>
       <c r="AL25" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AM25" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO25" t="n">
         <v>190</v>
       </c>
-      <c r="AN25" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>200</v>
-      </c>
       <c r="AP25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS25" t="n">
         <v>48</v>
@@ -5345,44 +5345,44 @@
         <v>8.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AW25" t="n">
         <v>40</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="BA25" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC25" t="n">
         <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE25" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF25" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG25" t="n">
         <v>46</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="G26" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="H26" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J26" t="n">
         <v>3.25</v>
       </c>
       <c r="K26" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L26" t="n">
         <v>1.51</v>
@@ -5437,34 +5437,34 @@
         <v>1.1</v>
       </c>
       <c r="N26" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="Q26" t="n">
         <v>2.36</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
         <v>4.6</v>
       </c>
       <c r="T26" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="V26" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W26" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X26" t="n">
         <v>10.5</v>
@@ -5476,25 +5476,25 @@
         <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
         <v>7.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
         <v>21</v>
@@ -5512,13 +5512,13 @@
         <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
         <v>36</v>
       </c>
       <c r="AO26" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP26" t="n">
         <v>9.800000000000001</v>
@@ -5527,56 +5527,56 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>17.5</v>
+        <v>8.6</v>
       </c>
       <c r="AS26" t="n">
-        <v>12.5</v>
+        <v>5.3</v>
       </c>
       <c r="AT26" t="n">
         <v>8.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
         <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY26" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>28</v>
+        <v>11.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="BD26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BE26" t="n">
-        <v>15</v>
+        <v>5.7</v>
       </c>
       <c r="BF26" t="n">
-        <v>30</v>
+        <v>10.5</v>
       </c>
       <c r="BG26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -5607,100 +5607,100 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="G27" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J27" t="n">
+        <v>4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N27" t="n">
         <v>3.85</v>
       </c>
-      <c r="K27" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.55</v>
-      </c>
       <c r="O27" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.06</v>
+        <v>1.96</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.97</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2.42</v>
+        <v>2.52</v>
       </c>
       <c r="X27" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="Y27" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="Z27" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE27" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AH27" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI27" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AL27" t="n">
         <v>42</v>
@@ -5709,68 +5709,68 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>11.5</v>
+        <v>1.26</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16.5</v>
+        <v>1.29</v>
       </c>
       <c r="AR27" t="n">
-        <v>7.8</v>
+        <v>1.33</v>
       </c>
       <c r="AS27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="AT27" t="n">
-        <v>6.8</v>
+        <v>1.36</v>
       </c>
       <c r="AU27" t="n">
-        <v>8.199999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="AV27" t="n">
-        <v>21</v>
+        <v>1.3</v>
       </c>
       <c r="AW27" t="n">
-        <v>8.6</v>
+        <v>1.36</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.199999999999999</v>
+        <v>1.36</v>
       </c>
       <c r="AY27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="AZ27" t="n">
-        <v>19</v>
+        <v>1.3</v>
       </c>
       <c r="BA27" t="n">
-        <v>8.6</v>
+        <v>1.36</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>1.36</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>1.27</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.6</v>
+        <v>1.32</v>
       </c>
       <c r="BE27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.36</v>
       </c>
       <c r="BF27" t="n">
-        <v>9.6</v>
+        <v>1.26</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.6</v>
+        <v>1.26</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="H28" t="n">
         <v>1.96</v>
       </c>
       <c r="I28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J28" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K28" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
         <v>1.48</v>
@@ -5828,13 +5828,13 @@
         <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R28" t="n">
         <v>1.28</v>
@@ -5843,128 +5843,128 @@
         <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="U28" t="n">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="V28" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W28" t="n">
         <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
         <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>4.1</v>
       </c>
       <c r="G29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I29" t="n">
         <v>2.24</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K29" t="n">
         <v>3.3</v>
@@ -6016,19 +6016,19 @@
         <v>1.56</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R29" t="n">
         <v>1.21</v>
@@ -6037,128 +6037,128 @@
         <v>5.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U29" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V29" t="n">
         <v>1.8</v>
       </c>
       <c r="W29" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="Y29" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="Z29" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA29" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AC29" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG29" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH29" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI29" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AL29" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AM29" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AR29" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS29" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT29" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW29" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX29" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ29" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB29" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BC29" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BG29" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -6189,16 +6189,16 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G30" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="H30" t="n">
         <v>4.9</v>
       </c>
       <c r="I30" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J30" t="n">
         <v>3.4</v>
@@ -6213,7 +6213,7 @@
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O30" t="n">
         <v>1.48</v>
@@ -6222,7 +6222,7 @@
         <v>1.64</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R30" t="n">
         <v>1.23</v>
@@ -6231,76 +6231,76 @@
         <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U30" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V30" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W30" t="n">
         <v>2.02</v>
       </c>
       <c r="X30" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y30" t="n">
         <v>14</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA30" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB30" t="n">
         <v>6.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD30" t="n">
         <v>21</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF30" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
       </c>
       <c r="AH30" t="n">
+        <v>30</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN30" t="n">
         <v>24</v>
       </c>
-      <c r="AI30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>28</v>
-      </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP30" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR30" t="n">
         <v>30</v>
@@ -6309,13 +6309,13 @@
         <v>40</v>
       </c>
       <c r="AT30" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW30" t="n">
         <v>34</v>
@@ -6324,7 +6324,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AY30" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ30" t="n">
         <v>21</v>
@@ -6333,7 +6333,7 @@
         <v>40</v>
       </c>
       <c r="BB30" t="n">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BC30" t="n">
         <v>22</v>
@@ -6345,14 +6345,14 @@
         <v>46</v>
       </c>
       <c r="BF30" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG30" t="n">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -6383,10 +6383,10 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="G31" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H31" t="n">
         <v>4.7</v>
@@ -6410,7 +6410,7 @@
         <v>3.55</v>
       </c>
       <c r="O31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P31" t="n">
         <v>1.84</v>
@@ -6425,128 +6425,128 @@
         <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.92</v>
+        <v>1.11</v>
       </c>
       <c r="U31" t="n">
-        <v>1.94</v>
+        <v>1.11</v>
       </c>
       <c r="V31" t="n">
         <v>1.24</v>
       </c>
       <c r="W31" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ31" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6583,7 @@
         <v>1.78</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="I32" t="n">
         <v>6.6</v>
@@ -6592,7 +6592,7 @@
         <v>3.55</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="L32" t="n">
         <v>1.51</v>
@@ -6604,10 +6604,10 @@
         <v>3.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="P32" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q32" t="n">
         <v>2.36</v>
@@ -6616,13 +6616,13 @@
         <v>1.25</v>
       </c>
       <c r="S32" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.16</v>
+        <v>1.11</v>
       </c>
       <c r="U32" t="n">
-        <v>1.72</v>
+        <v>1.11</v>
       </c>
       <c r="V32" t="n">
         <v>1.18</v>
@@ -6631,116 +6631,116 @@
         <v>2.28</v>
       </c>
       <c r="X32" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Y32" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z32" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA32" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AC32" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD32" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AE32" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AF32" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AG32" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AH32" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI32" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AK32" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL32" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM32" t="n">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR32" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AS32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV32" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW32" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AX32" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BA32" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB32" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC32" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD32" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BE32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BG32" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -6777,16 +6777,16 @@
         <v>1.27</v>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I33" t="n">
-        <v>16</v>
+        <v>870</v>
       </c>
       <c r="J33" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="K33" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L33" t="n">
         <v>1.27</v>
@@ -6795,146 +6795,146 @@
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O33" t="n">
         <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="Q33" t="n">
         <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="S33" t="n">
         <v>2.34</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>1.11</v>
       </c>
       <c r="U33" t="n">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W33" t="n">
         <v>4.5</v>
       </c>
       <c r="X33" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="Z33" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC33" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AD33" t="n">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AG33" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AH33" t="n">
         <v>950</v>
       </c>
       <c r="AI33" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AK33" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AL33" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM33" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>4.3</v>
+        <v>970</v>
       </c>
       <c r="AO33" t="n">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>24</v>
+        <v>1.07</v>
       </c>
       <c r="AQ33" t="n">
-        <v>38</v>
+        <v>1.07</v>
       </c>
       <c r="AR33" t="n">
-        <v>8.4</v>
+        <v>1.07</v>
       </c>
       <c r="AS33" t="n">
-        <v>8.800000000000001</v>
+        <v>1.07</v>
       </c>
       <c r="AT33" t="n">
-        <v>8.800000000000001</v>
+        <v>1.15</v>
       </c>
       <c r="AU33" t="n">
-        <v>13</v>
+        <v>1.15</v>
       </c>
       <c r="AV33" t="n">
-        <v>7.6</v>
+        <v>1.07</v>
       </c>
       <c r="AW33" t="n">
-        <v>8.4</v>
+        <v>1.07</v>
       </c>
       <c r="AX33" t="n">
-        <v>7.2</v>
+        <v>1.15</v>
       </c>
       <c r="AY33" t="n">
-        <v>9.6</v>
+        <v>1.15</v>
       </c>
       <c r="AZ33" t="n">
-        <v>7.2</v>
+        <v>1.05</v>
       </c>
       <c r="BA33" t="n">
-        <v>8.4</v>
+        <v>1.07</v>
       </c>
       <c r="BB33" t="n">
-        <v>8.6</v>
+        <v>1.15</v>
       </c>
       <c r="BC33" t="n">
-        <v>12</v>
+        <v>1.17</v>
       </c>
       <c r="BD33" t="n">
-        <v>7.2</v>
+        <v>1.05</v>
       </c>
       <c r="BE33" t="n">
-        <v>8.4</v>
+        <v>1.07</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.6</v>
+        <v>1.07</v>
       </c>
       <c r="BG33" t="n">
-        <v>8.6</v>
+        <v>1.07</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.29</v>
+        <v>1.04</v>
       </c>
       <c r="G34" t="n">
         <v>1000</v>
       </c>
       <c r="H34" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="I34" t="n">
         <v>1000</v>
@@ -6983,28 +6983,28 @@
         <v>950</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="O34" t="n">
         <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="R34" t="n">
-        <v>1.18</v>
+        <v>1.47</v>
       </c>
       <c r="S34" t="n">
-        <v>1.22</v>
+        <v>1.52</v>
       </c>
       <c r="T34" t="n">
         <v>1.11</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 03:35:09</t>
+          <t>2026-04-01 05:42:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -760,61 +760,61 @@
         <v>5.1</v>
       </c>
       <c r="G2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="H2" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="M2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="P2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S2" t="n">
         <v>6.8</v>
       </c>
       <c r="T2" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W2" t="n">
         <v>1.21</v>
       </c>
       <c r="X2" t="n">
-        <v>10</v>
+        <v>7.6</v>
       </c>
       <c r="Y2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z2" t="n">
         <v>9.800000000000001</v>
@@ -823,104 +823,104 @@
         <v>24</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="AF2" t="n">
         <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="AH2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AJ2" t="n">
         <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AL2" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="AO2" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
         <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AW2" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>32</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>14</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="BD2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AY2" t="n">
+      <c r="BE2" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF2" t="n">
         <v>15</v>
       </c>
-      <c r="AZ2" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8</v>
-      </c>
       <c r="BG2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="I3" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="L3" t="n">
         <v>1.69</v>
@@ -975,37 +975,37 @@
         <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O3" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="P3" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>1.11</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="V3" t="n">
         <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1017,10 +1017,10 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1029,10 +1029,10 @@
         <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH3" t="n">
         <v>1000</v>
@@ -1041,10 +1041,10 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.5</v>
+        <v>6.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.82</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.86</v>
+        <v>13</v>
       </c>
       <c r="AT3" t="n">
-        <v>2.62</v>
+        <v>4.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>3.95</v>
+        <v>5.1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.78</v>
+        <v>9.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.86</v>
+        <v>13</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.79</v>
+        <v>10</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.86</v>
+        <v>13</v>
       </c>
       <c r="BB3" t="n">
-        <v>2.3</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.83</v>
+        <v>12.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.88</v>
+        <v>46</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.86</v>
+        <v>4</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.86</v>
+        <v>8.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="I4" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L4" t="n">
         <v>1.52</v>
@@ -1169,146 +1169,146 @@
         <v>1.09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P4" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T4" t="n">
-        <v>1.11</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>1.57</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA4" t="n">
-        <v>370</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>120</v>
+        <v>26</v>
       </c>
       <c r="AE4" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AF4" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>170</v>
+        <v>700</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AK4" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>290</v>
+        <v>220</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>7.4</v>
+        <v>40</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.199999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AU4" t="n">
         <v>8</v>
       </c>
       <c r="AV4" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY4" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BC4" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.199999999999999</v>
+        <v>46</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.4</v>
+        <v>13</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="G5" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="I5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.55</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M5" t="n">
         <v>1.04</v>
       </c>
       <c r="N5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="X5" t="n">
+        <v>90</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>44</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>75</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY5" t="n">
         <v>5</v>
       </c>
-      <c r="O5" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="AZ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF5" t="n">
         <v>5.6</v>
       </c>
-      <c r="AY5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.55</v>
-      </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>5.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1536,13 +1536,13 @@
         <v>2.18</v>
       </c>
       <c r="G6" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H6" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
         <v>3.25</v>
@@ -1551,16 +1551,16 @@
         <v>3.55</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N6" t="n">
         <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
         <v>1.75</v>
@@ -1575,128 +1575,128 @@
         <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6" t="n">
         <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>7.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>600</v>
+        <v>36</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>6.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.05</v>
+        <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.95</v>
+        <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>7.4</v>
+        <v>14</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.91</v>
+        <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>6.2</v>
+        <v>9.6</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>12.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.95</v>
+        <v>10.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.84</v>
+        <v>12.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.94</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.97</v>
+        <v>11.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.04</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1727,115 +1727,115 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T7" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="U7" t="n">
         <v>2.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W7" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="X7" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA7" t="n">
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>17.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AE7" t="n">
         <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
         <v>11.5</v>
       </c>
       <c r="AH7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="n">
         <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL7" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>19.5</v>
       </c>
       <c r="AO7" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>11.5</v>
@@ -1844,10 +1844,10 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU7" t="n">
         <v>7.2</v>
@@ -1856,41 +1856,41 @@
         <v>12.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="AX7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ7" t="n">
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BC7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="BE7" t="n">
         <v>60</v>
       </c>
       <c r="BF7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG7" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -1921,148 +1921,148 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="I8" t="n">
         <v>3.9</v>
       </c>
-      <c r="I8" t="n">
-        <v>4</v>
-      </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O8" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="R8" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S8" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.86</v>
+        <v>1.95</v>
       </c>
       <c r="V8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
         <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AG8" t="n">
         <v>11.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI8" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AP8" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ8" t="n">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR8" t="n">
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="AT8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU8" t="n">
         <v>7</v>
       </c>
-      <c r="AU8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="AV8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW8" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY8" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BB8" t="n">
         <v>27</v>
@@ -2071,20 +2071,20 @@
         <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="BE8" t="n">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="BF8" t="n">
         <v>22</v>
       </c>
       <c r="BG8" t="n">
-        <v>12</v>
+        <v>65</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I9" t="n">
         <v>6.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G10" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="I10" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M10" t="n">
         <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
         <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R10" t="n">
         <v>1.31</v>
       </c>
       <c r="S10" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>1.77</v>
+        <v>2.16</v>
       </c>
       <c r="U10" t="n">
-        <v>1.37</v>
+        <v>1.74</v>
       </c>
       <c r="V10" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="X10" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Z10" t="n">
-        <v>500</v>
+        <v>160</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>970</v>
+        <v>7.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>950</v>
+        <v>120</v>
       </c>
       <c r="AE10" t="n">
         <v>700</v>
       </c>
       <c r="AF10" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG10" t="n">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>950</v>
+        <v>46</v>
       </c>
       <c r="AI10" t="n">
         <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>900</v>
+        <v>15.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>970</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AM10" t="n">
         <v>700</v>
       </c>
       <c r="AN10" t="n">
-        <v>29</v>
+        <v>11.5</v>
       </c>
       <c r="AO10" t="n">
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>3.2</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.2</v>
+        <v>13.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="AS10" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="AU10" t="n">
-        <v>4.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.2</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX10" t="n">
-        <v>3.95</v>
+        <v>7.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.67</v>
+        <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>4.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.6</v>
+        <v>12.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>3.5</v>
+        <v>16</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.67</v>
+        <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.73</v>
+        <v>20</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.46</v>
+        <v>9.4</v>
       </c>
       <c r="BG10" t="n">
         <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="G11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="H11" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="I11" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="K11" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="L11" t="n">
         <v>1.25</v>
@@ -2527,40 +2527,40 @@
         <v>1.02</v>
       </c>
       <c r="N11" t="n">
-        <v>2.5</v>
+        <v>5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S11" t="n">
         <v>2.36</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.93</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>1.83</v>
       </c>
       <c r="V11" t="n">
         <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="Z11" t="n">
         <v>1000</v>
@@ -2569,104 +2569,104 @@
         <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>900</v>
+        <v>11.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>4.5</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.57</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
         <v>5.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.6</v>
+        <v>5.3</v>
       </c>
       <c r="AV11" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="AW11" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY11" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.94</v>
+        <v>6.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="BB11" t="n">
         <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.77</v>
+        <v>5.7</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.88</v>
+        <v>6.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.51</v>
+        <v>3.65</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2697,28 +2697,28 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="H12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
         <v>4.5</v>
@@ -2727,10 +2727,10 @@
         <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="R12" t="n">
         <v>1.46</v>
@@ -2739,49 +2739,49 @@
         <v>3.05</v>
       </c>
       <c r="T12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U12" t="n">
         <v>2.3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X12" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
         <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AB12" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
         <v>17</v>
       </c>
       <c r="AE12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF12" t="n">
         <v>13</v>
       </c>
       <c r="AG12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
@@ -2796,10 +2796,10 @@
         <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="AN12" t="n">
-        <v>21</v>
+        <v>11.5</v>
       </c>
       <c r="AO12" t="n">
         <v>46</v>
@@ -2808,16 +2808,16 @@
         <v>15.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="AS12" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
         <v>8</v>
@@ -2826,41 +2826,41 @@
         <v>15</v>
       </c>
       <c r="AW12" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="AX12" t="n">
         <v>12</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.5</v>
+        <v>26</v>
       </c>
       <c r="BB12" t="n">
         <v>20</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
         <v>28</v>
       </c>
       <c r="BE12" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF12" t="n">
         <v>10.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G13" t="n">
         <v>2.54</v>
       </c>
-      <c r="G13" t="n">
-        <v>2.74</v>
-      </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K13" t="n">
         <v>3.1</v>
@@ -2918,70 +2918,70 @@
         <v>2.74</v>
       </c>
       <c r="O13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q13" t="n">
         <v>2.6</v>
       </c>
       <c r="R13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S13" t="n">
         <v>5.2</v>
       </c>
       <c r="T13" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.11</v>
+        <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AC13" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF13" t="n">
         <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AH13" t="n">
         <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.63</v>
+        <v>5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.63</v>
+        <v>5.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.72</v>
+        <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.79</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.6</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.57</v>
+        <v>6.2</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.77</v>
+        <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.79</v>
+        <v>9</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.77</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.69</v>
+        <v>6.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.75</v>
+        <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.78</v>
+        <v>17.5</v>
       </c>
       <c r="BC13" t="n">
-        <v>2.08</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.79</v>
+        <v>9</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.8</v>
+        <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.79</v>
+        <v>16</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.79</v>
+        <v>6.2</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3115,7 +3115,7 @@
         <v>1.43</v>
       </c>
       <c r="P14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
         <v>2.28</v>
@@ -3127,10 +3127,10 @@
         <v>4.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="V14" t="n">
         <v>1.3</v>
@@ -3139,116 +3139,116 @@
         <v>1.86</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AA14" t="n">
         <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>5.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT14" t="n">
         <v>7</v>
       </c>
-      <c r="AR14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AU14" t="n">
-        <v>4.4</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.75</v>
+        <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.83</v>
+        <v>11</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.77</v>
+        <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.83</v>
+        <v>11.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>6.4</v>
+        <v>12</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.8</v>
+        <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.83</v>
+        <v>20</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.85</v>
+        <v>12.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.84</v>
+        <v>12</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3285,22 +3285,22 @@
         <v>1.49</v>
       </c>
       <c r="H15" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>65</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="L15" t="n">
         <v>1.41</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
         <v>3.75</v>
@@ -3318,16 +3318,16 @@
         <v>1.36</v>
       </c>
       <c r="S15" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U15" t="n">
-        <v>1.11</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W15" t="n">
         <v>3</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>970</v>
+        <v>42</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -3357,10 +3357,10 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH15" t="n">
         <v>950</v>
@@ -3369,13 +3369,13 @@
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
+        <v>180</v>
+      </c>
+      <c r="AK15" t="n">
         <v>500</v>
       </c>
-      <c r="AK15" t="n">
-        <v>970</v>
-      </c>
       <c r="AL15" t="n">
-        <v>500</v>
+        <v>370</v>
       </c>
       <c r="AM15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.22</v>
+        <v>6.2</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.2</v>
+        <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.58</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.08</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>2.58</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX15" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AY15" t="n">
-        <v>2.1</v>
+        <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.78</v>
+        <v>7.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.2</v>
+        <v>9.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.83</v>
+        <v>7</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.78</v>
+        <v>29</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.84</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.74</v>
+        <v>4.5</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.2</v>
+        <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3473,28 +3473,28 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="G16" t="n">
         <v>2.8</v>
       </c>
-      <c r="G16" t="n">
-        <v>2.9</v>
-      </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J16" t="n">
         <v>2.98</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="N16" t="n">
         <v>2.62</v>
@@ -3506,7 +3506,7 @@
         <v>1.52</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
@@ -3515,128 +3515,128 @@
         <v>5.9</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U16" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X16" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="Y16" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z16" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>500</v>
+        <v>130</v>
       </c>
       <c r="AB16" t="n">
-        <v>970</v>
+        <v>7.8</v>
       </c>
       <c r="AC16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK16" t="n">
         <v>42</v>
       </c>
-      <c r="AD16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>500</v>
-      </c>
       <c r="AL16" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AM16" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN16" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AO16" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP16" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.77</v>
+        <v>7.8</v>
       </c>
       <c r="AR16" t="n">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.87</v>
+        <v>40</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.77</v>
+        <v>7.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>7.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.86</v>
+        <v>36</v>
       </c>
       <c r="AX16" t="n">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
-        <v>7.6</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.81</v>
+        <v>48</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.8</v>
+        <v>15.5</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.9</v>
+        <v>36</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.81</v>
+        <v>19.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.92</v>
+        <v>28</v>
       </c>
       <c r="BF16" t="n">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="BG16" t="n">
-        <v>3.55</v>
+        <v>18</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="G17" t="n">
         <v>4.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="I17" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="J17" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="K17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.52</v>
@@ -3691,40 +3691,40 @@
         <v>1.11</v>
       </c>
       <c r="N17" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O17" t="n">
         <v>1.46</v>
       </c>
       <c r="P17" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R17" t="n">
         <v>1.23</v>
       </c>
       <c r="S17" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T17" t="n">
-        <v>1.11</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="V17" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="W17" t="n">
         <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3736,19 +3736,19 @@
         <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>42</v>
+        <v>7.4</v>
       </c>
       <c r="AD17" t="n">
         <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -3775,62 +3775,62 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>5.1</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AR17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU17" t="n">
         <v>6.4</v>
       </c>
-      <c r="AS17" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AV17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
-        <v>2.3</v>
+        <v>13.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>2.26</v>
+        <v>9</v>
       </c>
       <c r="AZ17" t="n">
-        <v>2.48</v>
+        <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.54</v>
+        <v>36</v>
       </c>
       <c r="BB17" t="n">
-        <v>2.58</v>
+        <v>30</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.56</v>
+        <v>11</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>2.58</v>
+        <v>12.5</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG17" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -3861,19 +3861,19 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
         <v>4.9</v>
       </c>
       <c r="J18" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4055,10 +4055,10 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G19" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H19" t="n">
         <v>4.9</v>
@@ -4067,22 +4067,22 @@
         <v>5.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M19" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P19" t="n">
         <v>1.65</v>
@@ -4094,10 +4094,10 @@
         <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T19" t="n">
-        <v>1.11</v>
+        <v>2.12</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
@@ -4109,10 +4109,10 @@
         <v>2.04</v>
       </c>
       <c r="X19" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y19" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
         <v>36</v>
@@ -4121,25 +4121,25 @@
         <v>150</v>
       </c>
       <c r="AB19" t="n">
-        <v>9.4</v>
+        <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>13</v>
+        <v>7.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AE19" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF19" t="n">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="AG19" t="n">
         <v>11</v>
       </c>
       <c r="AH19" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>110</v>
@@ -4154,71 +4154,71 @@
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN19" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="n">
         <v>140</v>
       </c>
       <c r="AP19" t="n">
-        <v>6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="AS19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AT19" t="n">
         <v>6.4</v>
       </c>
       <c r="AU19" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AX19" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY19" t="n">
         <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="BA19" t="n">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BB19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="BC19" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="BD19" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="BE19" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BF19" t="n">
-        <v>9.199999999999999</v>
+        <v>18</v>
       </c>
       <c r="BG19" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4249,97 +4249,97 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="G20" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="H20" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I20" t="n">
         <v>3.45</v>
       </c>
       <c r="J20" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>3.15</v>
       </c>
       <c r="L20" t="n">
         <v>1.51</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P20" t="n">
         <v>1.68</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T20" t="n">
-        <v>1.11</v>
+        <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V20" t="n">
         <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="X20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="Y20" t="n">
         <v>11</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA20" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>16.5</v>
+        <v>9</v>
       </c>
       <c r="AC20" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AD20" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE20" t="n">
         <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG20" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI20" t="n">
         <v>65</v>
       </c>
       <c r="AJ20" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK20" t="n">
         <v>34</v>
@@ -4357,62 +4357,62 @@
         <v>55</v>
       </c>
       <c r="AP20" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AQ20" t="n">
-        <v>7.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="AT20" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>8.4</v>
+        <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AX20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12.5</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BC20" t="n">
-        <v>14.5</v>
+        <v>29</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.2</v>
+        <v>24</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BF20" t="n">
-        <v>6.2</v>
+        <v>29</v>
       </c>
       <c r="BG20" t="n">
-        <v>8.4</v>
+        <v>44</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G21" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H21" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I21" t="n">
         <v>3.4</v>
@@ -4464,16 +4464,16 @@
         <v>1.47</v>
       </c>
       <c r="M21" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O21" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P21" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="Q21" t="n">
         <v>2.14</v>
@@ -4482,25 +4482,25 @@
         <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T21" t="n">
         <v>1.9</v>
       </c>
       <c r="U21" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V21" t="n">
         <v>1.41</v>
       </c>
       <c r="W21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z21" t="n">
         <v>22</v>
@@ -4509,19 +4509,19 @@
         <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>42</v>
       </c>
       <c r="AF21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG21" t="n">
         <v>11</v>
@@ -4530,13 +4530,13 @@
         <v>19</v>
       </c>
       <c r="AI21" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ21" t="n">
         <v>32</v>
       </c>
       <c r="AK21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL21" t="n">
         <v>42</v>
@@ -4545,25 +4545,25 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO21" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP21" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR21" t="n">
         <v>20</v>
       </c>
       <c r="AS21" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT21" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU21" t="n">
         <v>7.2</v>
@@ -4572,10 +4572,10 @@
         <v>12.5</v>
       </c>
       <c r="AW21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AX21" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY21" t="n">
         <v>10.5</v>
@@ -4584,29 +4584,29 @@
         <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BB21" t="n">
         <v>29</v>
       </c>
       <c r="BC21" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BD21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="BF21" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG21" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>2.34</v>
       </c>
       <c r="G22" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I22" t="n">
         <v>3.65</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.7</v>
-      </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L22" t="n">
         <v>1.48</v>
@@ -4661,13 +4661,13 @@
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
         <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
         <v>2.22</v>
@@ -4682,19 +4682,19 @@
         <v>1.91</v>
       </c>
       <c r="U22" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W22" t="n">
         <v>1.73</v>
       </c>
       <c r="X22" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y22" t="n">
         <v>12</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>12.5</v>
       </c>
       <c r="Z22" t="n">
         <v>24</v>
@@ -4703,16 +4703,16 @@
         <v>75</v>
       </c>
       <c r="AB22" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD22" t="n">
         <v>15.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="AF22" t="n">
         <v>13.5</v>
@@ -4721,31 +4721,31 @@
         <v>11.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>370</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
         <v>30</v>
       </c>
       <c r="AK22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL22" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM22" t="n">
         <v>120</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO22" t="n">
         <v>55</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
         <v>11</v>
@@ -4766,41 +4766,41 @@
         <v>14</v>
       </c>
       <c r="AW22" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AX22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AY22" t="n">
         <v>10</v>
       </c>
       <c r="AZ22" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
       </c>
       <c r="BC22" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BD22" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BE22" t="n">
         <v>65</v>
       </c>
       <c r="BF22" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -4834,28 +4834,28 @@
         <v>2.08</v>
       </c>
       <c r="G23" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H23" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L23" t="n">
         <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N23" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="O23" t="n">
         <v>1.66</v>
@@ -4867,7 +4867,7 @@
         <v>3.1</v>
       </c>
       <c r="R23" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S23" t="n">
         <v>7</v>
@@ -4876,34 +4876,34 @@
         <v>2.42</v>
       </c>
       <c r="U23" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="V23" t="n">
         <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X23" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="Y23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC23" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4912,89 +4912,89 @@
         <v>11</v>
       </c>
       <c r="AG23" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ23" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN23" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AP23" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU23" t="n">
         <v>6.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AX23" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY23" t="n">
         <v>11</v>
       </c>
       <c r="AZ23" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BA23" t="n">
         <v>44</v>
       </c>
       <c r="BB23" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE23" t="n">
-        <v>55</v>
+        <v>100</v>
       </c>
       <c r="BF23" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BG23" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5025,82 +5025,82 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="G24" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H24" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J24" t="n">
         <v>3.6</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L24" t="n">
         <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R24" t="n">
         <v>1.29</v>
       </c>
       <c r="S24" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T24" t="n">
         <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W24" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X24" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AA24" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB24" t="n">
         <v>8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD24" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>990</v>
+        <v>70</v>
       </c>
       <c r="AF24" t="n">
         <v>11</v>
@@ -5115,10 +5115,10 @@
         <v>1000</v>
       </c>
       <c r="AJ24" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK24" t="n">
         <v>23</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>22</v>
       </c>
       <c r="AL24" t="n">
         <v>44</v>
@@ -5127,52 +5127,52 @@
         <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP24" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AS24" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AU24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV24" t="n">
         <v>16.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ24" t="n">
-        <v>16</v>
+        <v>19.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BD24" t="n">
         <v>30</v>
@@ -5181,14 +5181,14 @@
         <v>42</v>
       </c>
       <c r="BF24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG24" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5219,25 +5219,25 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I25" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="J25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K25" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M25" t="n">
         <v>1.08</v>
@@ -5249,49 +5249,49 @@
         <v>1.37</v>
       </c>
       <c r="P25" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="T25" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U25" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V25" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W25" t="n">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="X25" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z25" t="n">
         <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AB25" t="n">
         <v>7.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>950</v>
+        <v>28</v>
       </c>
       <c r="AE25" t="n">
         <v>130</v>
@@ -5300,73 +5300,73 @@
         <v>8.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH25" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AI25" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AJ25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="AM25" t="n">
         <v>180</v>
       </c>
       <c r="AN25" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO25" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="AP25" t="n">
         <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>14.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS25" t="n">
         <v>48</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU25" t="n">
         <v>8.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AW25" t="n">
         <v>40</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BA25" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BB25" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD25" t="n">
         <v>34</v>
@@ -5375,14 +5375,14 @@
         <v>46</v>
       </c>
       <c r="BF25" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG25" t="n">
         <v>46</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="G26" t="n">
         <v>2.74</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I26" t="n">
         <v>3.1</v>
@@ -5431,7 +5431,7 @@
         <v>3.35</v>
       </c>
       <c r="L26" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M26" t="n">
         <v>1.1</v>
@@ -5455,10 +5455,10 @@
         <v>4.6</v>
       </c>
       <c r="T26" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="U26" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V26" t="n">
         <v>1.48</v>
@@ -5470,40 +5470,40 @@
         <v>10.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA26" t="n">
         <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC26" t="n">
         <v>7.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
       </c>
       <c r="AG26" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI26" t="n">
         <v>60</v>
       </c>
       <c r="AJ26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AK26" t="n">
         <v>36</v>
@@ -5527,56 +5527,56 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>8.6</v>
+        <v>16.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="AT26" t="n">
         <v>8.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV26" t="n">
         <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="AX26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY26" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="BB26" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="BC26" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="BD26" t="n">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="BE26" t="n">
-        <v>5.7</v>
+        <v>44</v>
       </c>
       <c r="BF26" t="n">
-        <v>10.5</v>
+        <v>30</v>
       </c>
       <c r="BG26" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5607,100 +5607,100 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="G27" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="H27" t="n">
         <v>6.4</v>
       </c>
       <c r="I27" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J27" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K27" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="R27" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.11</v>
+        <v>1.85</v>
       </c>
       <c r="V27" t="n">
         <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="X27" t="n">
-        <v>970</v>
+        <v>16</v>
       </c>
       <c r="Y27" t="n">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>970</v>
+        <v>8</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>950</v>
+        <v>26</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG27" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>950</v>
+        <v>24</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>42</v>
@@ -5709,68 +5709,68 @@
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.26</v>
+        <v>11.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.29</v>
+        <v>16.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.36</v>
+        <v>8</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.36</v>
+        <v>6.4</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.3</v>
+        <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.36</v>
+        <v>8.6</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.36</v>
+        <v>8.6</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.3</v>
+        <v>20</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.36</v>
+        <v>38</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.36</v>
+        <v>13.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.27</v>
+        <v>15.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.32</v>
+        <v>7.4</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.36</v>
+        <v>7.8</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.26</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.26</v>
+        <v>7.8</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="G28" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="H28" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I28" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="J28" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.48</v>
@@ -5828,7 +5828,7 @@
         <v>3.25</v>
       </c>
       <c r="O28" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
         <v>1.73</v>
@@ -5843,128 +5843,128 @@
         <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="U28" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="W28" t="n">
         <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y28" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="Z28" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AA28" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AB28" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AF28" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AG28" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK28" t="n">
         <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM28" t="n">
         <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO28" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP28" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ28" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR28" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS28" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AT28" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY28" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BB28" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC28" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BE28" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF28" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG28" t="n">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>4.1</v>
       </c>
       <c r="G29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H29" t="n">
         <v>2.16</v>
       </c>
       <c r="I29" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J29" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K29" t="n">
         <v>3.3</v>
@@ -6022,13 +6022,13 @@
         <v>2.84</v>
       </c>
       <c r="O29" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P29" t="n">
         <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R29" t="n">
         <v>1.21</v>
@@ -6037,128 +6037,128 @@
         <v>5.1</v>
       </c>
       <c r="T29" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U29" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="V29" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W29" t="n">
         <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y29" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB29" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC29" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF29" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG29" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI29" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK29" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL29" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM29" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN29" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AO29" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AT29" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BD29" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG29" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="G30" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H30" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J30" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L30" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M30" t="n">
         <v>1.11</v>
@@ -6228,58 +6228,58 @@
         <v>1.23</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U30" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V30" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W30" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="Y30" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z30" t="n">
         <v>36</v>
       </c>
       <c r="AA30" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AB30" t="n">
         <v>6.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD30" t="n">
         <v>21</v>
       </c>
       <c r="AE30" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG30" t="n">
         <v>11</v>
       </c>
       <c r="AH30" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI30" t="n">
         <v>110</v>
       </c>
       <c r="AJ30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK30" t="n">
         <v>25</v>
@@ -6291,22 +6291,22 @@
         <v>190</v>
       </c>
       <c r="AN30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="n">
         <v>130</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>30</v>
       </c>
       <c r="AS30" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="AT30" t="n">
         <v>6.4</v>
@@ -6315,13 +6315,13 @@
         <v>7.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW30" t="n">
         <v>34</v>
       </c>
       <c r="AX30" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY30" t="n">
         <v>10</v>
@@ -6330,29 +6330,29 @@
         <v>21</v>
       </c>
       <c r="BA30" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BB30" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BC30" t="n">
         <v>22</v>
       </c>
       <c r="BD30" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE30" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="BF30" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="BG30" t="n">
         <v>40</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G31" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="H31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I31" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J31" t="n">
         <v>3.5</v>
@@ -6401,22 +6401,22 @@
         <v>3.75</v>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
         <v>1.84</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R31" t="n">
         <v>1.31</v>
@@ -6425,128 +6425,128 @@
         <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>1.11</v>
+        <v>1.92</v>
       </c>
       <c r="U31" t="n">
-        <v>1.11</v>
+        <v>1.94</v>
       </c>
       <c r="V31" t="n">
         <v>1.24</v>
       </c>
       <c r="W31" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G32" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H32" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I32" t="n">
         <v>6.6</v>
       </c>
       <c r="J32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K32" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L32" t="n">
         <v>1.51</v>
@@ -6601,16 +6601,16 @@
         <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R32" t="n">
         <v>1.25</v>
@@ -6619,128 +6619,128 @@
         <v>4.5</v>
       </c>
       <c r="T32" t="n">
-        <v>1.11</v>
+        <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="V32" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W32" t="n">
         <v>2.28</v>
       </c>
       <c r="X32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA32" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AB32" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE32" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF32" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG32" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI32" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM32" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN32" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AT32" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BA32" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6777,19 +6777,19 @@
         <v>1.27</v>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="I33" t="n">
-        <v>870</v>
+        <v>16.5</v>
       </c>
       <c r="J33" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="K33" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="L33" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
@@ -6801,140 +6801,140 @@
         <v>1.17</v>
       </c>
       <c r="P33" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q33" t="n">
         <v>1.53</v>
       </c>
       <c r="R33" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S33" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T33" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>1.11</v>
+        <v>1.82</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W33" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE33" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AF33" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG33" t="n">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AH33" t="n">
         <v>950</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AK33" t="n">
-        <v>970</v>
+        <v>15</v>
       </c>
       <c r="AL33" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AM33" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN33" t="n">
-        <v>970</v>
+        <v>4</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.07</v>
+        <v>19</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.07</v>
+        <v>6.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.07</v>
+        <v>7</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.07</v>
+        <v>7.4</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.15</v>
+        <v>9</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.15</v>
+        <v>14</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.07</v>
+        <v>6.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.07</v>
+        <v>7.2</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.15</v>
+        <v>7.8</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.15</v>
+        <v>10</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.05</v>
+        <v>6.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.07</v>
+        <v>7.2</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.15</v>
+        <v>8.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.17</v>
+        <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.07</v>
+        <v>7.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.07</v>
+        <v>3.4</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.07</v>
+        <v>7.2</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>
@@ -6965,100 +6965,100 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.04</v>
+        <v>2.6</v>
       </c>
       <c r="G34" t="n">
-        <v>1000</v>
+        <v>3.3</v>
       </c>
       <c r="H34" t="n">
-        <v>1.3</v>
+        <v>2.6</v>
       </c>
       <c r="I34" t="n">
-        <v>1000</v>
+        <v>3.05</v>
       </c>
       <c r="J34" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L34" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="M34" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="N34" t="n">
-        <v>1.49</v>
+        <v>3.75</v>
       </c>
       <c r="O34" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="P34" t="n">
-        <v>1.46</v>
+        <v>1.96</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.51</v>
+        <v>1.82</v>
       </c>
       <c r="R34" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="S34" t="n">
-        <v>1.52</v>
+        <v>3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U34" t="n">
-        <v>1.11</v>
+        <v>2.18</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI34" t="n">
         <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL34" t="n">
         <v>1000</v>
@@ -7067,68 +7067,68 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 05:42:54</t>
+          <t>2026-04-01 07:50:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H2" t="n">
         <v>1.93</v>
       </c>
       <c r="I2" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J2" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="M2" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="P2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="Q2" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="R2" t="n">
         <v>1.15</v>
       </c>
       <c r="S2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="U2" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="V2" t="n">
         <v>2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z2" t="n">
         <v>9.800000000000001</v>
@@ -829,7 +829,7 @@
         <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE2" t="n">
         <v>44</v>
@@ -838,7 +838,7 @@
         <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AH2" t="n">
         <v>34</v>
@@ -850,13 +850,13 @@
         <v>190</v>
       </c>
       <c r="AK2" t="n">
-        <v>130</v>
+        <v>240</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>330</v>
       </c>
       <c r="AN2" t="n">
         <v>250</v>
@@ -874,19 +874,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AT2" t="n">
         <v>11</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW2" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AX2" t="n">
         <v>32</v>
@@ -895,22 +895,22 @@
         <v>21</v>
       </c>
       <c r="AZ2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA2" t="n">
         <v>32</v>
       </c>
       <c r="BB2" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BD2" t="n">
         <v>14.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>46</v>
+        <v>200</v>
       </c>
       <c r="BF2" t="n">
         <v>15</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -951,10 +951,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="H3" t="n">
         <v>7</v>
@@ -966,155 +966,155 @@
         <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="M3" t="n">
         <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="P3" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S3" t="n">
         <v>7</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="U3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V3" t="n">
         <v>1.15</v>
       </c>
       <c r="W3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="X3" t="n">
-        <v>90</v>
+        <v>7.2</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA3" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>5.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG3" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AJ3" t="n">
-        <v>900</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
         <v>85</v>
       </c>
       <c r="AL3" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>450</v>
       </c>
       <c r="AP3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AQ3" t="n">
         <v>13</v>
       </c>
       <c r="AR3" t="n">
-        <v>11</v>
+        <v>18.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>4.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.6</v>
+        <v>21</v>
       </c>
       <c r="AW3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AX3" t="n">
         <v>7.4</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AZ3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>12.5</v>
+        <v>19</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>17</v>
       </c>
       <c r="BE3" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="BF3" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="H4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="I4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K4" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N4" t="n">
         <v>3</v>
@@ -1181,34 +1181,34 @@
         <v>2.36</v>
       </c>
       <c r="R4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
         <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>2.24</v>
       </c>
       <c r="X4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y4" t="n">
         <v>16.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA4" t="n">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="AB4" t="n">
         <v>6.4</v>
@@ -1217,13 +1217,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE4" t="n">
-        <v>700</v>
+        <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG4" t="n">
         <v>10.5</v>
@@ -1232,52 +1232,52 @@
         <v>28</v>
       </c>
       <c r="AI4" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>55</v>
       </c>
       <c r="AM4" t="n">
-        <v>700</v>
+        <v>220</v>
       </c>
       <c r="AN4" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO4" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP4" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR4" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.5</v>
+        <v>36</v>
       </c>
       <c r="AT4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU4" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV4" t="n">
         <v>21</v>
       </c>
       <c r="AW4" t="n">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="AX4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AY4" t="n">
         <v>9.4</v>
@@ -1286,29 +1286,29 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="BB4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC4" t="n">
         <v>19</v>
       </c>
       <c r="BD4" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="BE4" t="n">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="BF4" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG4" t="n">
         <v>13</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1339,67 +1339,67 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="G5" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K5" t="n">
         <v>3.55</v>
       </c>
       <c r="L5" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.54</v>
+        <v>2.82</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="U5" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="V5" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X5" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA5" t="n">
         <v>1000</v>
@@ -1408,28 +1408,28 @@
         <v>44</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AE5" t="n">
         <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
         <v>75</v>
@@ -1444,65 +1444,65 @@
         <v>55</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP5" t="n">
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW5" t="n">
         <v>6.8</v>
       </c>
-      <c r="AT5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>6.4</v>
-      </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB5" t="n">
-        <v>11</v>
+        <v>6.6</v>
       </c>
       <c r="BC5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1533,170 +1533,170 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.18</v>
+        <v>1.95</v>
       </c>
       <c r="G6" t="n">
-        <v>2.34</v>
+        <v>2.02</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="P6" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R6" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="U6" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.75</v>
+        <v>1.99</v>
       </c>
       <c r="X6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AE6" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AG6" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BB6" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>20</v>
+        <v>14.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="G7" t="n">
         <v>2.38</v>
       </c>
-      <c r="G7" t="n">
-        <v>2.4</v>
-      </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I7" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.55</v>
@@ -1751,13 +1751,13 @@
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
         <v>2</v>
@@ -1766,25 +1766,25 @@
         <v>1.37</v>
       </c>
       <c r="S7" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z7" t="n">
         <v>23</v>
@@ -1793,7 +1793,7 @@
         <v>60</v>
       </c>
       <c r="AB7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC7" t="n">
         <v>7.8</v>
@@ -1805,19 +1805,19 @@
         <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AG7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>17</v>
       </c>
       <c r="AI7" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AJ7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK7" t="n">
         <v>25</v>
@@ -1826,19 +1826,19 @@
         <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>38</v>
       </c>
       <c r="AP7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>11.5</v>
       </c>
       <c r="AR7" t="n">
         <v>20</v>
@@ -1847,50 +1847,50 @@
         <v>42</v>
       </c>
       <c r="AT7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AX7" t="n">
         <v>13.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA7" t="n">
         <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE7" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="BF7" t="n">
         <v>18</v>
       </c>
       <c r="BG7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G8" t="n">
         <v>2.28</v>
       </c>
-      <c r="G8" t="n">
-        <v>2.3</v>
-      </c>
       <c r="H8" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
         <v>3.9</v>
@@ -1936,10 +1936,10 @@
         <v>3.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -1966,16 +1966,16 @@
         <v>1.98</v>
       </c>
       <c r="U8" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V8" t="n">
         <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y8" t="n">
         <v>12</v>
@@ -2002,7 +2002,7 @@
         <v>13</v>
       </c>
       <c r="AG8" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH8" t="n">
         <v>20</v>
@@ -2011,7 +2011,7 @@
         <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK8" t="n">
         <v>28</v>
@@ -2026,10 +2026,10 @@
         <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AP8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ8" t="n">
         <v>10.5</v>
@@ -2047,7 +2047,7 @@
         <v>7</v>
       </c>
       <c r="AV8" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW8" t="n">
         <v>46</v>
@@ -2059,7 +2059,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA8" t="n">
         <v>55</v>
@@ -2077,14 +2077,14 @@
         <v>75</v>
       </c>
       <c r="BF8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG8" t="n">
         <v>65</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -2115,19 +2115,19 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="H9" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="I9" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
         <v>3.55</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="G10" t="n">
         <v>1.62</v>
@@ -2318,10 +2318,10 @@
         <v>6.8</v>
       </c>
       <c r="I10" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J10" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
         <v>4.5</v>
@@ -2360,7 +2360,7 @@
         <v>1.14</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X10" t="n">
         <v>13.5</v>
@@ -2420,7 +2420,7 @@
         <v>11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.5</v>
+        <v>17</v>
       </c>
       <c r="AR10" t="n">
         <v>27</v>
@@ -2435,7 +2435,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
         <v>9.199999999999999</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -2509,13 +2509,13 @@
         <v>1.31</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I11" t="n">
         <v>14</v>
       </c>
       <c r="J11" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="K11" t="n">
         <v>7.4</v>
@@ -2524,7 +2524,7 @@
         <v>1.25</v>
       </c>
       <c r="M11" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -2545,16 +2545,16 @@
         <v>2.36</v>
       </c>
       <c r="T11" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U11" t="n">
         <v>1.83</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="X11" t="n">
         <v>32</v>
@@ -2611,7 +2611,7 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ11" t="n">
         <v>6.6</v>
@@ -2626,7 +2626,7 @@
         <v>5.6</v>
       </c>
       <c r="AU11" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AV11" t="n">
         <v>6.6</v>
@@ -2641,7 +2641,7 @@
         <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BA11" t="n">
         <v>7.4</v>
@@ -2650,7 +2650,7 @@
         <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BD11" t="n">
         <v>6.4</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -2697,16 +2697,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="G12" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="H12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="J12" t="n">
         <v>3.8</v>
@@ -2715,73 +2715,73 @@
         <v>3.85</v>
       </c>
       <c r="L12" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O12" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
         <v>1.46</v>
       </c>
       <c r="S12" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
         <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC12" t="n">
         <v>8.6</v>
       </c>
       <c r="AD12" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH12" t="n">
         <v>17</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>48</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>16.5</v>
       </c>
       <c r="AI12" t="n">
         <v>55</v>
@@ -2796,49 +2796,49 @@
         <v>32</v>
       </c>
       <c r="AM12" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AN12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>44</v>
+      </c>
+      <c r="AX12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AO12" t="n">
-        <v>46</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT12" t="n">
+      <c r="AY12" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>15</v>
       </c>
       <c r="BA12" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="BB12" t="n">
         <v>20</v>
@@ -2853,14 +2853,14 @@
         <v>65</v>
       </c>
       <c r="BF12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="G13" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J13" t="n">
         <v>2.94</v>
       </c>
       <c r="K13" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="L13" t="n">
         <v>1.57</v>
@@ -2915,16 +2915,16 @@
         <v>1.12</v>
       </c>
       <c r="N13" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="O13" t="n">
         <v>1.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="R13" t="n">
         <v>1.2</v>
@@ -2939,16 +2939,16 @@
         <v>1.79</v>
       </c>
       <c r="V13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="X13" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="Z13" t="n">
         <v>1000</v>
@@ -2957,31 +2957,31 @@
         <v>900</v>
       </c>
       <c r="AB13" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
         <v>1000</v>
       </c>
       <c r="AE13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF13" t="n">
         <v>500</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AG13" t="n">
+        <v>25</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>500</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1000</v>
       </c>
-      <c r="AG13" t="n">
-        <v>500</v>
-      </c>
-      <c r="AH13" t="n">
+      <c r="AJ13" t="n">
         <v>1000</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>310</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2999,19 +2999,19 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR13" t="n">
         <v>11</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT13" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU13" t="n">
         <v>6.2</v>
@@ -3020,41 +3020,41 @@
         <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AX13" t="n">
-        <v>8.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="AZ13" t="n">
         <v>10</v>
       </c>
       <c r="BA13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BB13" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD13" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BE13" t="n">
         <v>10</v>
       </c>
       <c r="BF13" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.2</v>
+        <v>9.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
         <v>4</v>
       </c>
       <c r="I14" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
         <v>3.4</v>
@@ -3106,16 +3106,16 @@
         <v>1.49</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O14" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q14" t="n">
         <v>2.28</v>
@@ -3124,22 +3124,22 @@
         <v>1.27</v>
       </c>
       <c r="S14" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
         <v>1.96</v>
       </c>
       <c r="U14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W14" t="n">
         <v>1.86</v>
       </c>
       <c r="X14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y14" t="n">
         <v>13</v>
@@ -3154,7 +3154,7 @@
         <v>8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
         <v>30</v>
@@ -3169,7 +3169,7 @@
         <v>11</v>
       </c>
       <c r="AH14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
@@ -3190,19 +3190,19 @@
         <v>46</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>55</v>
       </c>
       <c r="AT14" t="n">
         <v>7</v>
@@ -3214,41 +3214,41 @@
         <v>14.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AX14" t="n">
         <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="BC14" t="n">
         <v>13.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="BE14" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF14" t="n">
         <v>18</v>
       </c>
       <c r="BG14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -3279,58 +3279,58 @@
         </is>
       </c>
       <c r="F15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G15" t="n">
         <v>1.44</v>
       </c>
-      <c r="G15" t="n">
-        <v>1.49</v>
-      </c>
       <c r="H15" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J15" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="K15" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="T15" t="n">
         <v>2.16</v>
       </c>
       <c r="U15" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="V15" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W15" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
@@ -3345,10 +3345,10 @@
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AC15" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -3357,7 +3357,7 @@
         <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AG15" t="n">
         <v>36</v>
@@ -3381,68 +3381,68 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AS15" t="n">
         <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AU15" t="n">
         <v>6.2</v>
       </c>
       <c r="AV15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX15" t="n">
         <v>4.8</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>4.5</v>
       </c>
       <c r="AY15" t="n">
         <v>7</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7.6</v>
+        <v>16</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>28</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF15" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>29</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>4.5</v>
       </c>
       <c r="BG15" t="n">
         <v>15</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -3473,170 +3473,170 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.68</v>
+        <v>2.48</v>
       </c>
       <c r="G16" t="n">
-        <v>2.8</v>
+        <v>2.52</v>
       </c>
       <c r="H16" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="J16" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="M16" t="n">
         <v>1.14</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="O16" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="P16" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R16" t="n">
         <v>1.18</v>
       </c>
       <c r="S16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T16" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="U16" t="n">
         <v>1.78</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="W16" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="X16" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AA16" t="n">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="AB16" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC16" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF16" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG16" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI16" t="n">
         <v>85</v>
       </c>
       <c r="AJ16" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AK16" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AL16" t="n">
         <v>75</v>
       </c>
       <c r="AM16" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AO16" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP16" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>40</v>
+        <v>19.5</v>
       </c>
       <c r="AT16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU16" t="n">
         <v>6.6</v>
       </c>
       <c r="AV16" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AY16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA16" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="BB16" t="n">
-        <v>15.5</v>
+        <v>32</v>
       </c>
       <c r="BC16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BD16" t="n">
-        <v>19.5</v>
+        <v>44</v>
       </c>
       <c r="BE16" t="n">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="BF16" t="n">
-        <v>15.5</v>
+        <v>34</v>
       </c>
       <c r="BG16" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>4.1</v>
       </c>
       <c r="H17" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I17" t="n">
         <v>2.36</v>
@@ -3721,10 +3721,10 @@
         <v>1.33</v>
       </c>
       <c r="X17" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="Z17" t="n">
         <v>1000</v>
@@ -3748,7 +3748,7 @@
         <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AH17" t="n">
         <v>1000</v>
@@ -3778,28 +3778,28 @@
         <v>8.6</v>
       </c>
       <c r="AQ17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR17" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS17" t="n">
         <v>14.5</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU17" t="n">
         <v>6.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW17" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX17" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AY17" t="n">
         <v>9</v>
@@ -3808,19 +3808,19 @@
         <v>10.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="BB17" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="BC17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD17" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="BE17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BF17" t="n">
         <v>9.800000000000001</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -3867,13 +3867,13 @@
         <v>2.1</v>
       </c>
       <c r="H18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>3.45</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q18" t="n">
         <v>2.52</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="n">
         <v>1.95</v>
@@ -4064,7 +4064,7 @@
         <v>4.9</v>
       </c>
       <c r="I19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
@@ -4082,13 +4082,13 @@
         <v>2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P19" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="R19" t="n">
         <v>1.23</v>
@@ -4097,7 +4097,7 @@
         <v>4.9</v>
       </c>
       <c r="T19" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="U19" t="n">
         <v>1.79</v>
@@ -4124,7 +4124,7 @@
         <v>7</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
         <v>21</v>
@@ -4148,7 +4148,7 @@
         <v>22</v>
       </c>
       <c r="AK19" t="n">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>55</v>
@@ -4157,7 +4157,7 @@
         <v>190</v>
       </c>
       <c r="AN19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO19" t="n">
         <v>140</v>
@@ -4169,10 +4169,10 @@
         <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AS19" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AT19" t="n">
         <v>6.4</v>
@@ -4181,10 +4181,10 @@
         <v>7.2</v>
       </c>
       <c r="AV19" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW19" t="n">
-        <v>16.5</v>
+        <v>40</v>
       </c>
       <c r="AX19" t="n">
         <v>9.199999999999999</v>
@@ -4196,29 +4196,29 @@
         <v>22</v>
       </c>
       <c r="BA19" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="BB19" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
       </c>
       <c r="BD19" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="BE19" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="BF19" t="n">
         <v>18</v>
       </c>
       <c r="BG19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -4273,28 +4273,28 @@
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R20" t="n">
         <v>1.25</v>
       </c>
       <c r="S20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T20" t="n">
         <v>1.96</v>
       </c>
       <c r="U20" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="V20" t="n">
         <v>1.4</v>
@@ -4318,7 +4318,7 @@
         <v>9</v>
       </c>
       <c r="AC20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AD20" t="n">
         <v>14.5</v>
@@ -4327,7 +4327,7 @@
         <v>48</v>
       </c>
       <c r="AF20" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG20" t="n">
         <v>12.5</v>
@@ -4336,7 +4336,7 @@
         <v>20</v>
       </c>
       <c r="AI20" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AJ20" t="n">
         <v>40</v>
@@ -4363,7 +4363,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS20" t="n">
         <v>32</v>
@@ -4378,7 +4378,7 @@
         <v>13</v>
       </c>
       <c r="AW20" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="AX20" t="n">
         <v>13.5</v>
@@ -4390,7 +4390,7 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BB20" t="n">
         <v>18.5</v>
@@ -4399,10 +4399,10 @@
         <v>29</v>
       </c>
       <c r="BD20" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="BE20" t="n">
-        <v>14</v>
+        <v>80</v>
       </c>
       <c r="BF20" t="n">
         <v>29</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>2.38</v>
       </c>
       <c r="H21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I21" t="n">
         <v>3.4</v>
@@ -4467,7 +4467,7 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.39</v>
@@ -4482,13 +4482,13 @@
         <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U21" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V21" t="n">
         <v>1.41</v>
@@ -4500,7 +4500,7 @@
         <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Z21" t="n">
         <v>22</v>
@@ -4509,10 +4509,10 @@
         <v>65</v>
       </c>
       <c r="AB21" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD21" t="n">
         <v>14</v>
@@ -4521,13 +4521,13 @@
         <v>42</v>
       </c>
       <c r="AF21" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG21" t="n">
         <v>11</v>
       </c>
       <c r="AH21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI21" t="n">
         <v>55</v>
@@ -4545,7 +4545,7 @@
         <v>110</v>
       </c>
       <c r="AN21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO21" t="n">
         <v>46</v>
@@ -4569,19 +4569,19 @@
         <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX21" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AY21" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
         <v>46</v>
@@ -4596,17 +4596,17 @@
         <v>36</v>
       </c>
       <c r="BE21" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="BF21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG21" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -4637,25 +4637,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G22" t="n">
         <v>2.38</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I22" t="n">
         <v>3.65</v>
       </c>
       <c r="J22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.35</v>
       </c>
-      <c r="K22" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
@@ -4664,22 +4664,22 @@
         <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P22" t="n">
         <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R22" t="n">
         <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
         <v>2.02</v>
@@ -4688,7 +4688,7 @@
         <v>1.37</v>
       </c>
       <c r="W22" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X22" t="n">
         <v>11</v>
@@ -4706,7 +4706,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
         <v>15.5</v>
@@ -4724,7 +4724,7 @@
         <v>19</v>
       </c>
       <c r="AI22" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ22" t="n">
         <v>30</v>
@@ -4772,25 +4772,25 @@
         <v>12.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ22" t="n">
         <v>16.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB22" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="BC22" t="n">
         <v>24</v>
       </c>
       <c r="BD22" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BE22" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BF22" t="n">
         <v>21</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -4855,16 +4855,16 @@
         <v>1.16</v>
       </c>
       <c r="N23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="O23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="P23" t="n">
         <v>1.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="R23" t="n">
         <v>1.15</v>
@@ -4876,7 +4876,7 @@
         <v>2.42</v>
       </c>
       <c r="U23" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
         <v>1.25</v>
@@ -4897,13 +4897,13 @@
         <v>150</v>
       </c>
       <c r="AB23" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC23" t="n">
         <v>7.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
@@ -4924,7 +4924,7 @@
         <v>29</v>
       </c>
       <c r="AK23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL23" t="n">
         <v>75</v>
@@ -4933,10 +4933,10 @@
         <v>330</v>
       </c>
       <c r="AN23" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO23" t="n">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="AP23" t="n">
         <v>6.8</v>
@@ -4945,13 +4945,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
         <v>50</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU23" t="n">
         <v>6.8</v>
@@ -4960,7 +4960,7 @@
         <v>20</v>
       </c>
       <c r="AW23" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AX23" t="n">
         <v>9.6</v>
@@ -4972,29 +4972,29 @@
         <v>27</v>
       </c>
       <c r="BA23" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BB23" t="n">
         <v>22</v>
       </c>
       <c r="BC23" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BD23" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="BE23" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF23" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BG23" t="n">
         <v>50</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G24" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="H24" t="n">
         <v>4.5</v>
@@ -5037,16 +5037,16 @@
         <v>4.7</v>
       </c>
       <c r="J24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K24" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L24" t="n">
         <v>1.48</v>
       </c>
       <c r="M24" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N24" t="n">
         <v>3.4</v>
@@ -5055,31 +5055,31 @@
         <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q24" t="n">
         <v>2.18</v>
       </c>
       <c r="R24" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S24" t="n">
         <v>4.1</v>
       </c>
       <c r="T24" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="V24" t="n">
         <v>1.27</v>
       </c>
       <c r="W24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X24" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y24" t="n">
         <v>14</v>
@@ -5118,16 +5118,16 @@
         <v>22</v>
       </c>
       <c r="AK24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM24" t="n">
         <v>140</v>
       </c>
       <c r="AN24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO24" t="n">
         <v>80</v>
@@ -5139,19 +5139,19 @@
         <v>12.5</v>
       </c>
       <c r="AR24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS24" t="n">
         <v>38</v>
       </c>
       <c r="AT24" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU24" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU24" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AV24" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AW24" t="n">
         <v>46</v>
@@ -5160,7 +5160,7 @@
         <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ24" t="n">
         <v>19.5</v>
@@ -5175,7 +5175,7 @@
         <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BE24" t="n">
         <v>42</v>
@@ -5184,11 +5184,11 @@
         <v>15</v>
       </c>
       <c r="BG24" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G25" t="n">
         <v>1.6</v>
@@ -5243,28 +5243,28 @@
         <v>1.08</v>
       </c>
       <c r="N25" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O25" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U25" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V25" t="n">
         <v>1.15</v>
@@ -5273,22 +5273,22 @@
         <v>2.66</v>
       </c>
       <c r="X25" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y25" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z25" t="n">
         <v>60</v>
       </c>
       <c r="AA25" t="n">
-        <v>300</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD25" t="n">
         <v>28</v>
@@ -5297,13 +5297,13 @@
         <v>130</v>
       </c>
       <c r="AF25" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AH25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI25" t="n">
         <v>130</v>
@@ -5315,74 +5315,74 @@
         <v>18</v>
       </c>
       <c r="AL25" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM25" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="AN25" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO25" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="AP25" t="n">
         <v>12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AS25" t="n">
-        <v>48</v>
+        <v>220</v>
       </c>
       <c r="AT25" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AW25" t="n">
         <v>40</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY25" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA25" t="n">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="BB25" t="n">
         <v>13</v>
       </c>
       <c r="BC25" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD25" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="BE25" t="n">
         <v>46</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG25" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -5416,79 +5416,79 @@
         <v>2.68</v>
       </c>
       <c r="G26" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="H26" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K26" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L26" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P26" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S26" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="T26" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="U26" t="n">
-        <v>1.96</v>
+        <v>1.93</v>
       </c>
       <c r="V26" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z26" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
         <v>55</v>
       </c>
       <c r="AB26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AF26" t="n">
         <v>16</v>
@@ -5497,10 +5497,10 @@
         <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ26" t="n">
         <v>42</v>
@@ -5512,40 +5512,40 @@
         <v>55</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN26" t="n">
         <v>36</v>
       </c>
       <c r="AO26" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ26" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AR26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AS26" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT26" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AU26" t="n">
         <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>11.5</v>
@@ -5554,16 +5554,16 @@
         <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BB26" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="BC26" t="n">
         <v>30</v>
       </c>
       <c r="BD26" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BE26" t="n">
         <v>44</v>
@@ -5572,11 +5572,11 @@
         <v>30</v>
       </c>
       <c r="BG26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -5607,25 +5607,25 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="G27" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="H27" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="I27" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
         <v>1.07</v>
@@ -5637,7 +5637,7 @@
         <v>1.35</v>
       </c>
       <c r="P27" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
         <v>2.04</v>
@@ -5649,128 +5649,128 @@
         <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="U27" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="V27" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W27" t="n">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="X27" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="Z27" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="AA27" t="n">
         <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AC27" t="n">
         <v>10</v>
       </c>
       <c r="AD27" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="AE27" t="n">
         <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG27" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AI27" t="n">
         <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AK27" t="n">
         <v>22</v>
       </c>
       <c r="AL27" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AM27" t="n">
         <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AO27" t="n">
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AQ27" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX27" t="n">
         <v>7.6</v>
       </c>
-      <c r="AS27" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>22</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="AY27" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA27" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BB27" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BC27" t="n">
         <v>15.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>7.4</v>
+        <v>32</v>
       </c>
       <c r="BE27" t="n">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
       <c r="BF27" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG27" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -5801,22 +5801,22 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="G28" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="I28" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L28" t="n">
         <v>1.48</v>
@@ -5834,7 +5834,7 @@
         <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
         <v>1.28</v>
@@ -5843,19 +5843,19 @@
         <v>4.1</v>
       </c>
       <c r="T28" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="U28" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="V28" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="W28" t="n">
         <v>1.25</v>
       </c>
       <c r="X28" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Y28" t="n">
         <v>8</v>
@@ -5882,13 +5882,13 @@
         <v>36</v>
       </c>
       <c r="AG28" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH28" t="n">
         <v>22</v>
       </c>
       <c r="AI28" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ28" t="n">
         <v>140</v>
@@ -5921,10 +5921,10 @@
         <v>20</v>
       </c>
       <c r="AT28" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>9.4</v>
@@ -5933,10 +5933,10 @@
         <v>20</v>
       </c>
       <c r="AX28" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY28" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AZ28" t="n">
         <v>17.5</v>
@@ -5945,7 +5945,7 @@
         <v>36</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC28" t="n">
         <v>23</v>
@@ -5954,17 +5954,17 @@
         <v>25</v>
       </c>
       <c r="BE28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG28" t="n">
         <v>16</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>4.4</v>
       </c>
       <c r="H29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I29" t="n">
         <v>2.26</v>
@@ -6010,7 +6010,7 @@
         <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L29" t="n">
         <v>1.56</v>
@@ -6028,7 +6028,7 @@
         <v>1.59</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R29" t="n">
         <v>1.21</v>
@@ -6037,10 +6037,10 @@
         <v>5.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="V29" t="n">
         <v>1.79</v>
@@ -6082,7 +6082,7 @@
         <v>950</v>
       </c>
       <c r="AI29" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ29" t="n">
         <v>120</v>
@@ -6091,10 +6091,10 @@
         <v>70</v>
       </c>
       <c r="AL29" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AM29" t="n">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AN29" t="n">
         <v>110</v>
@@ -6121,7 +6121,7 @@
         <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
         <v>24</v>
@@ -6136,7 +6136,7 @@
         <v>19.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB29" t="n">
         <v>32</v>
@@ -6145,20 +6145,20 @@
         <v>24</v>
       </c>
       <c r="BD29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -6189,46 +6189,46 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="H30" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J30" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S30" t="n">
         <v>4.8</v>
-      </c>
-      <c r="I30" t="n">
-        <v>5</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L30" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="P30" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S30" t="n">
-        <v>5.1</v>
       </c>
       <c r="T30" t="n">
         <v>2.14</v>
@@ -6237,103 +6237,103 @@
         <v>1.82</v>
       </c>
       <c r="V30" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="W30" t="n">
-        <v>2</v>
+        <v>2.16</v>
       </c>
       <c r="X30" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="Z30" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AA30" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AB30" t="n">
         <v>6.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF30" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG30" t="n">
         <v>10.5</v>
       </c>
-      <c r="AG30" t="n">
-        <v>11</v>
-      </c>
       <c r="AH30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI30" t="n">
         <v>110</v>
       </c>
       <c r="AJ30" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK30" t="n">
         <v>23</v>
       </c>
-      <c r="AK30" t="n">
-        <v>25</v>
-      </c>
       <c r="AL30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM30" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN30" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AO30" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="AP30" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS30" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="AT30" t="n">
         <v>6.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW30" t="n">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="AX30" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AY30" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BB30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC30" t="n">
         <v>22</v>
@@ -6342,17 +6342,17 @@
         <v>44</v>
       </c>
       <c r="BE30" t="n">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="BF30" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="BG30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -6383,170 +6383,170 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.88</v>
+        <v>1.81</v>
       </c>
       <c r="G31" t="n">
-        <v>1.93</v>
+        <v>1.82</v>
       </c>
       <c r="H31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I31" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K31" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L31" t="n">
         <v>1.44</v>
       </c>
       <c r="M31" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O31" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="R31" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="T31" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="U31" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="V31" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="W31" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="X31" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y31" t="n">
         <v>17.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AA31" t="n">
-        <v>140</v>
+        <v>170</v>
       </c>
       <c r="AB31" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC31" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AD31" t="n">
         <v>23</v>
       </c>
       <c r="AE31" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF31" t="n">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI31" t="n">
         <v>85</v>
       </c>
       <c r="AJ31" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AL31" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="AM31" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
-        <v>17</v>
+        <v>12.5</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="AT31" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>5.3</v>
+        <v>21</v>
       </c>
       <c r="AX31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.6</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>5.3</v>
+        <v>13</v>
       </c>
       <c r="BB31" t="n">
-        <v>4.6</v>
+        <v>16.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="BD31" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.5</v>
+        <v>14</v>
       </c>
       <c r="BF31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -6577,22 +6577,22 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G32" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="H32" t="n">
         <v>6</v>
       </c>
       <c r="I32" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K32" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
         <v>1.51</v>
@@ -6613,43 +6613,43 @@
         <v>2.34</v>
       </c>
       <c r="R32" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T32" t="n">
         <v>2.16</v>
       </c>
       <c r="U32" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="V32" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W32" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X32" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Z32" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AA32" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AB32" t="n">
         <v>7</v>
       </c>
       <c r="AC32" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD32" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE32" t="n">
         <v>130</v>
@@ -6658,16 +6658,16 @@
         <v>9.6</v>
       </c>
       <c r="AG32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI32" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AJ32" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK32" t="n">
         <v>23</v>
@@ -6676,28 +6676,28 @@
         <v>55</v>
       </c>
       <c r="AM32" t="n">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="AN32" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ32" t="n">
         <v>14</v>
       </c>
       <c r="AR32" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS32" t="n">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AU32" t="n">
         <v>7.2</v>
@@ -6706,41 +6706,41 @@
         <v>21</v>
       </c>
       <c r="AW32" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="AX32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB32" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC32" t="n">
         <v>18.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BF32" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BG32" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -6771,85 +6771,85 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="G33" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="H33" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="I33" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="J33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K33" t="n">
         <v>6.8</v>
       </c>
-      <c r="K33" t="n">
-        <v>7.8</v>
-      </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="M33" t="n">
         <v>1.03</v>
       </c>
       <c r="N33" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O33" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P33" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R33" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="S33" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="V33" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W33" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="X33" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="Y33" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="Z33" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
       </c>
       <c r="AB33" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC33" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AD33" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AE33" t="n">
-        <v>280</v>
+        <v>220</v>
       </c>
       <c r="AF33" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG33" t="n">
         <v>12.5</v>
@@ -6858,7 +6858,7 @@
         <v>950</v>
       </c>
       <c r="AI33" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AJ33" t="n">
         <v>11</v>
@@ -6867,74 +6867,74 @@
         <v>15</v>
       </c>
       <c r="AL33" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM33" t="n">
-        <v>210</v>
+        <v>180</v>
       </c>
       <c r="AN33" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AO33" t="n">
-        <v>350</v>
+        <v>270</v>
       </c>
       <c r="AP33" t="n">
-        <v>19</v>
+        <v>7.8</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR33" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AS33" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AT33" t="n">
         <v>9</v>
       </c>
       <c r="AU33" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AV33" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AW33" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX33" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY33" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AZ33" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA33" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BC33" t="n">
         <v>12</v>
       </c>
       <c r="BD33" t="n">
-        <v>6.4</v>
+        <v>27</v>
       </c>
       <c r="BE33" t="n">
-        <v>7.2</v>
+        <v>42</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="BG33" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
         <v>3.05</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
         <v>3.9</v>
@@ -6992,22 +6992,22 @@
         <v>3.75</v>
       </c>
       <c r="O34" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P34" t="n">
         <v>1.96</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="R34" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S34" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="T34" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="U34" t="n">
         <v>2.18</v>
@@ -7019,7 +7019,7 @@
         <v>1.45</v>
       </c>
       <c r="X34" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y34" t="n">
         <v>15</v>
@@ -7067,68 +7067,68 @@
         <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AO34" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AP34" t="n">
         <v>4.1</v>
       </c>
       <c r="AQ34" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AR34" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AS34" t="n">
         <v>4.8</v>
       </c>
       <c r="AT34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AZ34" t="n">
         <v>4</v>
       </c>
-      <c r="AU34" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BB34" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BC34" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD34" t="n">
         <v>4.8</v>
       </c>
       <c r="BE34" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-01 07:50:57</t>
+          <t>2026-04-01 10:01:22</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-01.xlsx
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>5.2</v>
+        <v>90</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>200</v>
       </c>
       <c r="H2" t="n">
-        <v>1.93</v>
+        <v>1.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1.99</v>
+        <v>1.05</v>
       </c>
       <c r="J2" t="n">
-        <v>3.2</v>
+        <v>24</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>27</v>
       </c>
       <c r="L2" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.47</v>
+        <v>3.55</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.96</v>
+        <v>1.37</v>
       </c>
       <c r="R2" t="n">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>6.6</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="U2" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>8</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.800000000000001</v>
+        <v>3.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>24</v>
+        <v>4.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AE2" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI2" t="n">
         <v>44</v>
       </c>
-      <c r="AF2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>160</v>
-      </c>
       <c r="AJ2" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>240</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>330</v>
       </c>
       <c r="AN2" t="n">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>30</v>
+        <v>6.2</v>
       </c>
       <c r="AP2" t="n">
-        <v>6.8</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.2</v>
+        <v>14.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>8.800000000000001</v>
+        <v>3.55</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.5</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>17.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.2</v>
+        <v>14.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AW2" t="n">
-        <v>21</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>32</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BA2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>28</v>
+        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>14.5</v>
+        <v>26</v>
       </c>
       <c r="BE2" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="BG2" t="n">
-        <v>24</v>
+        <v>5.6</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -951,170 +951,170 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="H3" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I3" t="n">
         <v>7.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="M3" t="n">
-        <v>1.15</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R3" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="S3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX3" t="n">
         <v>7</v>
       </c>
-      <c r="T3" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="X3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>700</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>34</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>190</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>270</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>410</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>450</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.4</v>
-      </c>
       <c r="AY3" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
-        <v>20</v>
+        <v>2.74</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.2</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>16.5</v>
+        <v>4.1</v>
       </c>
       <c r="BC3" t="n">
-        <v>19</v>
+        <v>2.62</v>
       </c>
       <c r="BD3" t="n">
-        <v>17</v>
+        <v>2.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>55</v>
+        <v>2.74</v>
       </c>
       <c r="BF3" t="n">
-        <v>10.5</v>
+        <v>2.62</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.8</v>
+        <v>2.62</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="H4" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I4" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="K4" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
         <v>1.1</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O4" t="n">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="R4" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="S4" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="X4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y4" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="AB4" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>980</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>700</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>140</v>
+      </c>
+      <c r="BF4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AC4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>17</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>210</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>70</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>38</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>14</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>13.5</v>
-      </c>
       <c r="BG4" t="n">
-        <v>13</v>
+        <v>4.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1339,49 +1339,49 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.3</v>
       </c>
-      <c r="G5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="H5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.22</v>
-      </c>
       <c r="Q5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U5" t="n">
         <v>2.44</v>
@@ -1390,119 +1390,119 @@
         <v>1.4</v>
       </c>
       <c r="W5" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y5" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB5" t="n">
-        <v>44</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
         <v>8.4</v>
       </c>
       <c r="AD5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>40</v>
+      </c>
+      <c r="AJ5" t="n">
         <v>500</v>
       </c>
-      <c r="AE5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
       <c r="AK5" t="n">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="AO5" t="n">
-        <v>500</v>
+        <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="AR5" t="n">
         <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>7.4</v>
+        <v>11.5</v>
       </c>
       <c r="AT5" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="AU5" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>6.8</v>
+        <v>17</v>
       </c>
       <c r="AX5" t="n">
-        <v>6</v>
+        <v>14.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AZ5" t="n">
-        <v>8.800000000000001</v>
+        <v>13.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="BB5" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BC5" t="n">
-        <v>9.199999999999999</v>
+        <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="BE5" t="n">
-        <v>7.4</v>
+        <v>25</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.5</v>
+        <v>12</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.8</v>
+        <v>22</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1533,25 +1533,25 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="G6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H6" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I6" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>1.08</v>
@@ -1566,52 +1566,52 @@
         <v>1.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
         <v>1.29</v>
       </c>
       <c r="S6" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U6" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W6" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="X6" t="n">
         <v>12.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>310</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
         <v>10.5</v>
@@ -1620,22 +1620,22 @@
         <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="AK6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL6" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AO6" t="n">
         <v>1000</v>
@@ -1653,19 +1653,19 @@
         <v>28</v>
       </c>
       <c r="AT6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
         <v>7.2</v>
       </c>
       <c r="AV6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW6" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AX6" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
         <v>9.199999999999999</v>
@@ -1677,7 +1677,7 @@
         <v>27</v>
       </c>
       <c r="BB6" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BC6" t="n">
         <v>15</v>
@@ -1686,17 +1686,17 @@
         <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF6" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H7" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M7" t="n">
         <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O7" t="n">
         <v>1.33</v>
@@ -1769,16 +1769,16 @@
         <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V7" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="X7" t="n">
         <v>14.5</v>
@@ -1787,16 +1787,16 @@
         <v>13</v>
       </c>
       <c r="Z7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB7" t="n">
         <v>11</v>
       </c>
       <c r="AC7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
         <v>14</v>
@@ -1805,7 +1805,7 @@
         <v>38</v>
       </c>
       <c r="AF7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AG7" t="n">
         <v>11</v>
@@ -1814,25 +1814,25 @@
         <v>17</v>
       </c>
       <c r="AI7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AJ7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
         <v>38</v>
       </c>
       <c r="AM7" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN7" t="n">
         <v>20</v>
       </c>
       <c r="AO7" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AP7" t="n">
         <v>13</v>
@@ -1844,7 +1844,7 @@
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="AT7" t="n">
         <v>9.800000000000001</v>
@@ -1856,7 +1856,7 @@
         <v>13</v>
       </c>
       <c r="AW7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AX7" t="n">
         <v>13.5</v>
@@ -1871,26 +1871,26 @@
         <v>40</v>
       </c>
       <c r="BB7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BC7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE7" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="BF7" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="G8" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H8" t="n">
         <v>3.85</v>
@@ -1933,67 +1933,67 @@
         <v>3.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S8" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="T8" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.98</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.97</v>
       </c>
       <c r="V8" t="n">
         <v>1.34</v>
       </c>
       <c r="W8" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA8" t="n">
         <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE8" t="n">
         <v>55</v>
@@ -2005,25 +2005,25 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI8" t="n">
         <v>70</v>
       </c>
       <c r="AJ8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL8" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM8" t="n">
         <v>150</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>75</v>
@@ -2035,7 +2035,7 @@
         <v>10.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
         <v>65</v>
@@ -2044,13 +2044,13 @@
         <v>7.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV8" t="n">
         <v>14.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX8" t="n">
         <v>11.5</v>
@@ -2059,22 +2059,22 @@
         <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>55</v>
       </c>
       <c r="BB8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD8" t="n">
         <v>40</v>
       </c>
       <c r="BE8" t="n">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="BF8" t="n">
         <v>21</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G9" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="H9" t="n">
         <v>6.6</v>
@@ -2127,158 +2127,158 @@
         <v>7</v>
       </c>
       <c r="J9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.5</v>
       </c>
-      <c r="K9" t="n">
-        <v>3.55</v>
-      </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="P9" t="n">
         <v>1.63</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2309,16 +2309,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H10" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="I10" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J10" t="n">
         <v>4.3</v>
@@ -2351,7 +2351,7 @@
         <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
         <v>1.74</v>
@@ -2375,13 +2375,13 @@
         <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC10" t="n">
         <v>10</v>
       </c>
       <c r="AD10" t="n">
-        <v>120</v>
+        <v>50</v>
       </c>
       <c r="AE10" t="n">
         <v>700</v>
@@ -2399,7 +2399,7 @@
         <v>700</v>
       </c>
       <c r="AJ10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK10" t="n">
         <v>20</v>
@@ -2417,7 +2417,7 @@
         <v>700</v>
       </c>
       <c r="AP10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
         <v>17</v>
@@ -2426,22 +2426,22 @@
         <v>27</v>
       </c>
       <c r="AS10" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AT10" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AU10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AV10" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY10" t="n">
         <v>8.800000000000001</v>
@@ -2450,19 +2450,19 @@
         <v>18.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC10" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BD10" t="n">
         <v>20</v>
       </c>
       <c r="BE10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="BF10" t="n">
         <v>9.4</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2503,61 +2503,61 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="G11" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="H11" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="J11" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="K11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
         <v>1.55</v>
       </c>
       <c r="R11" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S11" t="n">
         <v>2.36</v>
       </c>
       <c r="T11" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="W11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="Y11" t="n">
         <v>46</v>
@@ -2572,40 +2572,40 @@
         <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG11" t="n">
         <v>12</v>
       </c>
       <c r="AH11" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AL11" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="AM11" t="n">
         <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
@@ -2614,59 +2614,59 @@
         <v>6.6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT11" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU11" t="n">
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW11" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX11" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AY11" t="n">
         <v>6.4</v>
       </c>
       <c r="AZ11" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
         <v>5.1</v>
       </c>
       <c r="BC11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD11" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BG11" t="n">
         <v>10.5</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2697,73 +2697,73 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="G12" t="n">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M12" t="n">
         <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
         <v>1.76</v>
       </c>
       <c r="U12" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V12" t="n">
         <v>1.27</v>
       </c>
       <c r="W12" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AA12" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AB12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC12" t="n">
         <v>8.6</v>
@@ -2775,7 +2775,7 @@
         <v>55</v>
       </c>
       <c r="AF12" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
         <v>10</v>
@@ -2787,40 +2787,40 @@
         <v>55</v>
       </c>
       <c r="AJ12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK12" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AL12" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AM12" t="n">
         <v>85</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AP12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AR12" t="n">
         <v>30</v>
       </c>
       <c r="AS12" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="AT12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>16</v>
@@ -2835,32 +2835,32 @@
         <v>9.6</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BB12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="BF12" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="I13" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
         <v>3.25</v>
@@ -2936,13 +2936,13 @@
         <v>2.02</v>
       </c>
       <c r="U13" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="V13" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="X13" t="n">
         <v>13.5</v>
@@ -2954,7 +2954,7 @@
         <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB13" t="n">
         <v>13.5</v>
@@ -2978,10 +2978,10 @@
         <v>500</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2999,16 +2999,16 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AQ13" t="n">
         <v>6.2</v>
       </c>
       <c r="AR13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
         <v>6.6</v>
@@ -3020,10 +3020,10 @@
         <v>7</v>
       </c>
       <c r="AW13" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="AY13" t="n">
         <v>8</v>
@@ -3032,29 +3032,29 @@
         <v>10</v>
       </c>
       <c r="BA13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BD13" t="n">
         <v>9.6</v>
       </c>
-      <c r="BB13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BE13" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG13" t="n">
         <v>10</v>
       </c>
-      <c r="BF13" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-01 10:01:22</t>
+          <t>2026-04-01 12:12:56</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="G14" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I14" t="n">
         <v>4.2</v>
@@ -3100,13 +3100,13 @@
         <v>3.4</v>
       </c>
       <c r="K14" t="n">
-        <v>3.5